--- a/configs/Item.xlsx
+++ b/configs/Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84501539-6FF4-4E8C-82CD-565F44B11477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8A2C92-A661-44CA-B01D-C4D8D71ED4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$R$334</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$T$334</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="894">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="912">
   <si>
     <t>id</t>
   </si>
@@ -2723,6 +2723,60 @@
   </si>
   <si>
     <t>镶孔个数</t>
+  </si>
+  <si>
+    <t>INV_Sword_122</t>
+  </si>
+  <si>
+    <t>INV_Sword_137</t>
+  </si>
+  <si>
+    <t>INV_Axe_66</t>
+  </si>
+  <si>
+    <t>INV_Sword_119</t>
+  </si>
+  <si>
+    <t>INV_Sword_138</t>
+  </si>
+  <si>
+    <t>INV_Sword_120</t>
+  </si>
+  <si>
+    <t>INV_Sword_128</t>
+  </si>
+  <si>
+    <t>INV_Sword_156</t>
+  </si>
+  <si>
+    <t>INV_Staff_102</t>
+  </si>
+  <si>
+    <t>INV_Axe_116</t>
+  </si>
+  <si>
+    <t>rwOrder</t>
+  </si>
+  <si>
+    <t>ItemId[]</t>
+  </si>
+  <si>
+    <t>符文之语</t>
+  </si>
+  <si>
+    <t>rune23,rune17,rune23,rune18</t>
+  </si>
+  <si>
+    <t>$ed1,0/xfthp/:</t>
+  </si>
+  <si>
+    <t>killbclv1,0:spd1,0:tlr1,0</t>
+  </si>
+  <si>
+    <t>affixCount</t>
+  </si>
+  <si>
+    <t>通用词缀个数</t>
   </si>
 </sst>
 </file>
@@ -3119,7 +3173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:R334"/>
+  <dimension ref="A1:X337"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
@@ -3136,11 +3190,13 @@
     <col min="12" max="12" width="25.1796875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" customWidth="1"/>
+    <col min="16" max="16" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3184,19 +3240,25 @@
         <v>678</v>
       </c>
       <c r="O1" t="s">
+        <v>910</v>
+      </c>
+      <c r="P1" t="s">
         <v>686</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>762</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
+        <v>904</v>
+      </c>
+      <c r="S1" t="s">
         <v>768</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>892</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>824</v>
       </c>
@@ -3240,24 +3302,30 @@
         <v>5</v>
       </c>
       <c r="O2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P2" t="s">
         <v>668</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>763</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
+        <v>905</v>
+      </c>
+      <c r="S2" t="s">
         <v>5</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>498</v>
       </c>
@@ -3301,19 +3369,25 @@
         <v>680</v>
       </c>
       <c r="O4" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -3350,11 +3424,11 @@
       <c r="M5" t="s">
         <v>785</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -3385,11 +3459,11 @@
       <c r="L6" t="s">
         <v>772</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>116</v>
       </c>
@@ -3423,11 +3497,11 @@
       <c r="M7" t="s">
         <v>785</v>
       </c>
-      <c r="R7">
+      <c r="T7">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>117</v>
       </c>
@@ -3458,11 +3532,11 @@
       <c r="L8" t="s">
         <v>774</v>
       </c>
-      <c r="R8">
+      <c r="T8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>118</v>
       </c>
@@ -3496,11 +3570,11 @@
       <c r="M9" t="s">
         <v>785</v>
       </c>
-      <c r="R9">
+      <c r="T9">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>119</v>
       </c>
@@ -3531,11 +3605,11 @@
       <c r="L10" t="s">
         <v>780</v>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>120</v>
       </c>
@@ -3566,11 +3640,11 @@
       <c r="L11" t="s">
         <v>672</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>164</v>
       </c>
@@ -3601,11 +3675,11 @@
       <c r="L12" t="s">
         <v>674</v>
       </c>
-      <c r="R12">
+      <c r="T12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>126</v>
       </c>
@@ -3641,7 +3715,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>127</v>
       </c>
@@ -3677,7 +3751,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>128</v>
       </c>
@@ -3713,7 +3787,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>129</v>
       </c>
@@ -3749,7 +3823,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>134</v>
       </c>
@@ -3785,7 +3859,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>135</v>
       </c>
@@ -3821,7 +3895,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>136</v>
       </c>
@@ -3857,7 +3931,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>137</v>
       </c>
@@ -3893,7 +3967,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>146</v>
       </c>
@@ -3929,7 +4003,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>147</v>
       </c>
@@ -3965,7 +4039,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>148</v>
       </c>
@@ -4001,7 +4075,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>149</v>
       </c>
@@ -4037,7 +4111,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>346</v>
       </c>
@@ -4064,7 +4138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>534</v>
       </c>
@@ -4091,7 +4165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>535</v>
       </c>
@@ -4118,7 +4192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>536</v>
       </c>
@@ -4145,7 +4219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>537</v>
       </c>
@@ -4172,7 +4246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>538</v>
       </c>
@@ -4199,7 +4273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>384</v>
       </c>
@@ -4228,11 +4302,11 @@
       <c r="K31">
         <v>1</v>
       </c>
-      <c r="R31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>385</v>
       </c>
@@ -4261,11 +4335,11 @@
       <c r="K32">
         <v>1</v>
       </c>
-      <c r="R32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>386</v>
       </c>
@@ -4294,11 +4368,11 @@
       <c r="K33">
         <v>1</v>
       </c>
-      <c r="R33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>387</v>
       </c>
@@ -4327,11 +4401,11 @@
       <c r="K34">
         <v>1</v>
       </c>
-      <c r="R34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>388</v>
       </c>
@@ -4360,11 +4434,11 @@
       <c r="K35">
         <v>1</v>
       </c>
-      <c r="R35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>389</v>
       </c>
@@ -4393,11 +4467,11 @@
       <c r="K36">
         <v>1</v>
       </c>
-      <c r="R36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>390</v>
       </c>
@@ -4426,11 +4500,11 @@
       <c r="K37">
         <v>1</v>
       </c>
-      <c r="R37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>391</v>
       </c>
@@ -4457,7 +4531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>411</v>
       </c>
@@ -4484,7 +4558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>414</v>
       </c>
@@ -4511,7 +4585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>418</v>
       </c>
@@ -4538,7 +4612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>419</v>
       </c>
@@ -4565,7 +4639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>422</v>
       </c>
@@ -4595,7 +4669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>436</v>
       </c>
@@ -4622,7 +4696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>437</v>
       </c>
@@ -4649,7 +4723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>550</v>
       </c>
@@ -4676,7 +4750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>551</v>
       </c>
@@ -4703,7 +4777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>552</v>
       </c>
@@ -4730,7 +4804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>553</v>
       </c>
@@ -4757,7 +4831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>554</v>
       </c>
@@ -4784,7 +4858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>555</v>
       </c>
@@ -4811,7 +4885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>556</v>
       </c>
@@ -4838,7 +4912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>557</v>
       </c>
@@ -4865,7 +4939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>558</v>
       </c>
@@ -4892,7 +4966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>559</v>
       </c>
@@ -4919,7 +4993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>560</v>
       </c>
@@ -4946,7 +5020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>400</v>
       </c>
@@ -4975,11 +5049,11 @@
       <c r="K57">
         <v>1</v>
       </c>
-      <c r="R57">
+      <c r="T57">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>401</v>
       </c>
@@ -5008,11 +5082,11 @@
       <c r="K58">
         <v>1</v>
       </c>
-      <c r="R58">
+      <c r="T58">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>402</v>
       </c>
@@ -5041,11 +5115,11 @@
       <c r="K59">
         <v>1</v>
       </c>
-      <c r="R59">
+      <c r="T59">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>403</v>
       </c>
@@ -5074,11 +5148,11 @@
       <c r="K60">
         <v>1</v>
       </c>
-      <c r="R60">
+      <c r="T60">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>404</v>
       </c>
@@ -5107,11 +5181,11 @@
       <c r="K61">
         <v>1</v>
       </c>
-      <c r="R61">
+      <c r="T61">
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>405</v>
       </c>
@@ -5140,11 +5214,11 @@
       <c r="K62">
         <v>1</v>
       </c>
-      <c r="R62">
+      <c r="T62">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>406</v>
       </c>
@@ -5173,11 +5247,11 @@
       <c r="K63">
         <v>1</v>
       </c>
-      <c r="R63">
+      <c r="T63">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>407</v>
       </c>
@@ -5639,7 +5713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>579</v>
       </c>
@@ -5666,7 +5740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>580</v>
       </c>
@@ -5693,7 +5767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>494</v>
       </c>
@@ -5722,7 +5796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>495</v>
       </c>
@@ -5751,7 +5825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>496</v>
       </c>
@@ -5780,7 +5854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>373</v>
       </c>
@@ -5809,11 +5883,11 @@
       <c r="K86">
         <v>1</v>
       </c>
-      <c r="R86">
+      <c r="T86">
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>374</v>
       </c>
@@ -5842,11 +5916,11 @@
       <c r="K87">
         <v>1</v>
       </c>
-      <c r="R87">
+      <c r="T87">
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>375</v>
       </c>
@@ -5875,11 +5949,11 @@
       <c r="K88">
         <v>1</v>
       </c>
-      <c r="R88">
+      <c r="T88">
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>376</v>
       </c>
@@ -5908,11 +5982,11 @@
       <c r="K89">
         <v>1</v>
       </c>
-      <c r="R89">
+      <c r="T89">
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>377</v>
       </c>
@@ -5941,11 +6015,11 @@
       <c r="K90">
         <v>1</v>
       </c>
-      <c r="R90">
+      <c r="T90">
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>378</v>
       </c>
@@ -5974,11 +6048,11 @@
       <c r="K91">
         <v>1</v>
       </c>
-      <c r="R91">
+      <c r="T91">
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>379</v>
       </c>
@@ -6007,11 +6081,11 @@
       <c r="K92">
         <v>1</v>
       </c>
-      <c r="R92">
+      <c r="T92">
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>380</v>
       </c>
@@ -6038,7 +6112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>381</v>
       </c>
@@ -6065,7 +6139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>382</v>
       </c>
@@ -6092,7 +6166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>383</v>
       </c>
@@ -6119,7 +6193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>412</v>
       </c>
@@ -6146,7 +6220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>421</v>
       </c>
@@ -6173,7 +6247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>427</v>
       </c>
@@ -6200,7 +6274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>431</v>
       </c>
@@ -6227,7 +6301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>441</v>
       </c>
@@ -6254,7 +6328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>591</v>
       </c>
@@ -6281,7 +6355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>592</v>
       </c>
@@ -6308,7 +6382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>593</v>
       </c>
@@ -6335,7 +6409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>594</v>
       </c>
@@ -6362,7 +6436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>595</v>
       </c>
@@ -6389,7 +6463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>596</v>
       </c>
@@ -6416,7 +6490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>597</v>
       </c>
@@ -6443,7 +6517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>598</v>
       </c>
@@ -6470,7 +6544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>599</v>
       </c>
@@ -6497,7 +6571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>600</v>
       </c>
@@ -6524,7 +6598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>150</v>
       </c>
@@ -6553,11 +6627,11 @@
       <c r="K112">
         <v>1</v>
       </c>
-      <c r="R112">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T112">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>502</v>
       </c>
@@ -6586,11 +6660,11 @@
       <c r="K113">
         <v>1</v>
       </c>
-      <c r="R113">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T113">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>503</v>
       </c>
@@ -6619,11 +6693,11 @@
       <c r="K114">
         <v>1</v>
       </c>
-      <c r="R114">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T114">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>504</v>
       </c>
@@ -6655,11 +6729,11 @@
       <c r="L115" t="s">
         <v>771</v>
       </c>
-      <c r="R115">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T115">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>505</v>
       </c>
@@ -6688,11 +6762,11 @@
       <c r="K116">
         <v>1</v>
       </c>
-      <c r="R116">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T116">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>506</v>
       </c>
@@ -6721,11 +6795,11 @@
       <c r="K117">
         <v>1</v>
       </c>
-      <c r="R117">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T117">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>507</v>
       </c>
@@ -6754,11 +6828,11 @@
       <c r="K118">
         <v>1</v>
       </c>
-      <c r="R118">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T118">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>508</v>
       </c>
@@ -6791,7 +6865,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>509</v>
       </c>
@@ -6824,7 +6898,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>510</v>
       </c>
@@ -6854,7 +6928,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>511</v>
       </c>
@@ -6884,7 +6958,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>512</v>
       </c>
@@ -6917,7 +6991,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>513</v>
       </c>
@@ -6950,7 +7024,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>514</v>
       </c>
@@ -6983,7 +7057,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>429</v>
       </c>
@@ -7010,7 +7084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>433</v>
       </c>
@@ -7040,7 +7114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>434</v>
       </c>
@@ -7070,7 +7144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>435</v>
       </c>
@@ -7100,7 +7174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>609</v>
       </c>
@@ -7127,7 +7201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>610</v>
       </c>
@@ -7154,7 +7228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>611</v>
       </c>
@@ -7181,7 +7255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>612</v>
       </c>
@@ -7208,7 +7282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>613</v>
       </c>
@@ -7235,7 +7309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>614</v>
       </c>
@@ -7262,7 +7336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>615</v>
       </c>
@@ -7289,7 +7363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>616</v>
       </c>
@@ -7316,7 +7390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>825</v>
       </c>
@@ -7344,11 +7418,11 @@
       <c r="K138">
         <v>1</v>
       </c>
-      <c r="R138">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>472</v>
       </c>
@@ -7378,7 +7452,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>473</v>
       </c>
@@ -7408,7 +7482,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>474</v>
       </c>
@@ -7438,7 +7512,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>475</v>
       </c>
@@ -7468,7 +7542,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>476</v>
       </c>
@@ -7498,7 +7572,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>477</v>
       </c>
@@ -8011,7 +8085,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>621</v>
       </c>
@@ -8038,7 +8112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>622</v>
       </c>
@@ -8065,7 +8139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>623</v>
       </c>
@@ -8092,7 +8166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>624</v>
       </c>
@@ -8119,7 +8193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>392</v>
       </c>
@@ -8148,11 +8222,11 @@
       <c r="K165">
         <v>1</v>
       </c>
-      <c r="R165">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T165">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>393</v>
       </c>
@@ -8181,11 +8255,11 @@
       <c r="K166">
         <v>1</v>
       </c>
-      <c r="R166">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T166">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>394</v>
       </c>
@@ -8214,11 +8288,11 @@
       <c r="K167">
         <v>1</v>
       </c>
-      <c r="R167">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T167">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>395</v>
       </c>
@@ -8247,11 +8321,11 @@
       <c r="K168">
         <v>1</v>
       </c>
-      <c r="R168">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T168">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>396</v>
       </c>
@@ -8280,11 +8354,11 @@
       <c r="K169">
         <v>1</v>
       </c>
-      <c r="R169">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T169">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>397</v>
       </c>
@@ -8313,11 +8387,11 @@
       <c r="K170">
         <v>1</v>
       </c>
-      <c r="R170">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T170">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>398</v>
       </c>
@@ -8346,11 +8420,11 @@
       <c r="K171">
         <v>1</v>
       </c>
-      <c r="R171">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T171">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>399</v>
       </c>
@@ -8377,7 +8451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>413</v>
       </c>
@@ -8404,7 +8478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>415</v>
       </c>
@@ -8431,7 +8505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>416</v>
       </c>
@@ -8458,7 +8532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>420</v>
       </c>
@@ -8485,7 +8559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>424</v>
       </c>
@@ -8512,7 +8586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>426</v>
       </c>
@@ -8539,7 +8613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>432</v>
       </c>
@@ -8566,7 +8640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>442</v>
       </c>
@@ -8593,7 +8667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>635</v>
       </c>
@@ -8620,7 +8694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>636</v>
       </c>
@@ -8647,7 +8721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>637</v>
       </c>
@@ -8674,7 +8748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>638</v>
       </c>
@@ -8701,7 +8775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>639</v>
       </c>
@@ -8728,7 +8802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>640</v>
       </c>
@@ -8755,7 +8829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>641</v>
       </c>
@@ -8782,7 +8856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>642</v>
       </c>
@@ -8809,7 +8883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>643</v>
       </c>
@@ -8836,7 +8910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>644</v>
       </c>
@@ -8863,7 +8937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>515</v>
       </c>
@@ -8892,11 +8966,11 @@
       <c r="K191">
         <v>1</v>
       </c>
-      <c r="R191">
+      <c r="T191">
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>516</v>
       </c>
@@ -8925,11 +8999,11 @@
       <c r="K192">
         <v>1</v>
       </c>
-      <c r="R192">
+      <c r="T192">
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>517</v>
       </c>
@@ -8958,11 +9032,11 @@
       <c r="K193">
         <v>1</v>
       </c>
-      <c r="R193">
+      <c r="T193">
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>518</v>
       </c>
@@ -8991,11 +9065,11 @@
       <c r="K194">
         <v>1</v>
       </c>
-      <c r="R194">
+      <c r="T194">
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>519</v>
       </c>
@@ -9024,11 +9098,11 @@
       <c r="K195">
         <v>1</v>
       </c>
-      <c r="R195">
+      <c r="T195">
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>520</v>
       </c>
@@ -9057,11 +9131,11 @@
       <c r="K196">
         <v>1</v>
       </c>
-      <c r="R196">
+      <c r="T196">
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>521</v>
       </c>
@@ -9090,11 +9164,11 @@
       <c r="K197">
         <v>1</v>
       </c>
-      <c r="R197">
+      <c r="T197">
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>522</v>
       </c>
@@ -9121,7 +9195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>523</v>
       </c>
@@ -9148,7 +9222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>524</v>
       </c>
@@ -9175,7 +9249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>525</v>
       </c>
@@ -9202,7 +9276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>526</v>
       </c>
@@ -9229,7 +9303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>527</v>
       </c>
@@ -9256,7 +9330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>528</v>
       </c>
@@ -9283,7 +9357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>428</v>
       </c>
@@ -9310,7 +9384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>440</v>
       </c>
@@ -9337,7 +9411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>657</v>
       </c>
@@ -9364,7 +9438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>658</v>
       </c>
@@ -9391,7 +9465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>659</v>
       </c>
@@ -9418,7 +9492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>660</v>
       </c>
@@ -9445,7 +9519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>661</v>
       </c>
@@ -9472,7 +9546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>662</v>
       </c>
@@ -9499,7 +9573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>663</v>
       </c>
@@ -9526,7 +9600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>664</v>
       </c>
@@ -9553,7 +9627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>665</v>
       </c>
@@ -9580,7 +9654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>666</v>
       </c>
@@ -9607,7 +9681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>827</v>
       </c>
@@ -9635,11 +9709,11 @@
       <c r="K217">
         <v>1</v>
       </c>
-      <c r="R217">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>447</v>
       </c>
@@ -9666,7 +9740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>448</v>
       </c>
@@ -9693,7 +9767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>449</v>
       </c>
@@ -9720,7 +9794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>450</v>
       </c>
@@ -9747,7 +9821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>451</v>
       </c>
@@ -9774,7 +9848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>452</v>
       </c>
@@ -9801,7 +9875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>453</v>
       </c>
@@ -10260,7 +10334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>470</v>
       </c>
@@ -10287,7 +10361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>471</v>
       </c>
@@ -10314,7 +10388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>646</v>
       </c>
@@ -10341,7 +10415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>6</v>
       </c>
@@ -10375,11 +10449,11 @@
       <c r="L244" t="s">
         <v>798</v>
       </c>
-      <c r="R244">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T244">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="245" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>7</v>
       </c>
@@ -10413,11 +10487,11 @@
       <c r="L245" t="s">
         <v>805</v>
       </c>
-      <c r="R245">
+      <c r="T245">
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>8</v>
       </c>
@@ -10454,11 +10528,11 @@
       <c r="M246" t="s">
         <v>806</v>
       </c>
-      <c r="R246">
+      <c r="T246">
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>9</v>
       </c>
@@ -10492,11 +10566,11 @@
       <c r="L247" t="s">
         <v>800</v>
       </c>
-      <c r="R247">
+      <c r="T247">
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>10</v>
       </c>
@@ -10530,11 +10604,11 @@
       <c r="L248" t="s">
         <v>801</v>
       </c>
-      <c r="R248">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T248">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>11</v>
       </c>
@@ -10568,11 +10642,11 @@
       <c r="L249" t="s">
         <v>802</v>
       </c>
-      <c r="R249">
+      <c r="T249">
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>13</v>
       </c>
@@ -10606,11 +10680,11 @@
       <c r="L250" t="s">
         <v>803</v>
       </c>
-      <c r="R250">
+      <c r="T250">
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>12</v>
       </c>
@@ -10642,7 +10716,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>14</v>
       </c>
@@ -10674,7 +10748,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>15</v>
       </c>
@@ -10694,7 +10768,7 @@
         <v>81</v>
       </c>
       <c r="H253" t="s">
-        <v>39</v>
+        <v>895</v>
       </c>
       <c r="I253" t="s">
         <v>42</v>
@@ -10709,7 +10783,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>16</v>
       </c>
@@ -10729,7 +10803,7 @@
         <v>83</v>
       </c>
       <c r="H254" t="s">
-        <v>39</v>
+        <v>894</v>
       </c>
       <c r="I254" t="s">
         <v>42</v>
@@ -10744,7 +10818,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>17</v>
       </c>
@@ -10764,7 +10838,7 @@
         <v>84</v>
       </c>
       <c r="H255" t="s">
-        <v>39</v>
+        <v>896</v>
       </c>
       <c r="I255" t="s">
         <v>42</v>
@@ -10779,7 +10853,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>18</v>
       </c>
@@ -10799,7 +10873,7 @@
         <v>85</v>
       </c>
       <c r="H256" t="s">
-        <v>39</v>
+        <v>897</v>
       </c>
       <c r="I256" t="s">
         <v>42</v>
@@ -10834,7 +10908,7 @@
         <v>86</v>
       </c>
       <c r="H257" t="s">
-        <v>39</v>
+        <v>898</v>
       </c>
       <c r="I257" t="s">
         <v>42</v>
@@ -10869,7 +10943,7 @@
         <v>87</v>
       </c>
       <c r="H258" t="s">
-        <v>39</v>
+        <v>899</v>
       </c>
       <c r="I258" t="s">
         <v>42</v>
@@ -10904,7 +10978,7 @@
         <v>88</v>
       </c>
       <c r="H259" t="s">
-        <v>39</v>
+        <v>900</v>
       </c>
       <c r="I259" t="s">
         <v>42</v>
@@ -10939,7 +11013,7 @@
         <v>89</v>
       </c>
       <c r="H260" t="s">
-        <v>39</v>
+        <v>901</v>
       </c>
       <c r="I260" t="s">
         <v>42</v>
@@ -10974,7 +11048,7 @@
         <v>91</v>
       </c>
       <c r="H261" t="s">
-        <v>39</v>
+        <v>902</v>
       </c>
       <c r="I261" t="s">
         <v>42</v>
@@ -11009,7 +11083,7 @@
         <v>93</v>
       </c>
       <c r="H262" t="s">
-        <v>39</v>
+        <v>903</v>
       </c>
       <c r="I262" t="s">
         <v>42</v>
@@ -11395,7 +11469,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>497</v>
       </c>
@@ -11422,7 +11496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>499</v>
       </c>
@@ -11449,7 +11523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>500</v>
       </c>
@@ -11476,7 +11550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>501</v>
       </c>
@@ -11503,7 +11577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>439</v>
       </c>
@@ -11533,7 +11607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>443</v>
       </c>
@@ -11563,7 +11637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>444</v>
       </c>
@@ -11593,7 +11667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>445</v>
       </c>
@@ -11623,7 +11697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>446</v>
       </c>
@@ -11650,7 +11724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>347</v>
       </c>
@@ -11679,11 +11753,11 @@
       <c r="K282">
         <v>1</v>
       </c>
-      <c r="R282">
+      <c r="T282">
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>348</v>
       </c>
@@ -11712,11 +11786,11 @@
       <c r="K283">
         <v>1</v>
       </c>
-      <c r="R283">
+      <c r="T283">
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>349</v>
       </c>
@@ -11745,11 +11819,11 @@
       <c r="K284">
         <v>1</v>
       </c>
-      <c r="R284">
+      <c r="T284">
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>350</v>
       </c>
@@ -11778,11 +11852,11 @@
       <c r="K285">
         <v>1</v>
       </c>
-      <c r="R285">
+      <c r="T285">
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>351</v>
       </c>
@@ -11811,11 +11885,11 @@
       <c r="K286">
         <v>1</v>
       </c>
-      <c r="R286">
+      <c r="T286">
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>352</v>
       </c>
@@ -11844,11 +11918,11 @@
       <c r="K287">
         <v>1</v>
       </c>
-      <c r="R287">
+      <c r="T287">
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>353</v>
       </c>
@@ -11877,7 +11951,7 @@
       <c r="K288">
         <v>1</v>
       </c>
-      <c r="R288">
+      <c r="T288">
         <v>2</v>
       </c>
     </row>
@@ -12771,7 +12845,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="321" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>744</v>
       </c>
@@ -12800,7 +12874,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="322" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>745</v>
       </c>
@@ -12829,7 +12903,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="323" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>746</v>
       </c>
@@ -12858,7 +12932,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="324" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>747</v>
       </c>
@@ -12887,7 +12961,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="325" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>748</v>
       </c>
@@ -12916,7 +12990,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="326" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>749</v>
       </c>
@@ -12945,7 +13019,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>750</v>
       </c>
@@ -12974,7 +13048,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>751</v>
       </c>
@@ -13003,7 +13077,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="329" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>752</v>
       </c>
@@ -13032,7 +13106,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="330" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>753</v>
       </c>
@@ -13061,7 +13135,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="331" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>754</v>
       </c>
@@ -13090,7 +13164,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="332" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>755</v>
       </c>
@@ -13119,7 +13193,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="333" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>759</v>
       </c>
@@ -13143,13 +13217,25 @@
         <v>761</v>
       </c>
       <c r="K333">
-        <v>2</v>
-      </c>
-      <c r="P333" t="s">
+        <v>1</v>
+      </c>
+      <c r="L333" t="s">
+        <v>909</v>
+      </c>
+      <c r="M333" t="s">
+        <v>908</v>
+      </c>
+      <c r="O333">
+        <v>1</v>
+      </c>
+      <c r="Q333" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="334" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R333" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="334" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>765</v>
       </c>
@@ -13172,12 +13258,46 @@
       <c r="J334" t="s">
         <v>761</v>
       </c>
-      <c r="Q334">
+      <c r="S334">
         <v>2</v>
       </c>
+      <c r="W334">
+        <v>30</v>
+      </c>
+      <c r="X334">
+        <f>W334/33*25</f>
+        <v>22.727272727272727</v>
+      </c>
+    </row>
+    <row r="335" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="W335">
+        <v>23</v>
+      </c>
+      <c r="X335">
+        <f t="shared" ref="X335:X337" si="7">W335/33*25</f>
+        <v>17.424242424242426</v>
+      </c>
+    </row>
+    <row r="336" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="W336">
+        <v>30</v>
+      </c>
+      <c r="X336">
+        <f t="shared" si="7"/>
+        <v>22.727272727272727</v>
+      </c>
+    </row>
+    <row r="337" spans="23:24" x14ac:dyDescent="0.35">
+      <c r="W337">
+        <v>24</v>
+      </c>
+      <c r="X337">
+        <f t="shared" si="7"/>
+        <v>18.181818181818183</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R334" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}"/>
+  <autoFilter ref="A4:T334" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="12"/>

--- a/configs/Item.xlsx
+++ b/configs/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB10712-3523-42C6-9CD0-365432E56840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F1159F-FAB9-4C37-A206-1E87997F7588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2158,81 +2158,6 @@
     <t>bracelet</t>
   </si>
   <si>
-    <t>金灵珠</t>
-  </si>
-  <si>
-    <t>木灵珠</t>
-  </si>
-  <si>
-    <t>水灵珠</t>
-  </si>
-  <si>
-    <t>火灵珠</t>
-  </si>
-  <si>
-    <t>土灵珠</t>
-  </si>
-  <si>
-    <t>破碎金灵珠</t>
-  </si>
-  <si>
-    <t>破碎木灵珠</t>
-  </si>
-  <si>
-    <t>破碎水灵珠</t>
-  </si>
-  <si>
-    <t>破碎火灵珠</t>
-  </si>
-  <si>
-    <t>破碎土灵珠</t>
-  </si>
-  <si>
-    <t>开裂金灵珠</t>
-  </si>
-  <si>
-    <t>开裂木灵珠</t>
-  </si>
-  <si>
-    <t>开裂水灵珠</t>
-  </si>
-  <si>
-    <t>开裂火灵珠</t>
-  </si>
-  <si>
-    <t>开裂土灵珠</t>
-  </si>
-  <si>
-    <t>无瑕金灵珠</t>
-  </si>
-  <si>
-    <t>无瑕木灵珠</t>
-  </si>
-  <si>
-    <t>无瑕水灵珠</t>
-  </si>
-  <si>
-    <t>无瑕火灵珠</t>
-  </si>
-  <si>
-    <t>无瑕土灵珠</t>
-  </si>
-  <si>
-    <t>完美金灵珠</t>
-  </si>
-  <si>
-    <t>完美木灵珠</t>
-  </si>
-  <si>
-    <t>完美水灵珠</t>
-  </si>
-  <si>
-    <t>完美火灵珠</t>
-  </si>
-  <si>
-    <t>完美土灵珠</t>
-  </si>
-  <si>
     <t>rune1</t>
   </si>
   <si>
@@ -2822,25 +2747,132 @@
   </si>
   <si>
     <t>sok1,sok2,sok3,sok4,sok5,rw1</t>
+  </si>
+  <si>
+    <t>​​焚​</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崩​</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>​​铠​</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>​​涵​</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>​​炜​</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>​​冲​</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>​​熄​</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>销</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>栅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>润</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>塌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="1"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2870,12 +2902,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2902,7 +2936,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3219,29 +3253,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
   <dimension ref="A1:W337"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.81640625" customWidth="1"/>
-    <col min="8" max="8" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.54296875" customWidth="1"/>
-    <col min="11" max="11" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.875" customWidth="1"/>
+    <col min="8" max="8" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="25.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3255,7 +3289,7 @@
         <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>828</v>
+        <v>803</v>
       </c>
       <c r="F1" t="s">
         <v>36</v>
@@ -3285,27 +3319,27 @@
         <v>677</v>
       </c>
       <c r="O1" t="s">
-        <v>909</v>
+        <v>884</v>
       </c>
       <c r="P1" t="s">
         <v>685</v>
       </c>
       <c r="Q1" t="s">
-        <v>761</v>
+        <v>736</v>
       </c>
       <c r="R1" t="s">
-        <v>903</v>
+        <v>878</v>
       </c>
       <c r="S1" t="s">
-        <v>767</v>
+        <v>742</v>
       </c>
       <c r="T1" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>823</v>
+        <v>798</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -3353,27 +3387,27 @@
         <v>667</v>
       </c>
       <c r="Q2" t="s">
-        <v>762</v>
+        <v>737</v>
       </c>
       <c r="R2" t="s">
-        <v>904</v>
+        <v>879</v>
       </c>
       <c r="S2" t="s">
         <v>5</v>
       </c>
       <c r="T2" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>48</v>
       </c>
       <c r="I3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>497</v>
       </c>
@@ -3387,7 +3421,7 @@
         <v>50</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>829</v>
+        <v>804</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>57</v>
@@ -3417,25 +3451,25 @@
         <v>679</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>910</v>
+        <v>885</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>686</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>763</v>
+        <v>738</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>905</v>
+        <v>880</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>768</v>
+        <v>743</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -3455,7 +3489,7 @@
         <v>114</v>
       </c>
       <c r="H5" t="s">
-        <v>878</v>
+        <v>853</v>
       </c>
       <c r="I5" t="s">
         <v>43</v>
@@ -3467,16 +3501,16 @@
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>770</v>
+        <v>745</v>
       </c>
       <c r="M5" t="s">
-        <v>784</v>
+        <v>759</v>
       </c>
       <c r="T5" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -3493,7 +3527,7 @@
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>879</v>
+        <v>854</v>
       </c>
       <c r="I6" t="s">
         <v>43</v>
@@ -3505,13 +3539,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>771</v>
+        <v>746</v>
       </c>
       <c r="T6" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>115</v>
       </c>
@@ -3528,7 +3562,7 @@
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>880</v>
+        <v>855</v>
       </c>
       <c r="I7" t="s">
         <v>43</v>
@@ -3540,16 +3574,16 @@
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>772</v>
+        <v>747</v>
       </c>
       <c r="M7" t="s">
-        <v>784</v>
+        <v>759</v>
       </c>
       <c r="T7" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>116</v>
       </c>
@@ -3566,7 +3600,7 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>881</v>
+        <v>856</v>
       </c>
       <c r="I8" t="s">
         <v>43</v>
@@ -3578,13 +3612,13 @@
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>773</v>
+        <v>748</v>
       </c>
       <c r="T8" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>117</v>
       </c>
@@ -3601,7 +3635,7 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>882</v>
+        <v>857</v>
       </c>
       <c r="I9" t="s">
         <v>43</v>
@@ -3616,13 +3650,13 @@
         <v>670</v>
       </c>
       <c r="M9" t="s">
-        <v>784</v>
+        <v>759</v>
       </c>
       <c r="T9" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -3639,7 +3673,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>883</v>
+        <v>858</v>
       </c>
       <c r="I10" t="s">
         <v>43</v>
@@ -3651,13 +3685,13 @@
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>779</v>
+        <v>754</v>
       </c>
       <c r="T10" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>119</v>
       </c>
@@ -3674,7 +3708,7 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>884</v>
+        <v>859</v>
       </c>
       <c r="I11" t="s">
         <v>43</v>
@@ -3689,10 +3723,10 @@
         <v>671</v>
       </c>
       <c r="T11" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>163</v>
       </c>
@@ -3709,7 +3743,7 @@
         <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>885</v>
+        <v>860</v>
       </c>
       <c r="I12" t="s">
         <v>43</v>
@@ -3724,10 +3758,10 @@
         <v>673</v>
       </c>
       <c r="T12" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>125</v>
       </c>
@@ -3760,10 +3794,10 @@
         <v>671</v>
       </c>
       <c r="M13" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>126</v>
       </c>
@@ -3796,10 +3830,10 @@
         <v>674</v>
       </c>
       <c r="M14" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>127</v>
       </c>
@@ -3829,13 +3863,13 @@
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>780</v>
+        <v>755</v>
       </c>
       <c r="M15" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -3865,13 +3899,13 @@
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>781</v>
+        <v>756</v>
       </c>
       <c r="M16" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>133</v>
       </c>
@@ -3901,13 +3935,13 @@
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>774</v>
+        <v>749</v>
       </c>
       <c r="M17" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>134</v>
       </c>
@@ -3937,13 +3971,13 @@
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="M18" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>135</v>
       </c>
@@ -3973,13 +4007,13 @@
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>769</v>
+        <v>744</v>
       </c>
       <c r="M19" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>136</v>
       </c>
@@ -4009,13 +4043,13 @@
         <v>1</v>
       </c>
       <c r="L20" t="s">
-        <v>782</v>
+        <v>757</v>
       </c>
       <c r="M20" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>145</v>
       </c>
@@ -4045,13 +4079,13 @@
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>776</v>
+        <v>751</v>
       </c>
       <c r="M21" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>146</v>
       </c>
@@ -4081,13 +4115,13 @@
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>777</v>
+        <v>752</v>
       </c>
       <c r="M22" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>147</v>
       </c>
@@ -4117,13 +4151,13 @@
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>778</v>
+        <v>753</v>
       </c>
       <c r="M23" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>148</v>
       </c>
@@ -4153,13 +4187,13 @@
         <v>1</v>
       </c>
       <c r="L24" t="s">
-        <v>783</v>
+        <v>758</v>
       </c>
       <c r="M24" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>345</v>
       </c>
@@ -4186,7 +4220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>533</v>
       </c>
@@ -4213,7 +4247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>534</v>
       </c>
@@ -4240,7 +4274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>535</v>
       </c>
@@ -4267,7 +4301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>536</v>
       </c>
@@ -4294,7 +4328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>537</v>
       </c>
@@ -4321,7 +4355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>383</v>
       </c>
@@ -4351,10 +4385,10 @@
         <v>1</v>
       </c>
       <c r="T31" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>384</v>
       </c>
@@ -4384,10 +4418,10 @@
         <v>1</v>
       </c>
       <c r="T32" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>385</v>
       </c>
@@ -4417,10 +4451,10 @@
         <v>1</v>
       </c>
       <c r="T33" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>386</v>
       </c>
@@ -4450,10 +4484,10 @@
         <v>1</v>
       </c>
       <c r="T34" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>387</v>
       </c>
@@ -4483,10 +4517,10 @@
         <v>1</v>
       </c>
       <c r="T35" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>388</v>
       </c>
@@ -4516,10 +4550,10 @@
         <v>1</v>
       </c>
       <c r="T36" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>389</v>
       </c>
@@ -4549,10 +4583,10 @@
         <v>1</v>
       </c>
       <c r="T37" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>390</v>
       </c>
@@ -4579,7 +4613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>410</v>
       </c>
@@ -4606,7 +4640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>413</v>
       </c>
@@ -4633,7 +4667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>417</v>
       </c>
@@ -4660,7 +4694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>418</v>
       </c>
@@ -4687,7 +4721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>421</v>
       </c>
@@ -4717,7 +4751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>435</v>
       </c>
@@ -4744,7 +4778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>436</v>
       </c>
@@ -4771,7 +4805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>549</v>
       </c>
@@ -4798,7 +4832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>550</v>
       </c>
@@ -4825,7 +4859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>551</v>
       </c>
@@ -4852,7 +4886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>552</v>
       </c>
@@ -4879,7 +4913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>553</v>
       </c>
@@ -4906,7 +4940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>554</v>
       </c>
@@ -4933,7 +4967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>555</v>
       </c>
@@ -4960,7 +4994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>556</v>
       </c>
@@ -4987,7 +5021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>557</v>
       </c>
@@ -5014,7 +5048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>558</v>
       </c>
@@ -5041,7 +5075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>559</v>
       </c>
@@ -5068,7 +5102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>399</v>
       </c>
@@ -5098,10 +5132,10 @@
         <v>1</v>
       </c>
       <c r="T57" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>400</v>
       </c>
@@ -5131,10 +5165,10 @@
         <v>1</v>
       </c>
       <c r="T58" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>401</v>
       </c>
@@ -5164,10 +5198,10 @@
         <v>1</v>
       </c>
       <c r="T59" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>402</v>
       </c>
@@ -5197,10 +5231,10 @@
         <v>1</v>
       </c>
       <c r="T60" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>403</v>
       </c>
@@ -5230,10 +5264,10 @@
         <v>1</v>
       </c>
       <c r="T61" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>404</v>
       </c>
@@ -5263,10 +5297,10 @@
         <v>1</v>
       </c>
       <c r="T62" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>405</v>
       </c>
@@ -5296,10 +5330,10 @@
         <v>1</v>
       </c>
       <c r="T63" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>406</v>
       </c>
@@ -5326,7 +5360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>407</v>
       </c>
@@ -5353,7 +5387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>408</v>
       </c>
@@ -5380,7 +5414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>409</v>
       </c>
@@ -5407,7 +5441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>416</v>
       </c>
@@ -5434,7 +5468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>422</v>
       </c>
@@ -5461,7 +5495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>424</v>
       </c>
@@ -5488,7 +5522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>429</v>
       </c>
@@ -5515,7 +5549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>437</v>
       </c>
@@ -5545,7 +5579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>569</v>
       </c>
@@ -5572,7 +5606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>570</v>
       </c>
@@ -5599,7 +5633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>572</v>
       </c>
@@ -5626,7 +5660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>573</v>
       </c>
@@ -5653,7 +5687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>574</v>
       </c>
@@ -5680,7 +5714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>575</v>
       </c>
@@ -5707,7 +5741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>576</v>
       </c>
@@ -5734,7 +5768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>577</v>
       </c>
@@ -5761,7 +5795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>578</v>
       </c>
@@ -5788,7 +5822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>579</v>
       </c>
@@ -5815,7 +5849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>493</v>
       </c>
@@ -5832,7 +5866,7 @@
         <v>1</v>
       </c>
       <c r="H83" t="s">
-        <v>888</v>
+        <v>863</v>
       </c>
       <c r="I83" t="s">
         <v>272</v>
@@ -5844,7 +5878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>494</v>
       </c>
@@ -5861,7 +5895,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>889</v>
+        <v>864</v>
       </c>
       <c r="I84" t="s">
         <v>272</v>
@@ -5873,7 +5907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>495</v>
       </c>
@@ -5890,7 +5924,7 @@
         <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>890</v>
+        <v>865</v>
       </c>
       <c r="I85" t="s">
         <v>272</v>
@@ -5902,7 +5936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>372</v>
       </c>
@@ -5932,10 +5966,10 @@
         <v>1</v>
       </c>
       <c r="T86" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>373</v>
       </c>
@@ -5965,10 +5999,10 @@
         <v>1</v>
       </c>
       <c r="T87" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>374</v>
       </c>
@@ -5998,10 +6032,10 @@
         <v>1</v>
       </c>
       <c r="T88" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>375</v>
       </c>
@@ -6031,10 +6065,10 @@
         <v>1</v>
       </c>
       <c r="T89" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>376</v>
       </c>
@@ -6064,10 +6098,10 @@
         <v>1</v>
       </c>
       <c r="T90" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>377</v>
       </c>
@@ -6097,10 +6131,10 @@
         <v>1</v>
       </c>
       <c r="T91" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>378</v>
       </c>
@@ -6130,10 +6164,10 @@
         <v>1</v>
       </c>
       <c r="T92" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>379</v>
       </c>
@@ -6160,7 +6194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>380</v>
       </c>
@@ -6187,7 +6221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>381</v>
       </c>
@@ -6214,7 +6248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>382</v>
       </c>
@@ -6241,7 +6275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>411</v>
       </c>
@@ -6268,7 +6302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>420</v>
       </c>
@@ -6295,7 +6329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>426</v>
       </c>
@@ -6322,7 +6356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>430</v>
       </c>
@@ -6349,7 +6383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>440</v>
       </c>
@@ -6376,7 +6410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>590</v>
       </c>
@@ -6403,7 +6437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>591</v>
       </c>
@@ -6430,7 +6464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>592</v>
       </c>
@@ -6457,7 +6491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>593</v>
       </c>
@@ -6484,7 +6518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>594</v>
       </c>
@@ -6511,7 +6545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>595</v>
       </c>
@@ -6538,7 +6572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>596</v>
       </c>
@@ -6565,7 +6599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>597</v>
       </c>
@@ -6592,7 +6626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>598</v>
       </c>
@@ -6619,7 +6653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>599</v>
       </c>
@@ -6646,7 +6680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>149</v>
       </c>
@@ -6676,10 +6710,10 @@
         <v>1</v>
       </c>
       <c r="T112" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>501</v>
       </c>
@@ -6709,10 +6743,10 @@
         <v>1</v>
       </c>
       <c r="T113" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>502</v>
       </c>
@@ -6742,10 +6776,10 @@
         <v>1</v>
       </c>
       <c r="T114" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>503</v>
       </c>
@@ -6775,13 +6809,13 @@
         <v>1</v>
       </c>
       <c r="L115" t="s">
-        <v>770</v>
+        <v>745</v>
       </c>
       <c r="T115" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>504</v>
       </c>
@@ -6811,10 +6845,10 @@
         <v>1</v>
       </c>
       <c r="T116" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>505</v>
       </c>
@@ -6844,10 +6878,10 @@
         <v>1</v>
       </c>
       <c r="T117" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>506</v>
       </c>
@@ -6877,10 +6911,10 @@
         <v>1</v>
       </c>
       <c r="T118" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>507</v>
       </c>
@@ -6907,13 +6941,13 @@
         <v>1</v>
       </c>
       <c r="L119" t="s">
-        <v>770</v>
+        <v>745</v>
       </c>
       <c r="M119" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>508</v>
       </c>
@@ -6940,13 +6974,13 @@
         <v>1</v>
       </c>
       <c r="L120" t="s">
-        <v>770</v>
+        <v>745</v>
       </c>
       <c r="M120" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>509</v>
       </c>
@@ -6973,10 +7007,10 @@
         <v>1</v>
       </c>
       <c r="L121" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>510</v>
       </c>
@@ -7003,10 +7037,10 @@
         <v>1</v>
       </c>
       <c r="L122" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>511</v>
       </c>
@@ -7033,13 +7067,13 @@
         <v>1</v>
       </c>
       <c r="L123" t="s">
-        <v>773</v>
+        <v>748</v>
       </c>
       <c r="M123" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>512</v>
       </c>
@@ -7069,10 +7103,10 @@
         <v>673</v>
       </c>
       <c r="M124" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>513</v>
       </c>
@@ -7102,10 +7136,10 @@
         <v>672</v>
       </c>
       <c r="M125" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>428</v>
       </c>
@@ -7132,7 +7166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>432</v>
       </c>
@@ -7162,7 +7196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>433</v>
       </c>
@@ -7192,7 +7226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>434</v>
       </c>
@@ -7222,7 +7256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>608</v>
       </c>
@@ -7249,7 +7283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>609</v>
       </c>
@@ -7276,7 +7310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>610</v>
       </c>
@@ -7303,7 +7337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>611</v>
       </c>
@@ -7330,7 +7364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>612</v>
       </c>
@@ -7357,7 +7391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>613</v>
       </c>
@@ -7384,7 +7418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>614</v>
       </c>
@@ -7411,7 +7445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>615</v>
       </c>
@@ -7438,12 +7472,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>824</v>
+        <v>799</v>
       </c>
       <c r="B138" t="s">
-        <v>825</v>
+        <v>800</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -7455,7 +7489,7 @@
         <v>2</v>
       </c>
       <c r="H138" t="s">
-        <v>886</v>
+        <v>861</v>
       </c>
       <c r="I138" t="s">
         <v>265</v>
@@ -7467,10 +7501,10 @@
         <v>1</v>
       </c>
       <c r="T138" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.35">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>471</v>
       </c>
@@ -7497,10 +7531,10 @@
         <v>1</v>
       </c>
       <c r="L139" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>472</v>
       </c>
@@ -7527,10 +7561,10 @@
         <v>1</v>
       </c>
       <c r="L140" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>473</v>
       </c>
@@ -7557,10 +7591,10 @@
         <v>1</v>
       </c>
       <c r="L141" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>474</v>
       </c>
@@ -7587,10 +7621,10 @@
         <v>1</v>
       </c>
       <c r="L142" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>475</v>
       </c>
@@ -7617,10 +7651,10 @@
         <v>1</v>
       </c>
       <c r="L143" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>476</v>
       </c>
@@ -7647,13 +7681,13 @@
         <v>1</v>
       </c>
       <c r="L144" t="s">
-        <v>789</v>
+        <v>764</v>
       </c>
       <c r="M144" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>477</v>
       </c>
@@ -7680,10 +7714,10 @@
         <v>1</v>
       </c>
       <c r="L145" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>478</v>
       </c>
@@ -7710,10 +7744,10 @@
         <v>1</v>
       </c>
       <c r="L146" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>479</v>
       </c>
@@ -7740,10 +7774,10 @@
         <v>1</v>
       </c>
       <c r="L147" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>480</v>
       </c>
@@ -7770,10 +7804,10 @@
         <v>1</v>
       </c>
       <c r="L148" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>481</v>
       </c>
@@ -7800,10 +7834,10 @@
         <v>1</v>
       </c>
       <c r="L149" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>482</v>
       </c>
@@ -7830,10 +7864,10 @@
         <v>1</v>
       </c>
       <c r="L150" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>483</v>
       </c>
@@ -7860,10 +7894,10 @@
         <v>1</v>
       </c>
       <c r="L151" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>484</v>
       </c>
@@ -7890,10 +7924,10 @@
         <v>1</v>
       </c>
       <c r="L152" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>485</v>
       </c>
@@ -7920,10 +7954,10 @@
         <v>1</v>
       </c>
       <c r="L153" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>486</v>
       </c>
@@ -7950,10 +7984,10 @@
         <v>1</v>
       </c>
       <c r="L154" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>487</v>
       </c>
@@ -7980,10 +8014,10 @@
         <v>1</v>
       </c>
       <c r="L155" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>488</v>
       </c>
@@ -8010,10 +8044,10 @@
         <v>1</v>
       </c>
       <c r="L156" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>489</v>
       </c>
@@ -8040,10 +8074,10 @@
         <v>1</v>
       </c>
       <c r="L157" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>490</v>
       </c>
@@ -8070,10 +8104,10 @@
         <v>1</v>
       </c>
       <c r="L158" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>491</v>
       </c>
@@ -8100,10 +8134,10 @@
         <v>1</v>
       </c>
       <c r="L159" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>492</v>
       </c>
@@ -8130,10 +8164,10 @@
         <v>1</v>
       </c>
       <c r="L160" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="161" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>620</v>
       </c>
@@ -8160,7 +8194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>621</v>
       </c>
@@ -8187,7 +8221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>622</v>
       </c>
@@ -8214,7 +8248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>623</v>
       </c>
@@ -8241,7 +8275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>391</v>
       </c>
@@ -8271,10 +8305,10 @@
         <v>1</v>
       </c>
       <c r="T165" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>392</v>
       </c>
@@ -8304,10 +8338,10 @@
         <v>1</v>
       </c>
       <c r="T166" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>393</v>
       </c>
@@ -8337,10 +8371,10 @@
         <v>1</v>
       </c>
       <c r="T167" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>394</v>
       </c>
@@ -8370,10 +8404,10 @@
         <v>1</v>
       </c>
       <c r="T168" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>395</v>
       </c>
@@ -8403,10 +8437,10 @@
         <v>1</v>
       </c>
       <c r="T169" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>396</v>
       </c>
@@ -8436,10 +8470,10 @@
         <v>1</v>
       </c>
       <c r="T170" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="171" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>397</v>
       </c>
@@ -8469,10 +8503,10 @@
         <v>1</v>
       </c>
       <c r="T171" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>398</v>
       </c>
@@ -8499,7 +8533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>412</v>
       </c>
@@ -8526,7 +8560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>414</v>
       </c>
@@ -8553,7 +8587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>415</v>
       </c>
@@ -8580,7 +8614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>419</v>
       </c>
@@ -8607,7 +8641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>423</v>
       </c>
@@ -8634,7 +8668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>425</v>
       </c>
@@ -8661,7 +8695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>431</v>
       </c>
@@ -8688,7 +8722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>441</v>
       </c>
@@ -8715,7 +8749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>634</v>
       </c>
@@ -8742,7 +8776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>635</v>
       </c>
@@ -8769,7 +8803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>636</v>
       </c>
@@ -8796,7 +8830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>637</v>
       </c>
@@ -8823,7 +8857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>638</v>
       </c>
@@ -8850,7 +8884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>639</v>
       </c>
@@ -8877,7 +8911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>640</v>
       </c>
@@ -8904,7 +8938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>641</v>
       </c>
@@ -8931,7 +8965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>642</v>
       </c>
@@ -8958,7 +8992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>643</v>
       </c>
@@ -8985,7 +9019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>514</v>
       </c>
@@ -9015,10 +9049,10 @@
         <v>1</v>
       </c>
       <c r="T191" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="192" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>515</v>
       </c>
@@ -9048,10 +9082,10 @@
         <v>1</v>
       </c>
       <c r="T192" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="193" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>516</v>
       </c>
@@ -9081,10 +9115,10 @@
         <v>1</v>
       </c>
       <c r="T193" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="194" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>517</v>
       </c>
@@ -9114,10 +9148,10 @@
         <v>1</v>
       </c>
       <c r="T194" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="195" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>518</v>
       </c>
@@ -9147,10 +9181,10 @@
         <v>1</v>
       </c>
       <c r="T195" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="196" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>519</v>
       </c>
@@ -9180,10 +9214,10 @@
         <v>1</v>
       </c>
       <c r="T196" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="197" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>520</v>
       </c>
@@ -9213,10 +9247,10 @@
         <v>1</v>
       </c>
       <c r="T197" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="198" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>521</v>
       </c>
@@ -9243,7 +9277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>522</v>
       </c>
@@ -9270,7 +9304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>523</v>
       </c>
@@ -9297,7 +9331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>524</v>
       </c>
@@ -9324,7 +9358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>525</v>
       </c>
@@ -9351,7 +9385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>526</v>
       </c>
@@ -9378,7 +9412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>527</v>
       </c>
@@ -9405,7 +9439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>427</v>
       </c>
@@ -9432,7 +9466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>439</v>
       </c>
@@ -9459,7 +9493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>656</v>
       </c>
@@ -9486,7 +9520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>657</v>
       </c>
@@ -9513,7 +9547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>658</v>
       </c>
@@ -9540,7 +9574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>659</v>
       </c>
@@ -9567,7 +9601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>660</v>
       </c>
@@ -9594,7 +9628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>661</v>
       </c>
@@ -9621,7 +9655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>662</v>
       </c>
@@ -9648,7 +9682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>663</v>
       </c>
@@ -9675,7 +9709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>664</v>
       </c>
@@ -9702,7 +9736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>665</v>
       </c>
@@ -9729,12 +9763,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>826</v>
+        <v>801</v>
       </c>
       <c r="B217" t="s">
-        <v>827</v>
+        <v>802</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -9746,7 +9780,7 @@
         <v>2</v>
       </c>
       <c r="H217" t="s">
-        <v>887</v>
+        <v>862</v>
       </c>
       <c r="I217" t="s">
         <v>215</v>
@@ -9758,10 +9792,10 @@
         <v>1</v>
       </c>
       <c r="T217" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.35">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="218" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>446</v>
       </c>
@@ -9788,7 +9822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>447</v>
       </c>
@@ -9815,7 +9849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>448</v>
       </c>
@@ -9842,7 +9876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>449</v>
       </c>
@@ -9869,7 +9903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>450</v>
       </c>
@@ -9896,7 +9930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>451</v>
       </c>
@@ -9923,7 +9957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>452</v>
       </c>
@@ -9950,7 +9984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>453</v>
       </c>
@@ -9977,7 +10011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>454</v>
       </c>
@@ -10004,7 +10038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>455</v>
       </c>
@@ -10031,7 +10065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>456</v>
       </c>
@@ -10058,7 +10092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>457</v>
       </c>
@@ -10085,7 +10119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>458</v>
       </c>
@@ -10112,7 +10146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>459</v>
       </c>
@@ -10139,7 +10173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>460</v>
       </c>
@@ -10166,7 +10200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>461</v>
       </c>
@@ -10193,7 +10227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>462</v>
       </c>
@@ -10220,7 +10254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>463</v>
       </c>
@@ -10247,7 +10281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>464</v>
       </c>
@@ -10274,7 +10308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>465</v>
       </c>
@@ -10301,7 +10335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>466</v>
       </c>
@@ -10328,7 +10362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>467</v>
       </c>
@@ -10355,7 +10389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>468</v>
       </c>
@@ -10382,7 +10416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>469</v>
       </c>
@@ -10409,7 +10443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>470</v>
       </c>
@@ -10436,7 +10470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>645</v>
       </c>
@@ -10463,7 +10497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>6</v>
       </c>
@@ -10483,7 +10517,7 @@
         <v>63</v>
       </c>
       <c r="H244" t="s">
-        <v>919</v>
+        <v>894</v>
       </c>
       <c r="I244" t="s">
         <v>42</v>
@@ -10495,13 +10529,13 @@
         <v>1</v>
       </c>
       <c r="L244" t="s">
-        <v>797</v>
+        <v>772</v>
       </c>
       <c r="T244" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="245" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>7</v>
       </c>
@@ -10521,7 +10555,7 @@
         <v>65</v>
       </c>
       <c r="H245" t="s">
-        <v>920</v>
+        <v>895</v>
       </c>
       <c r="I245" t="s">
         <v>42</v>
@@ -10533,13 +10567,13 @@
         <v>1</v>
       </c>
       <c r="L245" t="s">
-        <v>804</v>
+        <v>779</v>
       </c>
       <c r="T245" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="246" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>8</v>
       </c>
@@ -10559,7 +10593,7 @@
         <v>67</v>
       </c>
       <c r="H246" t="s">
-        <v>921</v>
+        <v>896</v>
       </c>
       <c r="I246" t="s">
         <v>42</v>
@@ -10571,16 +10605,16 @@
         <v>1</v>
       </c>
       <c r="L246" t="s">
-        <v>798</v>
+        <v>773</v>
       </c>
       <c r="M246" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
       <c r="T246" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.35">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="247" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>9</v>
       </c>
@@ -10600,7 +10634,7 @@
         <v>69</v>
       </c>
       <c r="H247" t="s">
-        <v>922</v>
+        <v>897</v>
       </c>
       <c r="I247" t="s">
         <v>42</v>
@@ -10612,13 +10646,13 @@
         <v>1</v>
       </c>
       <c r="L247" t="s">
-        <v>799</v>
+        <v>774</v>
       </c>
       <c r="T247" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.35">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="248" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>10</v>
       </c>
@@ -10638,7 +10672,7 @@
         <v>71</v>
       </c>
       <c r="H248" t="s">
-        <v>923</v>
+        <v>898</v>
       </c>
       <c r="I248" t="s">
         <v>42</v>
@@ -10650,18 +10684,18 @@
         <v>1</v>
       </c>
       <c r="L248" t="s">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="T248" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.35">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="249" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>11</v>
       </c>
       <c r="B249" t="s">
-        <v>918</v>
+        <v>893</v>
       </c>
       <c r="C249">
         <v>10</v>
@@ -10676,7 +10710,7 @@
         <v>72</v>
       </c>
       <c r="H249" t="s">
-        <v>924</v>
+        <v>899</v>
       </c>
       <c r="I249" t="s">
         <v>42</v>
@@ -10688,13 +10722,13 @@
         <v>1</v>
       </c>
       <c r="L249" t="s">
-        <v>801</v>
+        <v>776</v>
       </c>
       <c r="T249" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.35">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="250" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>13</v>
       </c>
@@ -10714,7 +10748,7 @@
         <v>76</v>
       </c>
       <c r="H250" t="s">
-        <v>925</v>
+        <v>900</v>
       </c>
       <c r="I250" t="s">
         <v>42</v>
@@ -10726,13 +10760,13 @@
         <v>1</v>
       </c>
       <c r="L250" t="s">
-        <v>802</v>
+        <v>777</v>
       </c>
       <c r="T250" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.35">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="251" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>12</v>
       </c>
@@ -10761,10 +10795,10 @@
         <v>1</v>
       </c>
       <c r="L251" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.35">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="252" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>14</v>
       </c>
@@ -10793,10 +10827,10 @@
         <v>2</v>
       </c>
       <c r="L252" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.35">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="253" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>15</v>
       </c>
@@ -10816,7 +10850,7 @@
         <v>80</v>
       </c>
       <c r="H253" t="s">
-        <v>894</v>
+        <v>869</v>
       </c>
       <c r="I253" t="s">
         <v>42</v>
@@ -10828,10 +10862,10 @@
         <v>1</v>
       </c>
       <c r="L253" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.35">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="254" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>16</v>
       </c>
@@ -10851,7 +10885,7 @@
         <v>82</v>
       </c>
       <c r="H254" t="s">
-        <v>893</v>
+        <v>868</v>
       </c>
       <c r="I254" t="s">
         <v>42</v>
@@ -10863,10 +10897,10 @@
         <v>1</v>
       </c>
       <c r="L254" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.35">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="255" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>17</v>
       </c>
@@ -10886,7 +10920,7 @@
         <v>83</v>
       </c>
       <c r="H255" t="s">
-        <v>895</v>
+        <v>870</v>
       </c>
       <c r="I255" t="s">
         <v>42</v>
@@ -10898,10 +10932,10 @@
         <v>1</v>
       </c>
       <c r="L255" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.35">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="256" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>18</v>
       </c>
@@ -10921,7 +10955,7 @@
         <v>84</v>
       </c>
       <c r="H256" t="s">
-        <v>896</v>
+        <v>871</v>
       </c>
       <c r="I256" t="s">
         <v>42</v>
@@ -10936,7 +10970,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>19</v>
       </c>
@@ -10956,7 +10990,7 @@
         <v>85</v>
       </c>
       <c r="H257" t="s">
-        <v>897</v>
+        <v>872</v>
       </c>
       <c r="I257" t="s">
         <v>42</v>
@@ -10968,10 +11002,10 @@
         <v>2</v>
       </c>
       <c r="L257" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.35">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>20</v>
       </c>
@@ -10991,7 +11025,7 @@
         <v>86</v>
       </c>
       <c r="H258" t="s">
-        <v>898</v>
+        <v>873</v>
       </c>
       <c r="I258" t="s">
         <v>42</v>
@@ -11003,10 +11037,10 @@
         <v>1</v>
       </c>
       <c r="L258" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.35">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>21</v>
       </c>
@@ -11026,7 +11060,7 @@
         <v>87</v>
       </c>
       <c r="H259" t="s">
-        <v>899</v>
+        <v>874</v>
       </c>
       <c r="I259" t="s">
         <v>42</v>
@@ -11041,7 +11075,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>22</v>
       </c>
@@ -11061,7 +11095,7 @@
         <v>88</v>
       </c>
       <c r="H260" t="s">
-        <v>900</v>
+        <v>875</v>
       </c>
       <c r="I260" t="s">
         <v>42</v>
@@ -11076,7 +11110,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>23</v>
       </c>
@@ -11096,7 +11130,7 @@
         <v>90</v>
       </c>
       <c r="H261" t="s">
-        <v>901</v>
+        <v>876</v>
       </c>
       <c r="I261" t="s">
         <v>42</v>
@@ -11108,10 +11142,10 @@
         <v>1</v>
       </c>
       <c r="L261" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.35">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>24</v>
       </c>
@@ -11131,7 +11165,7 @@
         <v>92</v>
       </c>
       <c r="H262" t="s">
-        <v>902</v>
+        <v>877</v>
       </c>
       <c r="I262" t="s">
         <v>42</v>
@@ -11146,7 +11180,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>25</v>
       </c>
@@ -11178,13 +11212,13 @@
         <v>1</v>
       </c>
       <c r="L263" t="s">
-        <v>820</v>
+        <v>795</v>
       </c>
       <c r="M263" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>26</v>
       </c>
@@ -11216,10 +11250,10 @@
         <v>1</v>
       </c>
       <c r="L264" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>27</v>
       </c>
@@ -11251,10 +11285,10 @@
         <v>1</v>
       </c>
       <c r="L265" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>28</v>
       </c>
@@ -11286,13 +11320,13 @@
         <v>2</v>
       </c>
       <c r="L266" t="s">
-        <v>811</v>
+        <v>786</v>
       </c>
       <c r="M266" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.35">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>29</v>
       </c>
@@ -11324,10 +11358,10 @@
         <v>1</v>
       </c>
       <c r="L267" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.35">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>30</v>
       </c>
@@ -11359,13 +11393,13 @@
         <v>2</v>
       </c>
       <c r="L268" t="s">
-        <v>801</v>
+        <v>776</v>
       </c>
       <c r="M268" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.35">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>31</v>
       </c>
@@ -11397,13 +11431,13 @@
         <v>2</v>
       </c>
       <c r="L269" t="s">
-        <v>803</v>
+        <v>778</v>
       </c>
       <c r="M269" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>32</v>
       </c>
@@ -11441,7 +11475,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>33</v>
       </c>
@@ -11473,13 +11507,13 @@
         <v>1</v>
       </c>
       <c r="L271" t="s">
-        <v>809</v>
+        <v>784</v>
       </c>
       <c r="M271" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>34</v>
       </c>
@@ -11517,7 +11551,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>496</v>
       </c>
@@ -11544,7 +11578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>498</v>
       </c>
@@ -11571,7 +11605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>499</v>
       </c>
@@ -11598,7 +11632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>500</v>
       </c>
@@ -11625,7 +11659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>438</v>
       </c>
@@ -11655,7 +11689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>442</v>
       </c>
@@ -11685,7 +11719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>443</v>
       </c>
@@ -11715,7 +11749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>444</v>
       </c>
@@ -11745,7 +11779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>445</v>
       </c>
@@ -11772,7 +11806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>346</v>
       </c>
@@ -11802,10 +11836,10 @@
         <v>1</v>
       </c>
       <c r="T282" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="283" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>347</v>
       </c>
@@ -11835,10 +11869,10 @@
         <v>1</v>
       </c>
       <c r="T283" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="284" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>348</v>
       </c>
@@ -11868,10 +11902,10 @@
         <v>1</v>
       </c>
       <c r="T284" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="285" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>349</v>
       </c>
@@ -11901,10 +11935,10 @@
         <v>1</v>
       </c>
       <c r="T285" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="286" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>350</v>
       </c>
@@ -11934,10 +11968,10 @@
         <v>1</v>
       </c>
       <c r="T286" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="287" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>351</v>
       </c>
@@ -11967,10 +12001,10 @@
         <v>1</v>
       </c>
       <c r="T287" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="288" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>352</v>
       </c>
@@ -12000,10 +12034,10 @@
         <v>1</v>
       </c>
       <c r="T288" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>353</v>
       </c>
@@ -12030,7 +12064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>354</v>
       </c>
@@ -12057,7 +12091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>355</v>
       </c>
@@ -12084,7 +12118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>356</v>
       </c>
@@ -12111,7 +12145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>357</v>
       </c>
@@ -12138,7 +12172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>358</v>
       </c>
@@ -12165,7 +12199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>359</v>
       </c>
@@ -12192,7 +12226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>360</v>
       </c>
@@ -12219,7 +12253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>361</v>
       </c>
@@ -12246,7 +12280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>362</v>
       </c>
@@ -12273,7 +12307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>363</v>
       </c>
@@ -12300,7 +12334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>364</v>
       </c>
@@ -12327,7 +12361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>365</v>
       </c>
@@ -12354,7 +12388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>366</v>
       </c>
@@ -12381,7 +12415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>367</v>
       </c>
@@ -12408,7 +12442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>368</v>
       </c>
@@ -12435,7 +12469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>369</v>
       </c>
@@ -12462,7 +12496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>370</v>
       </c>
@@ -12489,7 +12523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>371</v>
       </c>
@@ -12516,12 +12550,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>730</v>
-      </c>
-      <c r="B308" t="s">
-        <v>710</v>
+        <v>705</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>909</v>
       </c>
       <c r="C308">
         <v>7</v>
@@ -12530,27 +12564,27 @@
         <v>0</v>
       </c>
       <c r="H308" t="s">
-        <v>853</v>
+        <v>828</v>
       </c>
       <c r="I308" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J308" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K308">
         <v>1</v>
       </c>
       <c r="L308" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>731</v>
-      </c>
-      <c r="B309" t="s">
-        <v>711</v>
+        <v>706</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>913</v>
       </c>
       <c r="C309">
         <v>7</v>
@@ -12559,27 +12593,27 @@
         <v>0</v>
       </c>
       <c r="H309" t="s">
-        <v>854</v>
+        <v>829</v>
       </c>
       <c r="I309" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J309" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K309">
         <v>1</v>
       </c>
       <c r="L309" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.35">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>732</v>
-      </c>
-      <c r="B310" t="s">
-        <v>712</v>
+        <v>707</v>
+      </c>
+      <c r="B310" s="3" t="s">
+        <v>918</v>
       </c>
       <c r="C310">
         <v>7</v>
@@ -12588,27 +12622,27 @@
         <v>0</v>
       </c>
       <c r="H310" t="s">
-        <v>855</v>
+        <v>830</v>
       </c>
       <c r="I310" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J310" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K310">
         <v>1</v>
       </c>
       <c r="L310" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.35">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>733</v>
-      </c>
-      <c r="B311" t="s">
-        <v>713</v>
+        <v>708</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>902</v>
       </c>
       <c r="C311">
         <v>7</v>
@@ -12617,27 +12651,27 @@
         <v>0</v>
       </c>
       <c r="H311" t="s">
-        <v>856</v>
+        <v>831</v>
       </c>
       <c r="I311" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J311" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K311">
         <v>1</v>
       </c>
       <c r="L311" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.35">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>734</v>
-      </c>
-      <c r="B312" t="s">
-        <v>714</v>
+        <v>709</v>
+      </c>
+      <c r="B312" s="3" t="s">
+        <v>903</v>
       </c>
       <c r="C312">
         <v>7</v>
@@ -12646,27 +12680,27 @@
         <v>0</v>
       </c>
       <c r="H312" t="s">
-        <v>857</v>
+        <v>832</v>
       </c>
       <c r="I312" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J312" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K312">
         <v>1</v>
       </c>
       <c r="L312" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.35">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>735</v>
-      </c>
-      <c r="B313" t="s">
-        <v>715</v>
+        <v>710</v>
+      </c>
+      <c r="B313" s="3" t="s">
+        <v>904</v>
       </c>
       <c r="C313">
         <v>14</v>
@@ -12675,27 +12709,27 @@
         <v>1</v>
       </c>
       <c r="H313" t="s">
-        <v>858</v>
+        <v>833</v>
       </c>
       <c r="I313" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J313" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K313">
         <v>1</v>
       </c>
       <c r="L313" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.35">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>736</v>
-      </c>
-      <c r="B314" t="s">
-        <v>716</v>
+        <v>711</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>914</v>
       </c>
       <c r="C314">
         <v>14</v>
@@ -12704,27 +12738,27 @@
         <v>1</v>
       </c>
       <c r="H314" t="s">
-        <v>859</v>
+        <v>834</v>
       </c>
       <c r="I314" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J314" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K314">
         <v>1</v>
       </c>
       <c r="L314" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.35">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>737</v>
-      </c>
-      <c r="B315" t="s">
-        <v>717</v>
+        <v>712</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>905</v>
       </c>
       <c r="C315">
         <v>14</v>
@@ -12733,27 +12767,27 @@
         <v>1</v>
       </c>
       <c r="H315" t="s">
-        <v>860</v>
+        <v>835</v>
       </c>
       <c r="I315" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J315" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K315">
         <v>1</v>
       </c>
       <c r="L315" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.35">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>738</v>
-      </c>
-      <c r="B316" t="s">
-        <v>718</v>
+        <v>713</v>
+      </c>
+      <c r="B316" s="3" t="s">
+        <v>906</v>
       </c>
       <c r="C316">
         <v>14</v>
@@ -12762,27 +12796,27 @@
         <v>1</v>
       </c>
       <c r="H316" t="s">
-        <v>861</v>
+        <v>836</v>
       </c>
       <c r="I316" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J316" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K316">
         <v>1</v>
       </c>
       <c r="L316" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.35">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>739</v>
-      </c>
-      <c r="B317" t="s">
-        <v>719</v>
+        <v>714</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>923</v>
       </c>
       <c r="C317">
         <v>14</v>
@@ -12791,27 +12825,27 @@
         <v>1</v>
       </c>
       <c r="H317" t="s">
-        <v>862</v>
+        <v>837</v>
       </c>
       <c r="I317" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J317" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K317">
         <v>1</v>
       </c>
       <c r="L317" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="318" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>740</v>
-      </c>
-      <c r="B318" t="s">
-        <v>705</v>
+        <v>715</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>910</v>
       </c>
       <c r="C318">
         <v>21</v>
@@ -12820,27 +12854,27 @@
         <v>2</v>
       </c>
       <c r="H318" t="s">
-        <v>863</v>
+        <v>838</v>
       </c>
       <c r="I318" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J318" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K318">
         <v>1</v>
       </c>
       <c r="L318" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.35">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>741</v>
-      </c>
-      <c r="B319" t="s">
-        <v>706</v>
+        <v>716</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>915</v>
       </c>
       <c r="C319">
         <v>21</v>
@@ -12849,27 +12883,27 @@
         <v>2</v>
       </c>
       <c r="H319" t="s">
-        <v>864</v>
+        <v>839</v>
       </c>
       <c r="I319" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J319" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K319">
         <v>1</v>
       </c>
       <c r="L319" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>742</v>
-      </c>
-      <c r="B320" t="s">
-        <v>707</v>
+        <v>717</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>919</v>
       </c>
       <c r="C320">
         <v>21</v>
@@ -12878,27 +12912,27 @@
         <v>2</v>
       </c>
       <c r="H320" t="s">
-        <v>865</v>
+        <v>840</v>
       </c>
       <c r="I320" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J320" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K320">
         <v>1</v>
       </c>
       <c r="L320" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="321" spans="1:23" x14ac:dyDescent="0.35">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="321" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>743</v>
-      </c>
-      <c r="B321" t="s">
-        <v>708</v>
+        <v>718</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>921</v>
       </c>
       <c r="C321">
         <v>21</v>
@@ -12907,27 +12941,27 @@
         <v>2</v>
       </c>
       <c r="H321" t="s">
-        <v>866</v>
+        <v>841</v>
       </c>
       <c r="I321" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J321" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K321">
         <v>1</v>
       </c>
       <c r="L321" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="322" spans="1:23" x14ac:dyDescent="0.35">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="322" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>744</v>
-      </c>
-      <c r="B322" t="s">
-        <v>709</v>
+        <v>719</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>924</v>
       </c>
       <c r="C322">
         <v>21</v>
@@ -12936,27 +12970,27 @@
         <v>2</v>
       </c>
       <c r="H322" t="s">
-        <v>867</v>
+        <v>842</v>
       </c>
       <c r="I322" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J322" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K322">
         <v>1</v>
       </c>
       <c r="L322" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="323" spans="1:23" x14ac:dyDescent="0.35">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="323" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>745</v>
-      </c>
-      <c r="B323" t="s">
         <v>720</v>
+      </c>
+      <c r="B323" s="3" t="s">
+        <v>911</v>
       </c>
       <c r="C323">
         <v>28</v>
@@ -12965,27 +12999,27 @@
         <v>3</v>
       </c>
       <c r="H323" t="s">
-        <v>868</v>
+        <v>843</v>
       </c>
       <c r="I323" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J323" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K323">
         <v>1</v>
       </c>
       <c r="L323" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="324" spans="1:23" x14ac:dyDescent="0.35">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="324" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>746</v>
-      </c>
-      <c r="B324" t="s">
         <v>721</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>916</v>
       </c>
       <c r="C324">
         <v>28</v>
@@ -12994,27 +13028,27 @@
         <v>3</v>
       </c>
       <c r="H324" t="s">
-        <v>869</v>
+        <v>844</v>
       </c>
       <c r="I324" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J324" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K324">
         <v>1</v>
       </c>
       <c r="L324" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="325" spans="1:23" x14ac:dyDescent="0.35">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="325" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>747</v>
-      </c>
-      <c r="B325" t="s">
         <v>722</v>
+      </c>
+      <c r="B325" s="3" t="s">
+        <v>907</v>
       </c>
       <c r="C325">
         <v>28</v>
@@ -13023,27 +13057,27 @@
         <v>3</v>
       </c>
       <c r="H325" t="s">
-        <v>870</v>
+        <v>845</v>
       </c>
       <c r="I325" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J325" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K325">
         <v>1</v>
       </c>
       <c r="L325" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="326" spans="1:23" x14ac:dyDescent="0.35">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="326" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>748</v>
-      </c>
-      <c r="B326" t="s">
         <v>723</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>922</v>
       </c>
       <c r="C326">
         <v>28</v>
@@ -13052,27 +13086,27 @@
         <v>3</v>
       </c>
       <c r="H326" t="s">
-        <v>871</v>
+        <v>846</v>
       </c>
       <c r="I326" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J326" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K326">
         <v>1</v>
       </c>
       <c r="L326" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="327" spans="1:23" x14ac:dyDescent="0.35">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="327" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>749</v>
-      </c>
-      <c r="B327" t="s">
         <v>724</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>925</v>
       </c>
       <c r="C327">
         <v>28</v>
@@ -13081,27 +13115,27 @@
         <v>3</v>
       </c>
       <c r="H327" t="s">
-        <v>872</v>
+        <v>847</v>
       </c>
       <c r="I327" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J327" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K327">
         <v>1</v>
       </c>
       <c r="L327" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="328" spans="1:23" x14ac:dyDescent="0.35">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="328" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>750</v>
-      </c>
-      <c r="B328" t="s">
         <v>725</v>
+      </c>
+      <c r="B328" s="3" t="s">
+        <v>912</v>
       </c>
       <c r="C328">
         <v>35</v>
@@ -13110,27 +13144,27 @@
         <v>4</v>
       </c>
       <c r="H328" t="s">
-        <v>873</v>
+        <v>848</v>
       </c>
       <c r="I328" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J328" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K328">
         <v>1</v>
       </c>
       <c r="L328" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="329" spans="1:23" x14ac:dyDescent="0.35">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="329" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>751</v>
-      </c>
-      <c r="B329" t="s">
         <v>726</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>917</v>
       </c>
       <c r="C329">
         <v>35</v>
@@ -13139,27 +13173,27 @@
         <v>4</v>
       </c>
       <c r="H329" t="s">
-        <v>874</v>
+        <v>849</v>
       </c>
       <c r="I329" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J329" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K329">
         <v>1</v>
       </c>
       <c r="L329" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="330" spans="1:23" x14ac:dyDescent="0.35">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="330" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>752</v>
-      </c>
-      <c r="B330" t="s">
         <v>727</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>920</v>
       </c>
       <c r="C330">
         <v>35</v>
@@ -13168,27 +13202,27 @@
         <v>4</v>
       </c>
       <c r="H330" t="s">
-        <v>875</v>
+        <v>850</v>
       </c>
       <c r="I330" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J330" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K330">
         <v>1</v>
       </c>
       <c r="L330" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="331" spans="1:23" x14ac:dyDescent="0.35">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="331" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>753</v>
-      </c>
-      <c r="B331" t="s">
         <v>728</v>
+      </c>
+      <c r="B331" s="3" t="s">
+        <v>908</v>
       </c>
       <c r="C331">
         <v>35</v>
@@ -13197,27 +13231,27 @@
         <v>4</v>
       </c>
       <c r="H331" t="s">
-        <v>876</v>
+        <v>851</v>
       </c>
       <c r="I331" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J331" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K331">
         <v>1</v>
       </c>
       <c r="L331" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="332" spans="1:23" x14ac:dyDescent="0.35">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="332" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>754</v>
-      </c>
-      <c r="B332" t="s">
         <v>729</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>926</v>
       </c>
       <c r="C332">
         <v>35</v>
@@ -13226,27 +13260,27 @@
         <v>4</v>
       </c>
       <c r="H332" t="s">
-        <v>877</v>
+        <v>852</v>
       </c>
       <c r="I332" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="J332" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="K332">
         <v>1</v>
       </c>
       <c r="L332" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="333" spans="1:23" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="333" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>758</v>
+        <v>733</v>
       </c>
       <c r="B333" t="s">
-        <v>757</v>
+        <v>732</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -13259,39 +13293,39 @@
         <v>无</v>
       </c>
       <c r="I333" t="s">
-        <v>759</v>
+        <v>734</v>
       </c>
       <c r="J333" t="s">
-        <v>760</v>
+        <v>735</v>
       </c>
       <c r="K333">
         <v>1</v>
       </c>
       <c r="L333" t="s">
-        <v>908</v>
+        <v>883</v>
       </c>
       <c r="M333" t="s">
-        <v>907</v>
+        <v>882</v>
       </c>
       <c r="O333">
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>926</v>
+        <v>901</v>
       </c>
       <c r="Q333" t="s">
         <v>42</v>
       </c>
       <c r="R333" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="334" spans="1:23" x14ac:dyDescent="0.35">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="334" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>764</v>
+        <v>739</v>
       </c>
       <c r="B334" t="s">
-        <v>765</v>
+        <v>740</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -13304,10 +13338,10 @@
         <v>沃</v>
       </c>
       <c r="I334" t="s">
-        <v>766</v>
+        <v>741</v>
       </c>
       <c r="J334" t="s">
-        <v>760</v>
+        <v>735</v>
       </c>
       <c r="S334">
         <v>2</v>
@@ -13320,7 +13354,7 @@
         <v>22.727272727272727</v>
       </c>
     </row>
-    <row r="335" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:23" x14ac:dyDescent="0.2">
       <c r="V335">
         <v>23</v>
       </c>
@@ -13329,7 +13363,7 @@
         <v>17.424242424242426</v>
       </c>
     </row>
-    <row r="336" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:23" x14ac:dyDescent="0.2">
       <c r="V336">
         <v>30</v>
       </c>
@@ -13338,7 +13372,7 @@
         <v>22.727272727272727</v>
       </c>
     </row>
-    <row r="337" spans="22:23" x14ac:dyDescent="0.35">
+    <row r="337" spans="22:23" x14ac:dyDescent="0.2">
       <c r="V337">
         <v>24</v>
       </c>

--- a/configs/Item.xlsx
+++ b/configs/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2DF5CA-7478-47BE-A886-76E47837FD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA0B89A-1342-4B84-BBC7-FC02417E8FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="991">
   <si>
     <t>id</t>
   </si>
@@ -3023,16 +3023,10 @@
     <t>沃玛战甲</t>
   </si>
   <si>
-    <t>setvoma,0</t>
-  </si>
-  <si>
     <t>vomaaxe</t>
   </si>
   <si>
     <t>沃玛战斧</t>
-  </si>
-  <si>
-    <t>setvoma,0:xdmg1,0</t>
   </si>
   <si>
     <t>INV_CHEST_LEATHER_15</t>
@@ -3115,37 +3109,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3516,27 +3480,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:T355"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.90625" customWidth="1"/>
-    <col min="8" max="8" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.1796875" customWidth="1"/>
-    <col min="15" max="15" width="25.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.08984375" customWidth="1"/>
-    <col min="17" max="17" width="21.453125" customWidth="1"/>
-    <col min="18" max="18" width="22.26953125" customWidth="1"/>
+    <col min="1" max="1" width="11.08984375" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" customWidth="1"/>
+    <col min="3" max="3" width="4.90625" customWidth="1"/>
+    <col min="4" max="4" width="6.54296875" customWidth="1"/>
+    <col min="5" max="5" width="6.453125" customWidth="1"/>
+    <col min="6" max="6" width="7.1796875" customWidth="1"/>
+    <col min="7" max="7" width="11.26953125" customWidth="1"/>
+    <col min="8" max="8" width="9.81640625" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="11" max="11" width="15.1796875" customWidth="1"/>
+    <col min="12" max="12" width="8.453125" customWidth="1"/>
+    <col min="13" max="13" width="9.453125" customWidth="1"/>
+    <col min="14" max="14" width="7" customWidth="1"/>
+    <col min="15" max="15" width="9.54296875" customWidth="1"/>
+    <col min="16" max="16" width="11.1796875" customWidth="1"/>
+    <col min="17" max="17" width="9.81640625" customWidth="1"/>
+    <col min="18" max="18" width="11.26953125" customWidth="1"/>
+    <col min="19" max="19" width="8.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.35">
@@ -3580,7 +3546,7 @@
         <v>856</v>
       </c>
       <c r="N1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="O1" t="s">
         <v>677</v>
@@ -3670,9 +3636,6 @@
       <c r="I3" t="s">
         <v>858</v>
       </c>
-      <c r="R3" t="s">
-        <v>858</v>
-      </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -3736,7 +3699,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>48</v>
       </c>
@@ -3771,7 +3734,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -3800,7 +3763,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>109</v>
       </c>
@@ -3832,7 +3795,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>110</v>
       </c>
@@ -3861,7 +3824,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>111</v>
       </c>
@@ -3893,7 +3856,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -3922,7 +3885,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>113</v>
       </c>
@@ -3951,7 +3914,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>157</v>
       </c>
@@ -3980,7 +3943,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>119</v>
       </c>
@@ -4010,7 +3973,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>120</v>
       </c>
@@ -4040,7 +4003,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>121</v>
       </c>
@@ -4070,7 +4033,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>122</v>
       </c>
@@ -4100,7 +4063,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>127</v>
       </c>
@@ -4130,7 +4093,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>128</v>
       </c>
@@ -4160,7 +4123,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>129</v>
       </c>
@@ -4190,7 +4153,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>130</v>
       </c>
@@ -4220,7 +4183,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>139</v>
       </c>
@@ -4250,7 +4213,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>140</v>
       </c>
@@ -4280,7 +4243,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>141</v>
       </c>
@@ -4310,7 +4273,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>142</v>
       </c>
@@ -4354,22 +4317,23 @@
         <v>2</v>
       </c>
       <c r="H25" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="I25" t="s">
         <v>40</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>985</v>
-      </c>
+      <c r="J25" s="3"/>
       <c r="M25">
         <v>3</v>
       </c>
       <c r="N25">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="R25" s="3" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>337</v>
       </c>
@@ -4390,7 +4354,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>525</v>
       </c>
@@ -4411,7 +4375,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>526</v>
       </c>
@@ -4432,7 +4396,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>527</v>
       </c>
@@ -4453,7 +4417,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>528</v>
       </c>
@@ -4474,7 +4438,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>529</v>
       </c>
@@ -4495,7 +4459,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>375</v>
       </c>
@@ -4522,7 +4486,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>376</v>
       </c>
@@ -4549,7 +4513,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>377</v>
       </c>
@@ -4576,7 +4540,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>378</v>
       </c>
@@ -4603,7 +4567,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>379</v>
       </c>
@@ -4630,7 +4594,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>380</v>
       </c>
@@ -4657,7 +4621,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>381</v>
       </c>
@@ -4684,7 +4648,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>382</v>
       </c>
@@ -4705,7 +4669,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>402</v>
       </c>
@@ -4726,7 +4690,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>405</v>
       </c>
@@ -4747,7 +4711,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>409</v>
       </c>
@@ -4768,7 +4732,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>410</v>
       </c>
@@ -4789,7 +4753,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>413</v>
       </c>
@@ -4813,7 +4777,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>427</v>
       </c>
@@ -4834,7 +4798,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>428</v>
       </c>
@@ -4855,7 +4819,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>541</v>
       </c>
@@ -4876,7 +4840,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>542</v>
       </c>
@@ -4897,7 +4861,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>543</v>
       </c>
@@ -4918,7 +4882,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>544</v>
       </c>
@@ -4939,7 +4903,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>545</v>
       </c>
@@ -4960,7 +4924,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>546</v>
       </c>
@@ -4981,7 +4945,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>547</v>
       </c>
@@ -5002,7 +4966,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>548</v>
       </c>
@@ -5023,7 +4987,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>549</v>
       </c>
@@ -5044,7 +5008,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>550</v>
       </c>
@@ -5065,7 +5029,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>551</v>
       </c>
@@ -5086,7 +5050,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>391</v>
       </c>
@@ -5113,7 +5077,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>392</v>
       </c>
@@ -5140,7 +5104,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>393</v>
       </c>
@@ -5167,7 +5131,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>394</v>
       </c>
@@ -5194,7 +5158,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>395</v>
       </c>
@@ -5221,7 +5185,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>396</v>
       </c>
@@ -5248,7 +5212,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>397</v>
       </c>
@@ -5275,7 +5239,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>398</v>
       </c>
@@ -5296,7 +5260,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>399</v>
       </c>
@@ -5317,7 +5281,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>400</v>
       </c>
@@ -5338,7 +5302,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>401</v>
       </c>
@@ -5359,7 +5323,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>408</v>
       </c>
@@ -5380,7 +5344,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>414</v>
       </c>
@@ -5401,7 +5365,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>416</v>
       </c>
@@ -5422,7 +5386,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>421</v>
       </c>
@@ -5443,7 +5407,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>429</v>
       </c>
@@ -5467,7 +5431,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>561</v>
       </c>
@@ -5488,7 +5452,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>562</v>
       </c>
@@ -5509,7 +5473,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>564</v>
       </c>
@@ -5530,7 +5494,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>565</v>
       </c>
@@ -5551,7 +5515,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>566</v>
       </c>
@@ -5572,7 +5536,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>567</v>
       </c>
@@ -5593,7 +5557,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>568</v>
       </c>
@@ -5614,7 +5578,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>569</v>
       </c>
@@ -5635,7 +5599,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>570</v>
       </c>
@@ -5656,7 +5620,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>571</v>
       </c>
@@ -5677,7 +5641,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>485</v>
       </c>
@@ -5700,7 +5664,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>486</v>
       </c>
@@ -5723,7 +5687,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>487</v>
       </c>
@@ -5746,7 +5710,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>364</v>
       </c>
@@ -5773,7 +5737,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>365</v>
       </c>
@@ -5800,7 +5764,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>366</v>
       </c>
@@ -5827,7 +5791,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>367</v>
       </c>
@@ -5854,7 +5818,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>368</v>
       </c>
@@ -5881,7 +5845,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>369</v>
       </c>
@@ -5908,7 +5872,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>370</v>
       </c>
@@ -5935,7 +5899,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>371</v>
       </c>
@@ -5956,7 +5920,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>372</v>
       </c>
@@ -5977,7 +5941,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>373</v>
       </c>
@@ -5998,7 +5962,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>374</v>
       </c>
@@ -6019,7 +5983,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>403</v>
       </c>
@@ -6040,7 +6004,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>412</v>
       </c>
@@ -6061,7 +6025,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>418</v>
       </c>
@@ -6082,7 +6046,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>422</v>
       </c>
@@ -6103,7 +6067,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>432</v>
       </c>
@@ -6124,7 +6088,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>582</v>
       </c>
@@ -6145,7 +6109,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>583</v>
       </c>
@@ -6166,7 +6130,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>584</v>
       </c>
@@ -6187,7 +6151,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>585</v>
       </c>
@@ -6208,7 +6172,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>586</v>
       </c>
@@ -6229,7 +6193,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>587</v>
       </c>
@@ -6250,7 +6214,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>588</v>
       </c>
@@ -6271,7 +6235,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>589</v>
       </c>
@@ -6292,7 +6256,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>590</v>
       </c>
@@ -6313,7 +6277,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>591</v>
       </c>
@@ -6334,7 +6298,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>143</v>
       </c>
@@ -6361,7 +6325,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>493</v>
       </c>
@@ -6388,7 +6352,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>494</v>
       </c>
@@ -6415,7 +6379,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>495</v>
       </c>
@@ -6445,7 +6409,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>496</v>
       </c>
@@ -6472,7 +6436,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>497</v>
       </c>
@@ -6499,7 +6463,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>498</v>
       </c>
@@ -6526,7 +6490,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>499</v>
       </c>
@@ -6553,7 +6517,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>500</v>
       </c>
@@ -6580,7 +6544,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>501</v>
       </c>
@@ -6604,7 +6568,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>502</v>
       </c>
@@ -6628,7 +6592,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>503</v>
       </c>
@@ -6655,7 +6619,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>504</v>
       </c>
@@ -6682,7 +6646,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>505</v>
       </c>
@@ -6709,7 +6673,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>420</v>
       </c>
@@ -6730,7 +6694,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>424</v>
       </c>
@@ -6754,7 +6718,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>425</v>
       </c>
@@ -6778,7 +6742,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>426</v>
       </c>
@@ -6802,7 +6766,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>600</v>
       </c>
@@ -6823,7 +6787,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>601</v>
       </c>
@@ -6844,7 +6808,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>602</v>
       </c>
@@ -6865,7 +6829,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>603</v>
       </c>
@@ -6886,7 +6850,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>604</v>
       </c>
@@ -6907,7 +6871,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>605</v>
       </c>
@@ -6928,7 +6892,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>606</v>
       </c>
@@ -6949,7 +6913,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>607</v>
       </c>
@@ -6970,7 +6934,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>773</v>
       </c>
@@ -6996,7 +6960,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>463</v>
       </c>
@@ -7020,7 +6984,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>464</v>
       </c>
@@ -7044,7 +7008,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>465</v>
       </c>
@@ -7068,7 +7032,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>466</v>
       </c>
@@ -7092,7 +7056,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>467</v>
       </c>
@@ -7116,7 +7080,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>468</v>
       </c>
@@ -7143,7 +7107,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>469</v>
       </c>
@@ -7167,7 +7131,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>470</v>
       </c>
@@ -7191,7 +7155,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>471</v>
       </c>
@@ -7215,7 +7179,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>472</v>
       </c>
@@ -7239,7 +7203,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>473</v>
       </c>
@@ -7263,7 +7227,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>474</v>
       </c>
@@ -7287,7 +7251,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>475</v>
       </c>
@@ -7311,7 +7275,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>476</v>
       </c>
@@ -7335,7 +7299,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>477</v>
       </c>
@@ -7359,7 +7323,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>478</v>
       </c>
@@ -7383,7 +7347,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>479</v>
       </c>
@@ -7407,7 +7371,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>480</v>
       </c>
@@ -7431,7 +7395,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>481</v>
       </c>
@@ -7455,7 +7419,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>482</v>
       </c>
@@ -7479,7 +7443,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>483</v>
       </c>
@@ -7503,7 +7467,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>484</v>
       </c>
@@ -7527,7 +7491,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>612</v>
       </c>
@@ -7548,7 +7512,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>613</v>
       </c>
@@ -7569,7 +7533,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>614</v>
       </c>
@@ -7590,7 +7554,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>615</v>
       </c>
@@ -7611,7 +7575,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>383</v>
       </c>
@@ -7638,7 +7602,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>384</v>
       </c>
@@ -7665,7 +7629,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>385</v>
       </c>
@@ -7692,7 +7656,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>386</v>
       </c>
@@ -7719,7 +7683,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>387</v>
       </c>
@@ -7746,7 +7710,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>388</v>
       </c>
@@ -7773,7 +7737,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>389</v>
       </c>
@@ -7800,7 +7764,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>390</v>
       </c>
@@ -7821,7 +7785,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>404</v>
       </c>
@@ -7842,7 +7806,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>406</v>
       </c>
@@ -7863,7 +7827,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>407</v>
       </c>
@@ -7884,7 +7848,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>411</v>
       </c>
@@ -7905,7 +7869,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>415</v>
       </c>
@@ -7926,7 +7890,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>417</v>
       </c>
@@ -7947,7 +7911,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>423</v>
       </c>
@@ -7968,7 +7932,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>433</v>
       </c>
@@ -7989,7 +7953,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>626</v>
       </c>
@@ -8010,7 +7974,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>627</v>
       </c>
@@ -8031,7 +7995,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>628</v>
       </c>
@@ -8052,7 +8016,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>629</v>
       </c>
@@ -8073,7 +8037,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>630</v>
       </c>
@@ -8094,7 +8058,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>631</v>
       </c>
@@ -8115,7 +8079,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>632</v>
       </c>
@@ -8136,7 +8100,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>633</v>
       </c>
@@ -8157,7 +8121,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>634</v>
       </c>
@@ -8178,7 +8142,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>635</v>
       </c>
@@ -8199,7 +8163,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>506</v>
       </c>
@@ -8226,7 +8190,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>507</v>
       </c>
@@ -8253,7 +8217,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>508</v>
       </c>
@@ -8280,7 +8244,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>509</v>
       </c>
@@ -8307,7 +8271,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>510</v>
       </c>
@@ -8334,7 +8298,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>511</v>
       </c>
@@ -8361,7 +8325,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>512</v>
       </c>
@@ -8388,7 +8352,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>513</v>
       </c>
@@ -8409,7 +8373,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>514</v>
       </c>
@@ -8430,7 +8394,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>515</v>
       </c>
@@ -8451,7 +8415,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>516</v>
       </c>
@@ -8472,7 +8436,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>517</v>
       </c>
@@ -8493,7 +8457,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>518</v>
       </c>
@@ -8514,7 +8478,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>519</v>
       </c>
@@ -8535,7 +8499,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>419</v>
       </c>
@@ -8556,7 +8520,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>431</v>
       </c>
@@ -8577,7 +8541,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>648</v>
       </c>
@@ -8598,7 +8562,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>649</v>
       </c>
@@ -8619,7 +8583,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>650</v>
       </c>
@@ -8640,7 +8604,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>651</v>
       </c>
@@ -8661,7 +8625,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>652</v>
       </c>
@@ -8682,7 +8646,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>653</v>
       </c>
@@ -8703,7 +8667,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>654</v>
       </c>
@@ -8724,7 +8688,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>655</v>
       </c>
@@ -8745,7 +8709,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>656</v>
       </c>
@@ -8766,7 +8730,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>657</v>
       </c>
@@ -8787,7 +8751,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>775</v>
       </c>
@@ -8813,7 +8777,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>438</v>
       </c>
@@ -8834,7 +8798,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>439</v>
       </c>
@@ -8855,7 +8819,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>440</v>
       </c>
@@ -8876,7 +8840,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>441</v>
       </c>
@@ -8897,7 +8861,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>442</v>
       </c>
@@ -8918,7 +8882,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>443</v>
       </c>
@@ -8939,7 +8903,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>444</v>
       </c>
@@ -8960,7 +8924,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>445</v>
       </c>
@@ -8981,7 +8945,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>446</v>
       </c>
@@ -9002,7 +8966,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>447</v>
       </c>
@@ -9023,7 +8987,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>448</v>
       </c>
@@ -9044,7 +9008,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>449</v>
       </c>
@@ -9065,7 +9029,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>450</v>
       </c>
@@ -9086,7 +9050,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>451</v>
       </c>
@@ -9107,7 +9071,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>452</v>
       </c>
@@ -9128,7 +9092,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>453</v>
       </c>
@@ -9149,7 +9113,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>454</v>
       </c>
@@ -9170,7 +9134,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>455</v>
       </c>
@@ -9191,7 +9155,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>456</v>
       </c>
@@ -9212,7 +9176,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>457</v>
       </c>
@@ -9233,7 +9197,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>458</v>
       </c>
@@ -9254,7 +9218,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>459</v>
       </c>
@@ -9275,7 +9239,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>460</v>
       </c>
@@ -9296,7 +9260,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>461</v>
       </c>
@@ -9317,7 +9281,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>462</v>
       </c>
@@ -9338,7 +9302,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>637</v>
       </c>
@@ -9359,7 +9323,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>6</v>
       </c>
@@ -9391,7 +9355,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>9</v>
       </c>
@@ -9423,7 +9387,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>8</v>
       </c>
@@ -9458,7 +9422,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>909</v>
       </c>
@@ -9487,7 +9451,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>10</v>
       </c>
@@ -9519,7 +9483,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>11</v>
       </c>
@@ -9551,7 +9515,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>913</v>
       </c>
@@ -9580,7 +9544,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>915</v>
       </c>
@@ -9609,7 +9573,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>7</v>
       </c>
@@ -9641,7 +9605,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>906</v>
       </c>
@@ -9670,7 +9634,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>911</v>
       </c>
@@ -9699,7 +9663,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>13</v>
       </c>
@@ -9731,7 +9695,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>918</v>
       </c>
@@ -9760,7 +9724,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>919</v>
       </c>
@@ -9789,7 +9753,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>922</v>
       </c>
@@ -9818,7 +9782,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>923</v>
       </c>
@@ -9847,7 +9811,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>924</v>
       </c>
@@ -9876,7 +9840,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>925</v>
       </c>
@@ -9905,7 +9869,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>931</v>
       </c>
@@ -9934,7 +9898,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>932</v>
       </c>
@@ -9963,7 +9927,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>933</v>
       </c>
@@ -9992,7 +9956,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>934</v>
       </c>
@@ -10021,7 +9985,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>943</v>
       </c>
@@ -10050,7 +10014,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>944</v>
       </c>
@@ -10079,7 +10043,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>12</v>
       </c>
@@ -10105,7 +10069,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>14</v>
       </c>
@@ -10131,7 +10095,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>15</v>
       </c>
@@ -10160,7 +10124,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>16</v>
       </c>
@@ -10189,7 +10153,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>17</v>
       </c>
@@ -10218,7 +10182,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>18</v>
       </c>
@@ -10247,7 +10211,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>19</v>
       </c>
@@ -10276,7 +10240,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>20</v>
       </c>
@@ -10305,7 +10269,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>21</v>
       </c>
@@ -10334,7 +10298,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>22</v>
       </c>
@@ -10363,7 +10327,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>23</v>
       </c>
@@ -10392,7 +10356,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>24</v>
       </c>
@@ -10421,7 +10385,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>25</v>
       </c>
@@ -10453,7 +10417,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>26</v>
       </c>
@@ -10482,7 +10446,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>27</v>
       </c>
@@ -10511,7 +10475,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>28</v>
       </c>
@@ -10543,7 +10507,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>29</v>
       </c>
@@ -10572,7 +10536,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>30</v>
       </c>
@@ -10604,7 +10568,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>31</v>
       </c>
@@ -10636,7 +10600,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>32</v>
       </c>
@@ -10668,7 +10632,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>33</v>
       </c>
@@ -10700,7 +10664,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>34</v>
       </c>
@@ -10732,7 +10696,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>488</v>
       </c>
@@ -10753,7 +10717,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>490</v>
       </c>
@@ -10774,7 +10738,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>491</v>
       </c>
@@ -10795,7 +10759,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>492</v>
       </c>
@@ -10816,7 +10780,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>430</v>
       </c>
@@ -10840,7 +10804,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>434</v>
       </c>
@@ -10864,7 +10828,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>435</v>
       </c>
@@ -10888,7 +10852,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>436</v>
       </c>
@@ -10912,7 +10876,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>437</v>
       </c>
@@ -10935,10 +10899,10 @@
     </row>
     <row r="300" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
+        <v>985</v>
+      </c>
+      <c r="B300" t="s">
         <v>986</v>
-      </c>
-      <c r="B300" t="s">
-        <v>987</v>
       </c>
       <c r="C300">
         <v>11</v>
@@ -10947,13 +10911,13 @@
         <v>2</v>
       </c>
       <c r="H300" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="I300" t="s">
         <v>900</v>
       </c>
       <c r="J300" s="3" t="s">
-        <v>988</v>
+        <v>748</v>
       </c>
       <c r="M300">
         <v>2</v>
@@ -10961,8 +10925,11 @@
       <c r="N300">
         <v>3</v>
       </c>
-    </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="R300" s="3" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="301" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>338</v>
       </c>
@@ -10989,7 +10956,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>339</v>
       </c>
@@ -11016,7 +10983,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>340</v>
       </c>
@@ -11043,7 +11010,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>341</v>
       </c>
@@ -11070,7 +11037,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>342</v>
       </c>
@@ -11097,7 +11064,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>343</v>
       </c>
@@ -11124,7 +11091,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>344</v>
       </c>
@@ -11165,22 +11132,23 @@
         <v>2</v>
       </c>
       <c r="H308" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="I308" t="s">
         <v>682</v>
       </c>
-      <c r="J308" s="3" t="s">
-        <v>985</v>
-      </c>
+      <c r="J308" s="3"/>
       <c r="M308">
         <v>3</v>
       </c>
       <c r="N308">
         <v>4</v>
       </c>
-    </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="R308" s="3" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="309" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>346</v>
       </c>
@@ -11201,7 +11169,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>347</v>
       </c>
@@ -11222,7 +11190,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>348</v>
       </c>
@@ -11243,7 +11211,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>349</v>
       </c>
@@ -11264,7 +11232,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>350</v>
       </c>
@@ -11285,7 +11253,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>351</v>
       </c>
@@ -11306,7 +11274,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>352</v>
       </c>
@@ -11327,7 +11295,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>353</v>
       </c>
@@ -11348,7 +11316,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>354</v>
       </c>
@@ -11369,7 +11337,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>355</v>
       </c>
@@ -11390,7 +11358,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>356</v>
       </c>
@@ -11411,7 +11379,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>357</v>
       </c>
@@ -11432,7 +11400,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>358</v>
       </c>
@@ -11453,7 +11421,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>359</v>
       </c>
@@ -11474,7 +11442,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>360</v>
       </c>
@@ -11495,7 +11463,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>361</v>
       </c>
@@ -11516,7 +11484,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>362</v>
       </c>
@@ -11537,7 +11505,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>363</v>
       </c>
@@ -11558,7 +11526,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>683</v>
       </c>
@@ -11581,7 +11549,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>684</v>
       </c>
@@ -11604,7 +11572,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>685</v>
       </c>
@@ -11627,7 +11595,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>686</v>
       </c>
@@ -11650,7 +11618,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>687</v>
       </c>
@@ -11673,7 +11641,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>688</v>
       </c>
@@ -11696,7 +11664,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>689</v>
       </c>
@@ -11719,7 +11687,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>690</v>
       </c>
@@ -11742,7 +11710,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>691</v>
       </c>
@@ -11765,7 +11733,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>692</v>
       </c>
@@ -11788,7 +11756,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>693</v>
       </c>
@@ -11811,7 +11779,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>694</v>
       </c>
@@ -11834,7 +11802,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>695</v>
       </c>
@@ -11857,7 +11825,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>696</v>
       </c>
@@ -11880,7 +11848,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>697</v>
       </c>
@@ -11903,7 +11871,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>698</v>
       </c>
@@ -11926,7 +11894,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>699</v>
       </c>
@@ -11949,7 +11917,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>700</v>
       </c>
@@ -11972,7 +11940,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>701</v>
       </c>
@@ -11995,7 +11963,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>702</v>
       </c>
@@ -12018,7 +11986,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>703</v>
       </c>
@@ -12041,7 +12009,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>704</v>
       </c>
@@ -12064,7 +12032,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>705</v>
       </c>
@@ -12087,7 +12055,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>706</v>
       </c>
@@ -12110,7 +12078,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="351" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>707</v>
       </c>
@@ -12133,7 +12101,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>971</v>
       </c>
@@ -12166,7 +12134,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="353" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>710</v>
       </c>
@@ -12269,13 +12237,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T355" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}"/>
+  <autoFilter ref="A4:T355" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="沃玛套装"/>
+        <filter val="沃玛战斧"/>
+        <filter val="沃玛战甲"/>
+        <filter val="沃玛手镯"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J25">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J300">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>

--- a/configs/Item.xlsx
+++ b/configs/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA0B89A-1342-4B84-BBC7-FC02417E8FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3F0DD3-4E48-47BB-85E0-C4B3C4730908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2344,9 +2344,6 @@
     <t>xdmg1,2</t>
   </si>
   <si>
-    <t>xdmg1rev,0.5:curs1,0</t>
-  </si>
-  <si>
     <t>xdmg1,0:luck1,0</t>
   </si>
   <si>
@@ -3039,6 +3036,9 @@
   </si>
   <si>
     <t>maxAffixCount</t>
+  </si>
+  <si>
+    <t>xdmglo1,0.5:curs1,0</t>
   </si>
 </sst>
 </file>
@@ -3480,7 +3480,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:T355"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3519,7 +3518,7 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F1" t="s">
         <v>36</v>
@@ -3543,10 +3542,10 @@
         <v>669</v>
       </c>
       <c r="M1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="N1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="O1" t="s">
         <v>677</v>
@@ -3555,21 +3554,21 @@
         <v>712</v>
       </c>
       <c r="Q1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="R1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="S1" t="s">
         <v>718</v>
       </c>
       <c r="T1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -3617,16 +3616,16 @@
         <v>713</v>
       </c>
       <c r="Q2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="S2" t="s">
         <v>5</v>
       </c>
       <c r="T2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
@@ -3634,7 +3633,7 @@
         <v>44</v>
       </c>
       <c r="I3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
@@ -3651,7 +3650,7 @@
         <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>53</v>
@@ -3675,10 +3674,10 @@
         <v>671</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>678</v>
@@ -3687,19 +3686,19 @@
         <v>714</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>719</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>48</v>
       </c>
@@ -3719,7 +3718,7 @@
         <v>108</v>
       </c>
       <c r="H5" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I5" t="s">
         <v>40</v>
@@ -3731,10 +3730,10 @@
         <v>735</v>
       </c>
       <c r="T5" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -3751,7 +3750,7 @@
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="I6" t="s">
         <v>40</v>
@@ -3760,10 +3759,10 @@
         <v>722</v>
       </c>
       <c r="T6" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>109</v>
       </c>
@@ -3780,7 +3779,7 @@
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="I7" t="s">
         <v>40</v>
@@ -3792,10 +3791,10 @@
         <v>735</v>
       </c>
       <c r="T7" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>110</v>
       </c>
@@ -3812,7 +3811,7 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="I8" t="s">
         <v>40</v>
@@ -3821,10 +3820,10 @@
         <v>724</v>
       </c>
       <c r="T8" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>111</v>
       </c>
@@ -3841,7 +3840,7 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="I9" t="s">
         <v>40</v>
@@ -3853,10 +3852,10 @@
         <v>735</v>
       </c>
       <c r="T9" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -3873,7 +3872,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="I10" t="s">
         <v>40</v>
@@ -3882,10 +3881,10 @@
         <v>730</v>
       </c>
       <c r="T10" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>113</v>
       </c>
@@ -3902,7 +3901,7 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="I11" t="s">
         <v>40</v>
@@ -3911,10 +3910,10 @@
         <v>663</v>
       </c>
       <c r="T11" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>157</v>
       </c>
@@ -3931,7 +3930,7 @@
         <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="I12" t="s">
         <v>40</v>
@@ -3940,10 +3939,10 @@
         <v>665</v>
       </c>
       <c r="T12" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>119</v>
       </c>
@@ -3973,7 +3972,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>120</v>
       </c>
@@ -4003,7 +4002,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>121</v>
       </c>
@@ -4033,7 +4032,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>122</v>
       </c>
@@ -4063,7 +4062,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>127</v>
       </c>
@@ -4093,7 +4092,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>128</v>
       </c>
@@ -4123,7 +4122,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>129</v>
       </c>
@@ -4153,7 +4152,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>130</v>
       </c>
@@ -4183,7 +4182,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>139</v>
       </c>
@@ -4213,7 +4212,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>140</v>
       </c>
@@ -4243,7 +4242,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>141</v>
       </c>
@@ -4273,7 +4272,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>142</v>
       </c>
@@ -4305,10 +4304,10 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>982</v>
+      </c>
+      <c r="B25" t="s">
         <v>983</v>
-      </c>
-      <c r="B25" t="s">
-        <v>984</v>
       </c>
       <c r="C25">
         <v>11</v>
@@ -4317,7 +4316,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="I25" t="s">
         <v>40</v>
@@ -4330,10 +4329,10 @@
         <v>4</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>337</v>
       </c>
@@ -4354,7 +4353,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>525</v>
       </c>
@@ -4375,7 +4374,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>526</v>
       </c>
@@ -4396,7 +4395,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>527</v>
       </c>
@@ -4417,7 +4416,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>528</v>
       </c>
@@ -4438,7 +4437,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>529</v>
       </c>
@@ -4459,7 +4458,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>375</v>
       </c>
@@ -4483,10 +4482,10 @@
         <v>235</v>
       </c>
       <c r="T32" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>376</v>
       </c>
@@ -4510,10 +4509,10 @@
         <v>235</v>
       </c>
       <c r="T33" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>377</v>
       </c>
@@ -4537,10 +4536,10 @@
         <v>235</v>
       </c>
       <c r="T34" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>378</v>
       </c>
@@ -4564,10 +4563,10 @@
         <v>235</v>
       </c>
       <c r="T35" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>379</v>
       </c>
@@ -4591,10 +4590,10 @@
         <v>235</v>
       </c>
       <c r="T36" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>380</v>
       </c>
@@ -4618,10 +4617,10 @@
         <v>235</v>
       </c>
       <c r="T37" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>381</v>
       </c>
@@ -4645,10 +4644,10 @@
         <v>235</v>
       </c>
       <c r="T38" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>382</v>
       </c>
@@ -4669,7 +4668,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>402</v>
       </c>
@@ -4690,7 +4689,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>405</v>
       </c>
@@ -4711,7 +4710,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>409</v>
       </c>
@@ -4732,7 +4731,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>410</v>
       </c>
@@ -4753,7 +4752,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>413</v>
       </c>
@@ -4777,7 +4776,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>427</v>
       </c>
@@ -4798,7 +4797,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>428</v>
       </c>
@@ -4819,7 +4818,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>541</v>
       </c>
@@ -4840,7 +4839,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>542</v>
       </c>
@@ -4861,7 +4860,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>543</v>
       </c>
@@ -4882,7 +4881,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>544</v>
       </c>
@@ -4903,7 +4902,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>545</v>
       </c>
@@ -4924,7 +4923,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>546</v>
       </c>
@@ -4945,7 +4944,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>547</v>
       </c>
@@ -4966,7 +4965,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>548</v>
       </c>
@@ -4987,7 +4986,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>549</v>
       </c>
@@ -5008,7 +5007,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>550</v>
       </c>
@@ -5029,7 +5028,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>551</v>
       </c>
@@ -5050,7 +5049,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>391</v>
       </c>
@@ -5074,10 +5073,10 @@
         <v>261</v>
       </c>
       <c r="T58" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>392</v>
       </c>
@@ -5101,10 +5100,10 @@
         <v>261</v>
       </c>
       <c r="T59" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>393</v>
       </c>
@@ -5128,10 +5127,10 @@
         <v>261</v>
       </c>
       <c r="T60" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>394</v>
       </c>
@@ -5155,10 +5154,10 @@
         <v>261</v>
       </c>
       <c r="T61" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>395</v>
       </c>
@@ -5182,10 +5181,10 @@
         <v>261</v>
       </c>
       <c r="T62" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>396</v>
       </c>
@@ -5209,10 +5208,10 @@
         <v>261</v>
       </c>
       <c r="T63" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>397</v>
       </c>
@@ -5236,10 +5235,10 @@
         <v>261</v>
       </c>
       <c r="T64" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>398</v>
       </c>
@@ -5260,7 +5259,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>399</v>
       </c>
@@ -5281,7 +5280,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>400</v>
       </c>
@@ -5302,7 +5301,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>401</v>
       </c>
@@ -5323,7 +5322,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>408</v>
       </c>
@@ -5344,7 +5343,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>414</v>
       </c>
@@ -5365,7 +5364,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>416</v>
       </c>
@@ -5386,7 +5385,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>421</v>
       </c>
@@ -5407,7 +5406,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>429</v>
       </c>
@@ -5431,7 +5430,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>561</v>
       </c>
@@ -5452,7 +5451,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>562</v>
       </c>
@@ -5473,7 +5472,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>564</v>
       </c>
@@ -5494,7 +5493,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>565</v>
       </c>
@@ -5515,7 +5514,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>566</v>
       </c>
@@ -5536,7 +5535,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>567</v>
       </c>
@@ -5557,7 +5556,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>568</v>
       </c>
@@ -5578,7 +5577,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>569</v>
       </c>
@@ -5599,7 +5598,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="82" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>570</v>
       </c>
@@ -5620,7 +5619,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>571</v>
       </c>
@@ -5641,7 +5640,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>485</v>
       </c>
@@ -5658,13 +5657,13 @@
         <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="I84" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>486</v>
       </c>
@@ -5681,13 +5680,13 @@
         <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="I85" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>487</v>
       </c>
@@ -5704,13 +5703,13 @@
         <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="I86" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>364</v>
       </c>
@@ -5734,10 +5733,10 @@
         <v>234</v>
       </c>
       <c r="T87" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>365</v>
       </c>
@@ -5761,10 +5760,10 @@
         <v>234</v>
       </c>
       <c r="T88" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>366</v>
       </c>
@@ -5788,10 +5787,10 @@
         <v>234</v>
       </c>
       <c r="T89" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>367</v>
       </c>
@@ -5815,10 +5814,10 @@
         <v>234</v>
       </c>
       <c r="T90" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>368</v>
       </c>
@@ -5842,10 +5841,10 @@
         <v>234</v>
       </c>
       <c r="T91" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>369</v>
       </c>
@@ -5869,10 +5868,10 @@
         <v>234</v>
       </c>
       <c r="T92" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>370</v>
       </c>
@@ -5896,10 +5895,10 @@
         <v>234</v>
       </c>
       <c r="T93" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>371</v>
       </c>
@@ -5920,7 +5919,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>372</v>
       </c>
@@ -5941,7 +5940,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>373</v>
       </c>
@@ -5962,7 +5961,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>374</v>
       </c>
@@ -5983,7 +5982,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>403</v>
       </c>
@@ -6004,7 +6003,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>412</v>
       </c>
@@ -6025,7 +6024,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>418</v>
       </c>
@@ -6046,7 +6045,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>422</v>
       </c>
@@ -6067,7 +6066,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>432</v>
       </c>
@@ -6088,7 +6087,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>582</v>
       </c>
@@ -6109,7 +6108,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>583</v>
       </c>
@@ -6130,7 +6129,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>584</v>
       </c>
@@ -6151,7 +6150,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>585</v>
       </c>
@@ -6172,7 +6171,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>586</v>
       </c>
@@ -6193,7 +6192,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>587</v>
       </c>
@@ -6214,7 +6213,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>588</v>
       </c>
@@ -6235,7 +6234,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>589</v>
       </c>
@@ -6256,7 +6255,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>590</v>
       </c>
@@ -6277,7 +6276,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>591</v>
       </c>
@@ -6298,7 +6297,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="113" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>143</v>
       </c>
@@ -6322,10 +6321,10 @@
         <v>160</v>
       </c>
       <c r="T113" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="114" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>493</v>
       </c>
@@ -6349,10 +6348,10 @@
         <v>160</v>
       </c>
       <c r="T114" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="115" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>494</v>
       </c>
@@ -6376,10 +6375,10 @@
         <v>160</v>
       </c>
       <c r="T115" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>495</v>
       </c>
@@ -6406,10 +6405,10 @@
         <v>721</v>
       </c>
       <c r="T116" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>496</v>
       </c>
@@ -6433,10 +6432,10 @@
         <v>160</v>
       </c>
       <c r="T117" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>497</v>
       </c>
@@ -6460,10 +6459,10 @@
         <v>160</v>
       </c>
       <c r="T118" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="119" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>498</v>
       </c>
@@ -6487,10 +6486,10 @@
         <v>160</v>
       </c>
       <c r="T119" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="120" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>499</v>
       </c>
@@ -6517,7 +6516,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="121" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>500</v>
       </c>
@@ -6544,7 +6543,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>501</v>
       </c>
@@ -6568,7 +6567,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="123" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>502</v>
       </c>
@@ -6592,7 +6591,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="124" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>503</v>
       </c>
@@ -6619,7 +6618,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="125" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>504</v>
       </c>
@@ -6646,7 +6645,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="126" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>505</v>
       </c>
@@ -6673,7 +6672,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="127" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>420</v>
       </c>
@@ -6694,7 +6693,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="128" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>424</v>
       </c>
@@ -6718,7 +6717,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="129" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>425</v>
       </c>
@@ -6742,7 +6741,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="130" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>426</v>
       </c>
@@ -6766,7 +6765,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>600</v>
       </c>
@@ -6787,7 +6786,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="132" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>601</v>
       </c>
@@ -6808,7 +6807,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="133" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>602</v>
       </c>
@@ -6829,7 +6828,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="134" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>603</v>
       </c>
@@ -6850,7 +6849,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="135" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>604</v>
       </c>
@@ -6871,7 +6870,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="136" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>605</v>
       </c>
@@ -6892,7 +6891,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="137" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>606</v>
       </c>
@@ -6913,7 +6912,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="138" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>607</v>
       </c>
@@ -6934,12 +6933,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="139" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
+        <v>772</v>
+      </c>
+      <c r="B139" t="s">
         <v>773</v>
-      </c>
-      <c r="B139" t="s">
-        <v>774</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -6951,16 +6950,16 @@
         <v>2</v>
       </c>
       <c r="H139" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="I139" t="s">
         <v>258</v>
       </c>
       <c r="T139" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="140" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>463</v>
       </c>
@@ -6984,7 +6983,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="141" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>464</v>
       </c>
@@ -7008,7 +7007,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="142" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>465</v>
       </c>
@@ -7032,7 +7031,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="143" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>466</v>
       </c>
@@ -7056,7 +7055,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="144" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>467</v>
       </c>
@@ -7080,7 +7079,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>468</v>
       </c>
@@ -7107,7 +7106,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>469</v>
       </c>
@@ -7131,7 +7130,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>470</v>
       </c>
@@ -7155,7 +7154,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>471</v>
       </c>
@@ -7179,7 +7178,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>472</v>
       </c>
@@ -7203,7 +7202,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>473</v>
       </c>
@@ -7227,7 +7226,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>474</v>
       </c>
@@ -7251,7 +7250,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>475</v>
       </c>
@@ -7275,7 +7274,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>476</v>
       </c>
@@ -7299,7 +7298,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>477</v>
       </c>
@@ -7323,7 +7322,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>478</v>
       </c>
@@ -7347,7 +7346,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>479</v>
       </c>
@@ -7371,7 +7370,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>480</v>
       </c>
@@ -7395,7 +7394,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>481</v>
       </c>
@@ -7419,7 +7418,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>482</v>
       </c>
@@ -7443,7 +7442,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>483</v>
       </c>
@@ -7467,7 +7466,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="161" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>484</v>
       </c>
@@ -7491,7 +7490,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="162" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>612</v>
       </c>
@@ -7512,7 +7511,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="163" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>613</v>
       </c>
@@ -7533,7 +7532,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="164" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>614</v>
       </c>
@@ -7554,7 +7553,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="165" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>615</v>
       </c>
@@ -7575,7 +7574,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="166" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>383</v>
       </c>
@@ -7599,10 +7598,10 @@
         <v>260</v>
       </c>
       <c r="T166" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="167" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>384</v>
       </c>
@@ -7626,10 +7625,10 @@
         <v>260</v>
       </c>
       <c r="T167" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="168" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>385</v>
       </c>
@@ -7653,10 +7652,10 @@
         <v>260</v>
       </c>
       <c r="T168" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="169" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>386</v>
       </c>
@@ -7680,10 +7679,10 @@
         <v>260</v>
       </c>
       <c r="T169" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="170" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>387</v>
       </c>
@@ -7707,10 +7706,10 @@
         <v>260</v>
       </c>
       <c r="T170" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="171" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="171" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>388</v>
       </c>
@@ -7734,10 +7733,10 @@
         <v>260</v>
       </c>
       <c r="T171" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="172" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>389</v>
       </c>
@@ -7761,10 +7760,10 @@
         <v>260</v>
       </c>
       <c r="T172" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="173" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="173" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>390</v>
       </c>
@@ -7785,7 +7784,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="174" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>404</v>
       </c>
@@ -7806,7 +7805,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="175" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>406</v>
       </c>
@@ -7827,7 +7826,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="176" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>407</v>
       </c>
@@ -7848,7 +7847,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="177" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>411</v>
       </c>
@@ -7869,7 +7868,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="178" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>415</v>
       </c>
@@ -7890,7 +7889,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="179" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>417</v>
       </c>
@@ -7911,7 +7910,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="180" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>423</v>
       </c>
@@ -7932,7 +7931,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="181" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>433</v>
       </c>
@@ -7953,7 +7952,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="182" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>626</v>
       </c>
@@ -7974,7 +7973,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="183" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>627</v>
       </c>
@@ -7995,7 +7994,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="184" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>628</v>
       </c>
@@ -8016,7 +8015,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="185" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>629</v>
       </c>
@@ -8037,7 +8036,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="186" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>630</v>
       </c>
@@ -8058,7 +8057,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="187" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>631</v>
       </c>
@@ -8079,7 +8078,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="188" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>632</v>
       </c>
@@ -8100,7 +8099,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="189" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>633</v>
       </c>
@@ -8121,7 +8120,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="190" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>634</v>
       </c>
@@ -8142,7 +8141,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="191" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>635</v>
       </c>
@@ -8163,7 +8162,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="192" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>506</v>
       </c>
@@ -8187,10 +8186,10 @@
         <v>259</v>
       </c>
       <c r="T192" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="193" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>507</v>
       </c>
@@ -8214,10 +8213,10 @@
         <v>259</v>
       </c>
       <c r="T193" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="194" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>508</v>
       </c>
@@ -8241,10 +8240,10 @@
         <v>259</v>
       </c>
       <c r="T194" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="195" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>509</v>
       </c>
@@ -8268,10 +8267,10 @@
         <v>259</v>
       </c>
       <c r="T195" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="196" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>510</v>
       </c>
@@ -8295,10 +8294,10 @@
         <v>259</v>
       </c>
       <c r="T196" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="197" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>511</v>
       </c>
@@ -8322,10 +8321,10 @@
         <v>259</v>
       </c>
       <c r="T197" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="198" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>512</v>
       </c>
@@ -8349,10 +8348,10 @@
         <v>259</v>
       </c>
       <c r="T198" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="199" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>513</v>
       </c>
@@ -8373,7 +8372,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="200" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>514</v>
       </c>
@@ -8394,7 +8393,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="201" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>515</v>
       </c>
@@ -8415,7 +8414,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="202" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>516</v>
       </c>
@@ -8436,7 +8435,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="203" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>517</v>
       </c>
@@ -8457,7 +8456,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="204" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>518</v>
       </c>
@@ -8478,7 +8477,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="205" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>519</v>
       </c>
@@ -8499,7 +8498,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="206" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>419</v>
       </c>
@@ -8520,7 +8519,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="207" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>431</v>
       </c>
@@ -8541,7 +8540,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="208" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>648</v>
       </c>
@@ -8562,7 +8561,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="209" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>649</v>
       </c>
@@ -8583,7 +8582,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="210" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>650</v>
       </c>
@@ -8604,7 +8603,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="211" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>651</v>
       </c>
@@ -8625,7 +8624,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="212" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>652</v>
       </c>
@@ -8646,7 +8645,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="213" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>653</v>
       </c>
@@ -8667,7 +8666,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="214" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>654</v>
       </c>
@@ -8688,7 +8687,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="215" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>655</v>
       </c>
@@ -8709,7 +8708,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="216" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>656</v>
       </c>
@@ -8730,7 +8729,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="217" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>657</v>
       </c>
@@ -8751,12 +8750,12 @@
         <v>259</v>
       </c>
     </row>
-    <row r="218" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
+        <v>774</v>
+      </c>
+      <c r="B218" t="s">
         <v>775</v>
-      </c>
-      <c r="B218" t="s">
-        <v>776</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -8768,16 +8767,16 @@
         <v>2</v>
       </c>
       <c r="H218" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="I218" t="s">
         <v>209</v>
       </c>
       <c r="T218" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="219" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="219" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>438</v>
       </c>
@@ -8798,7 +8797,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="220" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>439</v>
       </c>
@@ -8819,7 +8818,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="221" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>440</v>
       </c>
@@ -8840,7 +8839,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="222" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>441</v>
       </c>
@@ -8861,7 +8860,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="223" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>442</v>
       </c>
@@ -8882,7 +8881,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="224" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>443</v>
       </c>
@@ -8903,7 +8902,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>444</v>
       </c>
@@ -8924,7 +8923,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>445</v>
       </c>
@@ -8945,7 +8944,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>446</v>
       </c>
@@ -8966,7 +8965,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>447</v>
       </c>
@@ -8987,7 +8986,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>448</v>
       </c>
@@ -9008,7 +9007,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>449</v>
       </c>
@@ -9029,7 +9028,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>450</v>
       </c>
@@ -9050,7 +9049,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>451</v>
       </c>
@@ -9071,7 +9070,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>452</v>
       </c>
@@ -9092,7 +9091,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>453</v>
       </c>
@@ -9113,7 +9112,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>454</v>
       </c>
@@ -9134,7 +9133,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>455</v>
       </c>
@@ -9155,7 +9154,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>456</v>
       </c>
@@ -9176,7 +9175,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>457</v>
       </c>
@@ -9197,7 +9196,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>458</v>
       </c>
@@ -9218,7 +9217,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>459</v>
       </c>
@@ -9239,7 +9238,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="241" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>460</v>
       </c>
@@ -9260,7 +9259,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="242" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>461</v>
       </c>
@@ -9281,7 +9280,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="243" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>462</v>
       </c>
@@ -9302,7 +9301,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="244" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>637</v>
       </c>
@@ -9323,7 +9322,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="245" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>6</v>
       </c>
@@ -9343,19 +9342,19 @@
         <v>58</v>
       </c>
       <c r="H245" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="I245" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="J245" t="s">
         <v>748</v>
       </c>
       <c r="T245" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="246" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="246" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>9</v>
       </c>
@@ -9375,19 +9374,19 @@
         <v>64</v>
       </c>
       <c r="H246" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="I246" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="J246" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="T246" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="247" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="247" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>8</v>
       </c>
@@ -9407,27 +9406,27 @@
         <v>62</v>
       </c>
       <c r="H247" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="I247" t="s">
+        <v>903</v>
+      </c>
+      <c r="J247" t="s">
         <v>904</v>
-      </c>
-      <c r="J247" t="s">
-        <v>905</v>
       </c>
       <c r="K247" t="s">
         <v>754</v>
       </c>
       <c r="T247" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="248" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="248" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
+        <v>908</v>
+      </c>
+      <c r="B248" t="s">
         <v>909</v>
-      </c>
-      <c r="B248" t="s">
-        <v>910</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9439,24 +9438,24 @@
         <v>2</v>
       </c>
       <c r="H248" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="I248" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="J248" t="s">
         <v>749</v>
       </c>
       <c r="T248" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="249" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="249" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>10</v>
       </c>
       <c r="B249" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C249">
         <v>10</v>
@@ -9471,24 +9470,24 @@
         <v>65</v>
       </c>
       <c r="H249" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="I249" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="J249" t="s">
         <v>749</v>
       </c>
       <c r="T249" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="250" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="250" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>11</v>
       </c>
       <c r="B250" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C250">
         <v>10</v>
@@ -9503,24 +9502,24 @@
         <v>66</v>
       </c>
       <c r="H250" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="I250" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="J250" t="s">
         <v>750</v>
       </c>
       <c r="T250" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="251" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="251" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
+        <v>912</v>
+      </c>
+      <c r="B251" t="s">
         <v>913</v>
-      </c>
-      <c r="B251" t="s">
-        <v>914</v>
       </c>
       <c r="C251">
         <v>10</v>
@@ -9532,24 +9531,24 @@
         <v>2</v>
       </c>
       <c r="H251" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="I251" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="J251" t="s">
         <v>750</v>
       </c>
       <c r="T251" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="252" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="252" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
+        <v>914</v>
+      </c>
+      <c r="B252" t="s">
         <v>915</v>
-      </c>
-      <c r="B252" t="s">
-        <v>916</v>
       </c>
       <c r="C252">
         <v>10</v>
@@ -9561,19 +9560,19 @@
         <v>2</v>
       </c>
       <c r="H252" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="I252" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="J252" t="s">
         <v>750</v>
       </c>
       <c r="T252" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="253" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="253" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>7</v>
       </c>
@@ -9593,7 +9592,7 @@
         <v>60</v>
       </c>
       <c r="H253" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="I253" t="s">
         <v>7</v>
@@ -9602,15 +9601,15 @@
         <v>753</v>
       </c>
       <c r="T253" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="254" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="254" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
+        <v>905</v>
+      </c>
+      <c r="B254" t="s">
         <v>906</v>
-      </c>
-      <c r="B254" t="s">
-        <v>907</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9622,24 +9621,24 @@
         <v>2</v>
       </c>
       <c r="H254" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="I254" t="s">
         <v>7</v>
       </c>
       <c r="J254" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="T254" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="255" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="255" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
+        <v>910</v>
+      </c>
+      <c r="B255" t="s">
         <v>911</v>
-      </c>
-      <c r="B255" t="s">
-        <v>912</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9651,19 +9650,19 @@
         <v>2</v>
       </c>
       <c r="H255" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="I255" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J255" t="s">
         <v>749</v>
       </c>
       <c r="T255" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="256" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="256" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>13</v>
       </c>
@@ -9683,24 +9682,24 @@
         <v>70</v>
       </c>
       <c r="H256" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="I256" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J256" t="s">
         <v>751</v>
       </c>
       <c r="T256" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="257" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="257" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B257" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C257">
         <v>11</v>
@@ -9712,24 +9711,24 @@
         <v>2</v>
       </c>
       <c r="H257" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="I257" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="J257" t="s">
         <v>751</v>
       </c>
       <c r="T257" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="258" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="258" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B258" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C258">
         <v>11</v>
@@ -9741,24 +9740,24 @@
         <v>2</v>
       </c>
       <c r="H258" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="I258" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="J258" t="s">
         <v>751</v>
       </c>
       <c r="T258" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="259" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="259" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B259" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C259">
         <v>11</v>
@@ -9770,24 +9769,24 @@
         <v>2</v>
       </c>
       <c r="H259" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="I259" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="J259" t="s">
         <v>751</v>
       </c>
       <c r="T259" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="260" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="260" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B260" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C260">
         <v>11</v>
@@ -9799,24 +9798,24 @@
         <v>2</v>
       </c>
       <c r="H260" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="I260" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="J260" t="s">
         <v>751</v>
       </c>
       <c r="T260" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="261" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="261" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B261" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C261">
         <v>11</v>
@@ -9828,24 +9827,24 @@
         <v>2</v>
       </c>
       <c r="H261" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="I261" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="J261" t="s">
         <v>751</v>
       </c>
       <c r="T261" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="262" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="262" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B262" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C262">
         <v>11</v>
@@ -9857,24 +9856,24 @@
         <v>2</v>
       </c>
       <c r="H262" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="I262" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="J262" t="s">
         <v>751</v>
       </c>
       <c r="T262" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="263" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="263" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B263" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C263">
         <v>11</v>
@@ -9886,24 +9885,24 @@
         <v>2</v>
       </c>
       <c r="H263" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="I263" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="J263" t="s">
         <v>751</v>
       </c>
       <c r="T263" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="264" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="264" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B264" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C264">
         <v>11</v>
@@ -9915,24 +9914,24 @@
         <v>2</v>
       </c>
       <c r="H264" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="I264" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="J264" t="s">
         <v>751</v>
       </c>
       <c r="T264" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="265" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="265" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B265" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C265">
         <v>11</v>
@@ -9944,24 +9943,24 @@
         <v>2</v>
       </c>
       <c r="H265" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="I265" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="J265" t="s">
         <v>751</v>
       </c>
       <c r="T265" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="266" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="266" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B266" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C266">
         <v>11</v>
@@ -9973,24 +9972,24 @@
         <v>2</v>
       </c>
       <c r="H266" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="I266" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="J266" t="s">
         <v>751</v>
       </c>
       <c r="T266" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="267" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="267" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B267" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C267">
         <v>11</v>
@@ -10002,24 +10001,24 @@
         <v>2</v>
       </c>
       <c r="H267" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="I267" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="K267" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="T267" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="268" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="268" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B268" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C268">
         <v>11</v>
@@ -10031,19 +10030,19 @@
         <v>2</v>
       </c>
       <c r="H268" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I268" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="K268" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="T268" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="269" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="269" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>12</v>
       </c>
@@ -10060,16 +10059,16 @@
         <v>68</v>
       </c>
       <c r="H269" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="I269" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J269" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="270" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="270" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>14</v>
       </c>
@@ -10086,16 +10085,16 @@
         <v>72</v>
       </c>
       <c r="H270" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="I270" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="J270" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="271" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="271" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>15</v>
       </c>
@@ -10115,16 +10114,16 @@
         <v>74</v>
       </c>
       <c r="H271" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="I271" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="J271" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="272" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>16</v>
       </c>
@@ -10144,16 +10143,16 @@
         <v>76</v>
       </c>
       <c r="H272" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="I272" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="J272" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>17</v>
       </c>
@@ -10173,16 +10172,16 @@
         <v>77</v>
       </c>
       <c r="H273" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="I273" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="J273" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>18</v>
       </c>
@@ -10202,16 +10201,16 @@
         <v>78</v>
       </c>
       <c r="H274" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="I274" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="J274" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>19</v>
       </c>
@@ -10231,16 +10230,16 @@
         <v>79</v>
       </c>
       <c r="H275" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="I275" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J275" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>20</v>
       </c>
@@ -10260,16 +10259,16 @@
         <v>80</v>
       </c>
       <c r="H276" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="I276" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="J276" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>21</v>
       </c>
@@ -10289,16 +10288,16 @@
         <v>81</v>
       </c>
       <c r="H277" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="I277" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="J277" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>22</v>
       </c>
@@ -10318,16 +10317,16 @@
         <v>82</v>
       </c>
       <c r="H278" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="I278" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="J278" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>23</v>
       </c>
@@ -10347,16 +10346,16 @@
         <v>84</v>
       </c>
       <c r="H279" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="I279" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="J279" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>24</v>
       </c>
@@ -10376,16 +10375,16 @@
         <v>86</v>
       </c>
       <c r="H280" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="I280" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="J280" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>25</v>
       </c>
@@ -10408,16 +10407,16 @@
         <v>39</v>
       </c>
       <c r="I281" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="J281" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="K281" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>26</v>
       </c>
@@ -10440,13 +10439,13 @@
         <v>39</v>
       </c>
       <c r="I282" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="J282" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>27</v>
       </c>
@@ -10469,13 +10468,13 @@
         <v>39</v>
       </c>
       <c r="I283" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="J283" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>28</v>
       </c>
@@ -10498,7 +10497,7 @@
         <v>39</v>
       </c>
       <c r="I284" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="J284" t="s">
         <v>760</v>
@@ -10507,7 +10506,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>29</v>
       </c>
@@ -10530,13 +10529,13 @@
         <v>39</v>
       </c>
       <c r="I285" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="J285" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>30</v>
       </c>
@@ -10559,7 +10558,7 @@
         <v>39</v>
       </c>
       <c r="I286" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="J286" t="s">
         <v>750</v>
@@ -10568,7 +10567,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>31</v>
       </c>
@@ -10591,7 +10590,7 @@
         <v>39</v>
       </c>
       <c r="I287" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="J287" t="s">
         <v>752</v>
@@ -10600,7 +10599,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>32</v>
       </c>
@@ -10623,7 +10622,7 @@
         <v>39</v>
       </c>
       <c r="I288" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="J288" t="s">
         <v>667</v>
@@ -10632,7 +10631,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="289" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>33</v>
       </c>
@@ -10655,7 +10654,7 @@
         <v>39</v>
       </c>
       <c r="I289" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="J289" t="s">
         <v>758</v>
@@ -10664,7 +10663,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="290" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>34</v>
       </c>
@@ -10687,7 +10686,7 @@
         <v>39</v>
       </c>
       <c r="I290" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="J290" t="s">
         <v>675</v>
@@ -10696,7 +10695,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="291" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>488</v>
       </c>
@@ -10714,10 +10713,10 @@
         <v>虹</v>
       </c>
       <c r="I291" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="292" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="292" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>490</v>
       </c>
@@ -10735,10 +10734,10 @@
         <v>神</v>
       </c>
       <c r="I292" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="293" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="293" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>491</v>
       </c>
@@ -10756,10 +10755,10 @@
         <v>魔</v>
       </c>
       <c r="I293" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="294" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="294" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>492</v>
       </c>
@@ -10777,10 +10776,10 @@
         <v>赤</v>
       </c>
       <c r="I294" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="295" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="295" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>430</v>
       </c>
@@ -10801,10 +10800,10 @@
         <v>启</v>
       </c>
       <c r="I295" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="296" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="296" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>434</v>
       </c>
@@ -10825,10 +10824,10 @@
         <v>怒</v>
       </c>
       <c r="I296" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="297" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="297" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>435</v>
       </c>
@@ -10852,7 +10851,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="298" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>436</v>
       </c>
@@ -10873,10 +10872,10 @@
         <v>逍</v>
       </c>
       <c r="I298" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="299" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="299" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>437</v>
       </c>
@@ -10894,15 +10893,15 @@
         <v>卧</v>
       </c>
       <c r="I299" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="300" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
+        <v>984</v>
+      </c>
+      <c r="B300" t="s">
         <v>985</v>
-      </c>
-      <c r="B300" t="s">
-        <v>986</v>
       </c>
       <c r="C300">
         <v>11</v>
@@ -10911,10 +10910,10 @@
         <v>2</v>
       </c>
       <c r="H300" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="I300" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J300" s="3" t="s">
         <v>748</v>
@@ -10926,10 +10925,10 @@
         <v>3</v>
       </c>
       <c r="R300" s="3" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="301" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="301" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>338</v>
       </c>
@@ -10953,10 +10952,10 @@
         <v>682</v>
       </c>
       <c r="T301" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="302" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="302" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>339</v>
       </c>
@@ -10980,10 +10979,10 @@
         <v>682</v>
       </c>
       <c r="T302" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="303" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="303" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>340</v>
       </c>
@@ -11007,10 +11006,10 @@
         <v>682</v>
       </c>
       <c r="T303" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="304" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="304" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>341</v>
       </c>
@@ -11034,10 +11033,10 @@
         <v>682</v>
       </c>
       <c r="T304" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="305" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="305" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>342</v>
       </c>
@@ -11061,10 +11060,10 @@
         <v>682</v>
       </c>
       <c r="T305" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="306" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="306" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>343</v>
       </c>
@@ -11088,10 +11087,10 @@
         <v>682</v>
       </c>
       <c r="T306" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="307" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="307" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>344</v>
       </c>
@@ -11115,7 +11114,7 @@
         <v>682</v>
       </c>
       <c r="T307" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="308" spans="1:20" x14ac:dyDescent="0.35">
@@ -11132,7 +11131,7 @@
         <v>2</v>
       </c>
       <c r="H308" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="I308" t="s">
         <v>682</v>
@@ -11145,10 +11144,10 @@
         <v>4</v>
       </c>
       <c r="R308" s="3" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="309" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="309" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>346</v>
       </c>
@@ -11169,7 +11168,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="310" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>347</v>
       </c>
@@ -11190,7 +11189,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="311" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>348</v>
       </c>
@@ -11211,7 +11210,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="312" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>349</v>
       </c>
@@ -11232,7 +11231,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="313" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>350</v>
       </c>
@@ -11253,7 +11252,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="314" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>351</v>
       </c>
@@ -11274,7 +11273,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="315" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>352</v>
       </c>
@@ -11295,7 +11294,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="316" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>353</v>
       </c>
@@ -11316,7 +11315,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="317" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>354</v>
       </c>
@@ -11337,7 +11336,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="318" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>355</v>
       </c>
@@ -11358,7 +11357,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="319" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>356</v>
       </c>
@@ -11379,7 +11378,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="320" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>357</v>
       </c>
@@ -11400,7 +11399,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>358</v>
       </c>
@@ -11421,7 +11420,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="322" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>359</v>
       </c>
@@ -11442,7 +11441,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>360</v>
       </c>
@@ -11463,7 +11462,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>361</v>
       </c>
@@ -11484,7 +11483,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>362</v>
       </c>
@@ -11505,7 +11504,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>363</v>
       </c>
@@ -11526,12 +11525,12 @@
         <v>682</v>
       </c>
     </row>
-    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>683</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C327">
         <v>7</v>
@@ -11540,7 +11539,7 @@
         <v>0</v>
       </c>
       <c r="H327" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="I327" t="s">
         <v>708</v>
@@ -11549,12 +11548,12 @@
         <v>748</v>
       </c>
     </row>
-    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>684</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C328">
         <v>7</v>
@@ -11563,21 +11562,21 @@
         <v>0</v>
       </c>
       <c r="H328" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="I328" t="s">
         <v>708</v>
       </c>
       <c r="J328" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>685</v>
       </c>
       <c r="B329" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C329">
         <v>7</v>
@@ -11586,21 +11585,21 @@
         <v>0</v>
       </c>
       <c r="H329" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="I329" t="s">
         <v>708</v>
       </c>
       <c r="J329" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>686</v>
       </c>
       <c r="B330" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C330">
         <v>7</v>
@@ -11609,21 +11608,21 @@
         <v>0</v>
       </c>
       <c r="H330" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="I330" t="s">
         <v>708</v>
       </c>
       <c r="J330" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>687</v>
       </c>
       <c r="B331" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C331">
         <v>7</v>
@@ -11632,21 +11631,21 @@
         <v>0</v>
       </c>
       <c r="H331" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="I331" t="s">
         <v>708</v>
       </c>
       <c r="J331" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="332" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>688</v>
       </c>
       <c r="B332" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C332">
         <v>14</v>
@@ -11655,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="H332" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="I332" t="s">
         <v>708</v>
@@ -11664,12 +11663,12 @@
         <v>721</v>
       </c>
     </row>
-    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>689</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C333">
         <v>14</v>
@@ -11678,21 +11677,21 @@
         <v>1</v>
       </c>
       <c r="H333" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="I333" t="s">
         <v>708</v>
       </c>
       <c r="J333" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="334" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>690</v>
       </c>
       <c r="B334" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C334">
         <v>14</v>
@@ -11701,21 +11700,21 @@
         <v>1</v>
       </c>
       <c r="H334" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="I334" t="s">
         <v>708</v>
       </c>
       <c r="J334" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="335" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>691</v>
       </c>
       <c r="B335" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C335">
         <v>14</v>
@@ -11724,21 +11723,21 @@
         <v>1</v>
       </c>
       <c r="H335" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="I335" t="s">
         <v>708</v>
       </c>
       <c r="J335" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="336" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>692</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C336">
         <v>14</v>
@@ -11747,21 +11746,21 @@
         <v>1</v>
       </c>
       <c r="H336" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="I336" t="s">
         <v>708</v>
       </c>
       <c r="J336" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="337" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="337" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>693</v>
       </c>
       <c r="B337" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C337">
         <v>21</v>
@@ -11770,21 +11769,21 @@
         <v>2</v>
       </c>
       <c r="H337" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="I337" t="s">
         <v>708</v>
       </c>
       <c r="J337" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="338" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="338" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>694</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C338">
         <v>21</v>
@@ -11793,21 +11792,21 @@
         <v>2</v>
       </c>
       <c r="H338" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="I338" t="s">
         <v>708</v>
       </c>
       <c r="J338" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="339" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="339" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>695</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C339">
         <v>21</v>
@@ -11816,21 +11815,21 @@
         <v>2</v>
       </c>
       <c r="H339" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="I339" t="s">
         <v>708</v>
       </c>
       <c r="J339" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="340" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="340" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>696</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C340">
         <v>21</v>
@@ -11839,21 +11838,21 @@
         <v>2</v>
       </c>
       <c r="H340" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="I340" t="s">
         <v>708</v>
       </c>
       <c r="J340" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="341" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="341" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>697</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C341">
         <v>21</v>
@@ -11862,21 +11861,21 @@
         <v>2</v>
       </c>
       <c r="H341" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="I341" t="s">
         <v>708</v>
       </c>
       <c r="J341" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="342" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="342" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>698</v>
       </c>
       <c r="B342" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C342">
         <v>28</v>
@@ -11885,21 +11884,21 @@
         <v>3</v>
       </c>
       <c r="H342" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="I342" t="s">
         <v>708</v>
       </c>
       <c r="J342" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="343" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="343" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>699</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C343">
         <v>28</v>
@@ -11908,21 +11907,21 @@
         <v>3</v>
       </c>
       <c r="H343" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I343" t="s">
         <v>708</v>
       </c>
       <c r="J343" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="344" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="344" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>700</v>
       </c>
       <c r="B344" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C344">
         <v>28</v>
@@ -11931,21 +11930,21 @@
         <v>3</v>
       </c>
       <c r="H344" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I344" t="s">
         <v>708</v>
       </c>
       <c r="J344" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="345" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="345" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>701</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C345">
         <v>28</v>
@@ -11954,21 +11953,21 @@
         <v>3</v>
       </c>
       <c r="H345" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="I345" t="s">
         <v>708</v>
       </c>
       <c r="J345" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="346" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="346" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>702</v>
       </c>
       <c r="B346" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C346">
         <v>28</v>
@@ -11977,21 +11976,21 @@
         <v>3</v>
       </c>
       <c r="H346" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="I346" t="s">
         <v>708</v>
       </c>
       <c r="J346" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="347" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="347" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>703</v>
       </c>
       <c r="B347" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C347">
         <v>35</v>
@@ -12000,21 +11999,21 @@
         <v>4</v>
       </c>
       <c r="H347" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="I347" t="s">
         <v>708</v>
       </c>
       <c r="J347" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="348" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="348" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>704</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C348">
         <v>35</v>
@@ -12023,21 +12022,21 @@
         <v>4</v>
       </c>
       <c r="H348" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I348" t="s">
         <v>708</v>
       </c>
       <c r="J348" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="349" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="349" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>705</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C349">
         <v>35</v>
@@ -12046,21 +12045,21 @@
         <v>4</v>
       </c>
       <c r="H349" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="I349" t="s">
         <v>708</v>
       </c>
       <c r="J349" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="350" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="350" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>706</v>
       </c>
       <c r="B350" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C350">
         <v>35</v>
@@ -12069,21 +12068,21 @@
         <v>4</v>
       </c>
       <c r="H350" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="I350" t="s">
         <v>708</v>
       </c>
       <c r="J350" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="351" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="351" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>707</v>
       </c>
       <c r="B351" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C351">
         <v>35</v>
@@ -12092,21 +12091,21 @@
         <v>4</v>
       </c>
       <c r="H351" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="I351" t="s">
         <v>708</v>
       </c>
       <c r="J351" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="352" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="352" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
+        <v>970</v>
+      </c>
+      <c r="B352" t="s">
         <v>971</v>
-      </c>
-      <c r="B352" t="s">
-        <v>972</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -12122,19 +12121,19 @@
         <v>711</v>
       </c>
       <c r="J352" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="O352" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="P352" t="s">
+        <v>972</v>
+      </c>
+      <c r="Q352" t="s">
         <v>973</v>
       </c>
-      <c r="Q352" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="353" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>710</v>
       </c>
@@ -12155,10 +12154,10 @@
         <v>711</v>
       </c>
       <c r="J353" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="K353" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="M353">
         <v>0</v>
@@ -12167,13 +12166,13 @@
         <v>1</v>
       </c>
       <c r="O353" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="P353" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="Q353" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="354" spans="1:19" x14ac:dyDescent="0.35">
@@ -12197,10 +12196,10 @@
         <v>717</v>
       </c>
       <c r="J354" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="R354" s="3" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="S354">
         <v>2</v>
@@ -12208,7 +12207,7 @@
     </row>
     <row r="355" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B355" t="s">
         <v>716</v>
@@ -12227,26 +12226,17 @@
         <v>717</v>
       </c>
       <c r="J355" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="R355" s="3" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="S355">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T355" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="沃玛套装"/>
-        <filter val="沃玛战斧"/>
-        <filter val="沃玛战甲"/>
-        <filter val="沃玛手镯"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A4:T355" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="3" priority="17"/>

--- a/configs/Item.xlsx
+++ b/configs/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3F0DD3-4E48-47BB-85E0-C4B3C4730908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DB7AA1-79C4-4C3B-9697-8F67B1F16D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="13710" windowHeight="20970" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="993">
   <si>
     <t>id</t>
   </si>
@@ -2377,75 +2377,6 @@
     <t>最大品质</t>
   </si>
   <si>
-    <t>xlr1,0</t>
-  </si>
-  <si>
-    <t>hlr1,0</t>
-  </si>
-  <si>
-    <t>tlr1,0</t>
-  </si>
-  <si>
-    <t>flr1,0</t>
-  </si>
-  <si>
-    <t>plr1,0</t>
-  </si>
-  <si>
-    <t>hdmg1,0</t>
-  </si>
-  <si>
-    <t>tdmg1,0</t>
-  </si>
-  <si>
-    <t>fdmg1,0</t>
-  </si>
-  <si>
-    <t>pdmg1,0</t>
-  </si>
-  <si>
-    <t>hdr1,0</t>
-  </si>
-  <si>
-    <t>tdr1,0</t>
-  </si>
-  <si>
-    <t>fdr1,0</t>
-  </si>
-  <si>
-    <t>pdr1,0</t>
-  </si>
-  <si>
-    <t>xed1,0</t>
-  </si>
-  <si>
-    <t>hed1,0</t>
-  </si>
-  <si>
-    <t>ted1,0</t>
-  </si>
-  <si>
-    <t>fed1,0</t>
-  </si>
-  <si>
-    <t>ped1,0</t>
-  </si>
-  <si>
-    <t>xres1,0</t>
-  </si>
-  <si>
-    <t>hres1,0</t>
-  </si>
-  <si>
-    <t>tres1,0</t>
-  </si>
-  <si>
-    <t>fres1,0</t>
-  </si>
-  <si>
-    <t>pres1,0</t>
-  </si>
-  <si>
     <t>INV_Elemental_Mote_Nether</t>
   </si>
   <si>
@@ -3039,6 +2970,81 @@
   </si>
   <si>
     <t>xdmglo1,0.5:curs1,0</t>
+  </si>
+  <si>
+    <t>xdmgs,-0.9</t>
+  </si>
+  <si>
+    <t>hdmgs,-0.9</t>
+  </si>
+  <si>
+    <t>tdmgs,-0.9</t>
+  </si>
+  <si>
+    <t>fdmgs,-0.9</t>
+  </si>
+  <si>
+    <t>pdmgs,-0.9</t>
+  </si>
+  <si>
+    <t>xdrs,-0.7</t>
+  </si>
+  <si>
+    <t>hdrs,-0.7</t>
+  </si>
+  <si>
+    <t>tdrs,-0.7</t>
+  </si>
+  <si>
+    <t>fdrs,-0.7</t>
+  </si>
+  <si>
+    <t>pdrs,-0.7</t>
+  </si>
+  <si>
+    <t>xeds,1</t>
+  </si>
+  <si>
+    <t>heds,1</t>
+  </si>
+  <si>
+    <t>teds,1</t>
+  </si>
+  <si>
+    <t>feds,1</t>
+  </si>
+  <si>
+    <t>peds,1</t>
+  </si>
+  <si>
+    <t>xress,-0.3</t>
+  </si>
+  <si>
+    <t>hress,-0.3</t>
+  </si>
+  <si>
+    <t>tress,-0.3</t>
+  </si>
+  <si>
+    <t>fress,-0.3</t>
+  </si>
+  <si>
+    <t>press,-0.3</t>
+  </si>
+  <si>
+    <t>xlrs,0</t>
+  </si>
+  <si>
+    <t>hlrs,0</t>
+  </si>
+  <si>
+    <t>tlrs,0</t>
+  </si>
+  <si>
+    <t>flrs,0</t>
+  </si>
+  <si>
+    <t>plrs,0</t>
   </si>
 </sst>
 </file>
@@ -3542,10 +3548,10 @@
         <v>669</v>
       </c>
       <c r="M1" t="s">
-        <v>855</v>
+        <v>832</v>
       </c>
       <c r="N1" t="s">
-        <v>989</v>
+        <v>966</v>
       </c>
       <c r="O1" t="s">
         <v>677</v>
@@ -3554,16 +3560,16 @@
         <v>712</v>
       </c>
       <c r="Q1" t="s">
-        <v>849</v>
+        <v>826</v>
       </c>
       <c r="R1" t="s">
-        <v>978</v>
+        <v>955</v>
       </c>
       <c r="S1" t="s">
         <v>718</v>
       </c>
       <c r="T1" t="s">
-        <v>839</v>
+        <v>816</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
@@ -3616,16 +3622,16 @@
         <v>713</v>
       </c>
       <c r="Q2" t="s">
-        <v>850</v>
+        <v>827</v>
       </c>
       <c r="R2" t="s">
-        <v>979</v>
+        <v>956</v>
       </c>
       <c r="S2" t="s">
         <v>5</v>
       </c>
       <c r="T2" t="s">
-        <v>863</v>
+        <v>840</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
@@ -3633,7 +3639,7 @@
         <v>44</v>
       </c>
       <c r="I3" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
@@ -3674,10 +3680,10 @@
         <v>671</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>856</v>
+        <v>833</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>856</v>
+        <v>833</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>678</v>
@@ -3686,16 +3692,16 @@
         <v>714</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>980</v>
+        <v>957</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>719</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.35">
@@ -3718,7 +3724,7 @@
         <v>108</v>
       </c>
       <c r="H5" t="s">
-        <v>826</v>
+        <v>803</v>
       </c>
       <c r="I5" t="s">
         <v>40</v>
@@ -3730,7 +3736,7 @@
         <v>735</v>
       </c>
       <c r="T5" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
@@ -3750,7 +3756,7 @@
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>827</v>
+        <v>804</v>
       </c>
       <c r="I6" t="s">
         <v>40</v>
@@ -3759,7 +3765,7 @@
         <v>722</v>
       </c>
       <c r="T6" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
@@ -3779,7 +3785,7 @@
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>828</v>
+        <v>805</v>
       </c>
       <c r="I7" t="s">
         <v>40</v>
@@ -3791,7 +3797,7 @@
         <v>735</v>
       </c>
       <c r="T7" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
@@ -3811,7 +3817,7 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>829</v>
+        <v>806</v>
       </c>
       <c r="I8" t="s">
         <v>40</v>
@@ -3820,7 +3826,7 @@
         <v>724</v>
       </c>
       <c r="T8" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.35">
@@ -3840,7 +3846,7 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>830</v>
+        <v>807</v>
       </c>
       <c r="I9" t="s">
         <v>40</v>
@@ -3852,7 +3858,7 @@
         <v>735</v>
       </c>
       <c r="T9" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.35">
@@ -3872,7 +3878,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>831</v>
+        <v>808</v>
       </c>
       <c r="I10" t="s">
         <v>40</v>
@@ -3881,7 +3887,7 @@
         <v>730</v>
       </c>
       <c r="T10" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
@@ -3901,7 +3907,7 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>832</v>
+        <v>809</v>
       </c>
       <c r="I11" t="s">
         <v>40</v>
@@ -3910,7 +3916,7 @@
         <v>663</v>
       </c>
       <c r="T11" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
@@ -3930,7 +3936,7 @@
         <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>833</v>
+        <v>810</v>
       </c>
       <c r="I12" t="s">
         <v>40</v>
@@ -3939,7 +3945,7 @@
         <v>665</v>
       </c>
       <c r="T12" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
@@ -4304,10 +4310,10 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>982</v>
+        <v>959</v>
       </c>
       <c r="B25" t="s">
-        <v>983</v>
+        <v>960</v>
       </c>
       <c r="C25">
         <v>11</v>
@@ -4316,7 +4322,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="s">
-        <v>986</v>
+        <v>963</v>
       </c>
       <c r="I25" t="s">
         <v>40</v>
@@ -4329,7 +4335,7 @@
         <v>4</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>981</v>
+        <v>958</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.35">
@@ -4482,7 +4488,7 @@
         <v>235</v>
       </c>
       <c r="T32" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.35">
@@ -4509,7 +4515,7 @@
         <v>235</v>
       </c>
       <c r="T33" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.35">
@@ -4536,7 +4542,7 @@
         <v>235</v>
       </c>
       <c r="T34" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.35">
@@ -4563,7 +4569,7 @@
         <v>235</v>
       </c>
       <c r="T35" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.35">
@@ -4590,7 +4596,7 @@
         <v>235</v>
       </c>
       <c r="T36" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.35">
@@ -4617,7 +4623,7 @@
         <v>235</v>
       </c>
       <c r="T37" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.35">
@@ -4644,7 +4650,7 @@
         <v>235</v>
       </c>
       <c r="T38" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.35">
@@ -5073,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="T58" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.35">
@@ -5100,7 +5106,7 @@
         <v>261</v>
       </c>
       <c r="T59" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.35">
@@ -5127,7 +5133,7 @@
         <v>261</v>
       </c>
       <c r="T60" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.35">
@@ -5154,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="T61" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.35">
@@ -5181,7 +5187,7 @@
         <v>261</v>
       </c>
       <c r="T62" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.35">
@@ -5208,7 +5214,7 @@
         <v>261</v>
       </c>
       <c r="T63" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.35">
@@ -5235,7 +5241,7 @@
         <v>261</v>
       </c>
       <c r="T64" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
@@ -5657,10 +5663,10 @@
         <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>836</v>
+        <v>813</v>
       </c>
       <c r="I84" t="s">
-        <v>939</v>
+        <v>916</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.35">
@@ -5680,10 +5686,10 @@
         <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>837</v>
+        <v>814</v>
       </c>
       <c r="I85" t="s">
-        <v>940</v>
+        <v>917</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.35">
@@ -5703,10 +5709,10 @@
         <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>838</v>
+        <v>815</v>
       </c>
       <c r="I86" t="s">
-        <v>941</v>
+        <v>918</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.35">
@@ -5733,7 +5739,7 @@
         <v>234</v>
       </c>
       <c r="T87" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.35">
@@ -5760,7 +5766,7 @@
         <v>234</v>
       </c>
       <c r="T88" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.35">
@@ -5787,7 +5793,7 @@
         <v>234</v>
       </c>
       <c r="T89" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.35">
@@ -5814,7 +5820,7 @@
         <v>234</v>
       </c>
       <c r="T90" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.35">
@@ -5841,7 +5847,7 @@
         <v>234</v>
       </c>
       <c r="T91" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.35">
@@ -5868,7 +5874,7 @@
         <v>234</v>
       </c>
       <c r="T92" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.35">
@@ -5895,7 +5901,7 @@
         <v>234</v>
       </c>
       <c r="T93" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.35">
@@ -6321,7 +6327,7 @@
         <v>160</v>
       </c>
       <c r="T113" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="114" spans="1:20" x14ac:dyDescent="0.35">
@@ -6348,7 +6354,7 @@
         <v>160</v>
       </c>
       <c r="T114" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="115" spans="1:20" x14ac:dyDescent="0.35">
@@ -6375,7 +6381,7 @@
         <v>160</v>
       </c>
       <c r="T115" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="116" spans="1:20" x14ac:dyDescent="0.35">
@@ -6405,7 +6411,7 @@
         <v>721</v>
       </c>
       <c r="T116" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="117" spans="1:20" x14ac:dyDescent="0.35">
@@ -6432,7 +6438,7 @@
         <v>160</v>
       </c>
       <c r="T117" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="118" spans="1:20" x14ac:dyDescent="0.35">
@@ -6459,7 +6465,7 @@
         <v>160</v>
       </c>
       <c r="T118" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.35">
@@ -6486,7 +6492,7 @@
         <v>160</v>
       </c>
       <c r="T119" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="120" spans="1:20" x14ac:dyDescent="0.35">
@@ -6950,13 +6956,13 @@
         <v>2</v>
       </c>
       <c r="H139" t="s">
-        <v>834</v>
+        <v>811</v>
       </c>
       <c r="I139" t="s">
         <v>258</v>
       </c>
       <c r="T139" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
     </row>
     <row r="140" spans="1:20" x14ac:dyDescent="0.35">
@@ -7598,7 +7604,7 @@
         <v>260</v>
       </c>
       <c r="T166" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="167" spans="1:20" x14ac:dyDescent="0.35">
@@ -7625,7 +7631,7 @@
         <v>260</v>
       </c>
       <c r="T167" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.35">
@@ -7652,7 +7658,7 @@
         <v>260</v>
       </c>
       <c r="T168" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.35">
@@ -7679,7 +7685,7 @@
         <v>260</v>
       </c>
       <c r="T169" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="170" spans="1:20" x14ac:dyDescent="0.35">
@@ -7706,7 +7712,7 @@
         <v>260</v>
       </c>
       <c r="T170" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="171" spans="1:20" x14ac:dyDescent="0.35">
@@ -7733,7 +7739,7 @@
         <v>260</v>
       </c>
       <c r="T171" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="172" spans="1:20" x14ac:dyDescent="0.35">
@@ -7760,7 +7766,7 @@
         <v>260</v>
       </c>
       <c r="T172" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="173" spans="1:20" x14ac:dyDescent="0.35">
@@ -8186,7 +8192,7 @@
         <v>259</v>
       </c>
       <c r="T192" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="193" spans="1:20" x14ac:dyDescent="0.35">
@@ -8213,7 +8219,7 @@
         <v>259</v>
       </c>
       <c r="T193" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="194" spans="1:20" x14ac:dyDescent="0.35">
@@ -8240,7 +8246,7 @@
         <v>259</v>
       </c>
       <c r="T194" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="195" spans="1:20" x14ac:dyDescent="0.35">
@@ -8267,7 +8273,7 @@
         <v>259</v>
       </c>
       <c r="T195" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="196" spans="1:20" x14ac:dyDescent="0.35">
@@ -8294,7 +8300,7 @@
         <v>259</v>
       </c>
       <c r="T196" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.35">
@@ -8321,7 +8327,7 @@
         <v>259</v>
       </c>
       <c r="T197" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="198" spans="1:20" x14ac:dyDescent="0.35">
@@ -8348,7 +8354,7 @@
         <v>259</v>
       </c>
       <c r="T198" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="199" spans="1:20" x14ac:dyDescent="0.35">
@@ -8767,13 +8773,13 @@
         <v>2</v>
       </c>
       <c r="H218" t="s">
-        <v>835</v>
+        <v>812</v>
       </c>
       <c r="I218" t="s">
         <v>209</v>
       </c>
       <c r="T218" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
     </row>
     <row r="219" spans="1:20" x14ac:dyDescent="0.35">
@@ -9342,16 +9348,16 @@
         <v>58</v>
       </c>
       <c r="H245" t="s">
-        <v>865</v>
+        <v>842</v>
       </c>
       <c r="I245" t="s">
-        <v>898</v>
+        <v>875</v>
       </c>
       <c r="J245" t="s">
         <v>748</v>
       </c>
       <c r="T245" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="246" spans="1:20" x14ac:dyDescent="0.35">
@@ -9374,16 +9380,16 @@
         <v>64</v>
       </c>
       <c r="H246" t="s">
-        <v>868</v>
+        <v>845</v>
       </c>
       <c r="I246" t="s">
-        <v>898</v>
+        <v>875</v>
       </c>
       <c r="J246" t="s">
-        <v>904</v>
+        <v>881</v>
       </c>
       <c r="T246" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="247" spans="1:20" x14ac:dyDescent="0.35">
@@ -9406,27 +9412,27 @@
         <v>62</v>
       </c>
       <c r="H247" t="s">
-        <v>867</v>
+        <v>844</v>
       </c>
       <c r="I247" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
       <c r="J247" t="s">
-        <v>904</v>
+        <v>881</v>
       </c>
       <c r="K247" t="s">
         <v>754</v>
       </c>
       <c r="T247" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
     </row>
     <row r="248" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>908</v>
+        <v>885</v>
       </c>
       <c r="B248" t="s">
-        <v>909</v>
+        <v>886</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9438,16 +9444,16 @@
         <v>2</v>
       </c>
       <c r="H248" t="s">
-        <v>869</v>
+        <v>846</v>
       </c>
       <c r="I248" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
       <c r="J248" t="s">
         <v>749</v>
       </c>
       <c r="T248" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
     </row>
     <row r="249" spans="1:20" x14ac:dyDescent="0.35">
@@ -9455,7 +9461,7 @@
         <v>10</v>
       </c>
       <c r="B249" t="s">
-        <v>901</v>
+        <v>878</v>
       </c>
       <c r="C249">
         <v>10</v>
@@ -9470,16 +9476,16 @@
         <v>65</v>
       </c>
       <c r="H249" t="s">
-        <v>870</v>
+        <v>847</v>
       </c>
       <c r="I249" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
       <c r="J249" t="s">
         <v>749</v>
       </c>
       <c r="T249" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="250" spans="1:20" x14ac:dyDescent="0.35">
@@ -9487,7 +9493,7 @@
         <v>11</v>
       </c>
       <c r="B250" t="s">
-        <v>864</v>
+        <v>841</v>
       </c>
       <c r="C250">
         <v>10</v>
@@ -9502,24 +9508,24 @@
         <v>66</v>
       </c>
       <c r="H250" t="s">
-        <v>947</v>
+        <v>924</v>
       </c>
       <c r="I250" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
       <c r="J250" t="s">
         <v>750</v>
       </c>
       <c r="T250" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="251" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>912</v>
+        <v>889</v>
       </c>
       <c r="B251" t="s">
-        <v>913</v>
+        <v>890</v>
       </c>
       <c r="C251">
         <v>10</v>
@@ -9531,24 +9537,24 @@
         <v>2</v>
       </c>
       <c r="H251" t="s">
-        <v>948</v>
+        <v>925</v>
       </c>
       <c r="I251" t="s">
-        <v>916</v>
+        <v>893</v>
       </c>
       <c r="J251" t="s">
         <v>750</v>
       </c>
       <c r="T251" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
     </row>
     <row r="252" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>914</v>
+        <v>891</v>
       </c>
       <c r="B252" t="s">
-        <v>915</v>
+        <v>892</v>
       </c>
       <c r="C252">
         <v>10</v>
@@ -9560,16 +9566,16 @@
         <v>2</v>
       </c>
       <c r="H252" t="s">
-        <v>949</v>
+        <v>926</v>
       </c>
       <c r="I252" t="s">
-        <v>916</v>
+        <v>893</v>
       </c>
       <c r="J252" t="s">
         <v>750</v>
       </c>
       <c r="T252" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
     </row>
     <row r="253" spans="1:20" x14ac:dyDescent="0.35">
@@ -9592,7 +9598,7 @@
         <v>60</v>
       </c>
       <c r="H253" t="s">
-        <v>866</v>
+        <v>843</v>
       </c>
       <c r="I253" t="s">
         <v>7</v>
@@ -9601,15 +9607,15 @@
         <v>753</v>
       </c>
       <c r="T253" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="254" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>905</v>
+        <v>882</v>
       </c>
       <c r="B254" t="s">
-        <v>906</v>
+        <v>883</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9621,24 +9627,24 @@
         <v>2</v>
       </c>
       <c r="H254" t="s">
-        <v>950</v>
+        <v>927</v>
       </c>
       <c r="I254" t="s">
         <v>7</v>
       </c>
       <c r="J254" t="s">
-        <v>907</v>
+        <v>884</v>
       </c>
       <c r="T254" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="255" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>910</v>
+        <v>887</v>
       </c>
       <c r="B255" t="s">
-        <v>911</v>
+        <v>888</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9650,16 +9656,16 @@
         <v>2</v>
       </c>
       <c r="H255" t="s">
-        <v>951</v>
+        <v>928</v>
       </c>
       <c r="I255" t="s">
-        <v>899</v>
+        <v>876</v>
       </c>
       <c r="J255" t="s">
         <v>749</v>
       </c>
       <c r="T255" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="256" spans="1:20" x14ac:dyDescent="0.35">
@@ -9682,24 +9688,24 @@
         <v>70</v>
       </c>
       <c r="H256" t="s">
-        <v>871</v>
+        <v>848</v>
       </c>
       <c r="I256" t="s">
-        <v>899</v>
+        <v>876</v>
       </c>
       <c r="J256" t="s">
         <v>751</v>
       </c>
       <c r="T256" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="257" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>917</v>
+        <v>894</v>
       </c>
       <c r="B257" t="s">
-        <v>919</v>
+        <v>896</v>
       </c>
       <c r="C257">
         <v>11</v>
@@ -9711,24 +9717,24 @@
         <v>2</v>
       </c>
       <c r="H257" t="s">
-        <v>952</v>
+        <v>929</v>
       </c>
       <c r="I257" t="s">
-        <v>900</v>
+        <v>877</v>
       </c>
       <c r="J257" t="s">
         <v>751</v>
       </c>
       <c r="T257" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
     </row>
     <row r="258" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>918</v>
+        <v>895</v>
       </c>
       <c r="B258" t="s">
-        <v>920</v>
+        <v>897</v>
       </c>
       <c r="C258">
         <v>11</v>
@@ -9740,24 +9746,24 @@
         <v>2</v>
       </c>
       <c r="H258" t="s">
-        <v>953</v>
+        <v>930</v>
       </c>
       <c r="I258" t="s">
-        <v>900</v>
+        <v>877</v>
       </c>
       <c r="J258" t="s">
         <v>751</v>
       </c>
       <c r="T258" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
     </row>
     <row r="259" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>921</v>
+        <v>898</v>
       </c>
       <c r="B259" t="s">
-        <v>925</v>
+        <v>902</v>
       </c>
       <c r="C259">
         <v>11</v>
@@ -9769,24 +9775,24 @@
         <v>2</v>
       </c>
       <c r="H259" t="s">
-        <v>954</v>
+        <v>931</v>
       </c>
       <c r="I259" t="s">
-        <v>922</v>
+        <v>899</v>
       </c>
       <c r="J259" t="s">
         <v>751</v>
       </c>
       <c r="T259" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="260" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>922</v>
+        <v>899</v>
       </c>
       <c r="B260" t="s">
-        <v>926</v>
+        <v>903</v>
       </c>
       <c r="C260">
         <v>11</v>
@@ -9798,24 +9804,24 @@
         <v>2</v>
       </c>
       <c r="H260" t="s">
-        <v>956</v>
+        <v>933</v>
       </c>
       <c r="I260" t="s">
-        <v>922</v>
+        <v>899</v>
       </c>
       <c r="J260" t="s">
         <v>751</v>
       </c>
       <c r="T260" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="261" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>923</v>
+        <v>900</v>
       </c>
       <c r="B261" t="s">
-        <v>927</v>
+        <v>904</v>
       </c>
       <c r="C261">
         <v>11</v>
@@ -9827,24 +9833,24 @@
         <v>2</v>
       </c>
       <c r="H261" t="s">
-        <v>955</v>
+        <v>932</v>
       </c>
       <c r="I261" t="s">
-        <v>929</v>
+        <v>906</v>
       </c>
       <c r="J261" t="s">
         <v>751</v>
       </c>
       <c r="T261" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
     </row>
     <row r="262" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>924</v>
+        <v>901</v>
       </c>
       <c r="B262" t="s">
-        <v>928</v>
+        <v>905</v>
       </c>
       <c r="C262">
         <v>11</v>
@@ -9856,24 +9862,24 @@
         <v>2</v>
       </c>
       <c r="H262" t="s">
-        <v>957</v>
+        <v>934</v>
       </c>
       <c r="I262" t="s">
-        <v>929</v>
+        <v>906</v>
       </c>
       <c r="J262" t="s">
         <v>751</v>
       </c>
       <c r="T262" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
     </row>
     <row r="263" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>930</v>
+        <v>907</v>
       </c>
       <c r="B263" t="s">
-        <v>934</v>
+        <v>911</v>
       </c>
       <c r="C263">
         <v>11</v>
@@ -9885,24 +9891,24 @@
         <v>2</v>
       </c>
       <c r="H263" t="s">
-        <v>958</v>
+        <v>935</v>
       </c>
       <c r="I263" t="s">
-        <v>930</v>
+        <v>907</v>
       </c>
       <c r="J263" t="s">
         <v>751</v>
       </c>
       <c r="T263" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
     </row>
     <row r="264" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>931</v>
+        <v>908</v>
       </c>
       <c r="B264" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
       <c r="C264">
         <v>11</v>
@@ -9914,24 +9920,24 @@
         <v>2</v>
       </c>
       <c r="H264" t="s">
-        <v>959</v>
+        <v>936</v>
       </c>
       <c r="I264" t="s">
-        <v>930</v>
+        <v>907</v>
       </c>
       <c r="J264" t="s">
         <v>751</v>
       </c>
       <c r="T264" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
     </row>
     <row r="265" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>932</v>
+        <v>909</v>
       </c>
       <c r="B265" t="s">
-        <v>936</v>
+        <v>913</v>
       </c>
       <c r="C265">
         <v>11</v>
@@ -9943,24 +9949,24 @@
         <v>2</v>
       </c>
       <c r="H265" t="s">
-        <v>960</v>
+        <v>937</v>
       </c>
       <c r="I265" t="s">
-        <v>938</v>
+        <v>915</v>
       </c>
       <c r="J265" t="s">
         <v>751</v>
       </c>
       <c r="T265" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="266" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>933</v>
+        <v>910</v>
       </c>
       <c r="B266" t="s">
-        <v>937</v>
+        <v>914</v>
       </c>
       <c r="C266">
         <v>11</v>
@@ -9972,24 +9978,24 @@
         <v>2</v>
       </c>
       <c r="H266" t="s">
-        <v>961</v>
+        <v>938</v>
       </c>
       <c r="I266" t="s">
-        <v>938</v>
+        <v>915</v>
       </c>
       <c r="J266" t="s">
         <v>751</v>
       </c>
       <c r="T266" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
     </row>
     <row r="267" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>942</v>
+        <v>919</v>
       </c>
       <c r="B267" t="s">
-        <v>944</v>
+        <v>921</v>
       </c>
       <c r="C267">
         <v>11</v>
@@ -10001,24 +10007,24 @@
         <v>2</v>
       </c>
       <c r="H267" t="s">
-        <v>962</v>
+        <v>939</v>
       </c>
       <c r="I267" t="s">
+        <v>923</v>
+      </c>
+      <c r="K267" t="s">
         <v>946</v>
       </c>
-      <c r="K267" t="s">
-        <v>969</v>
-      </c>
       <c r="T267" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="268" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>943</v>
+        <v>920</v>
       </c>
       <c r="B268" t="s">
-        <v>945</v>
+        <v>922</v>
       </c>
       <c r="C268">
         <v>11</v>
@@ -10030,16 +10036,16 @@
         <v>2</v>
       </c>
       <c r="H268" t="s">
-        <v>963</v>
+        <v>940</v>
       </c>
       <c r="I268" t="s">
+        <v>923</v>
+      </c>
+      <c r="K268" t="s">
         <v>946</v>
       </c>
-      <c r="K268" t="s">
-        <v>969</v>
-      </c>
       <c r="T268" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="269" spans="1:20" x14ac:dyDescent="0.35">
@@ -10059,10 +10065,10 @@
         <v>68</v>
       </c>
       <c r="H269" t="s">
-        <v>964</v>
+        <v>941</v>
       </c>
       <c r="I269" t="s">
-        <v>899</v>
+        <v>876</v>
       </c>
       <c r="J269" t="s">
         <v>767</v>
@@ -10085,13 +10091,13 @@
         <v>72</v>
       </c>
       <c r="H270" t="s">
-        <v>843</v>
+        <v>820</v>
       </c>
       <c r="I270" t="s">
-        <v>900</v>
+        <v>877</v>
       </c>
       <c r="J270" t="s">
-        <v>990</v>
+        <v>967</v>
       </c>
     </row>
     <row r="271" spans="1:20" x14ac:dyDescent="0.35">
@@ -10114,10 +10120,10 @@
         <v>74</v>
       </c>
       <c r="H271" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="I271" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
       <c r="J271" t="s">
         <v>766</v>
@@ -10143,10 +10149,10 @@
         <v>76</v>
       </c>
       <c r="H272" t="s">
-        <v>841</v>
+        <v>818</v>
       </c>
       <c r="I272" t="s">
-        <v>916</v>
+        <v>893</v>
       </c>
       <c r="J272" t="s">
         <v>765</v>
@@ -10172,10 +10178,10 @@
         <v>77</v>
       </c>
       <c r="H273" t="s">
-        <v>965</v>
+        <v>942</v>
       </c>
       <c r="I273" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
       <c r="J273" t="s">
         <v>764</v>
@@ -10201,10 +10207,10 @@
         <v>78</v>
       </c>
       <c r="H274" t="s">
-        <v>844</v>
+        <v>821</v>
       </c>
       <c r="I274" t="s">
-        <v>916</v>
+        <v>893</v>
       </c>
       <c r="J274" t="s">
         <v>676</v>
@@ -10230,10 +10236,10 @@
         <v>79</v>
       </c>
       <c r="H275" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="I275" t="s">
-        <v>899</v>
+        <v>876</v>
       </c>
       <c r="J275" t="s">
         <v>763</v>
@@ -10259,10 +10265,10 @@
         <v>80</v>
       </c>
       <c r="H276" t="s">
-        <v>846</v>
+        <v>823</v>
       </c>
       <c r="I276" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
       <c r="J276" t="s">
         <v>762</v>
@@ -10288,10 +10294,10 @@
         <v>81</v>
       </c>
       <c r="H277" t="s">
-        <v>966</v>
+        <v>943</v>
       </c>
       <c r="I277" t="s">
-        <v>900</v>
+        <v>877</v>
       </c>
       <c r="J277" t="s">
         <v>672</v>
@@ -10317,10 +10323,10 @@
         <v>82</v>
       </c>
       <c r="H278" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
       <c r="I278" t="s">
-        <v>916</v>
+        <v>893</v>
       </c>
       <c r="J278" t="s">
         <v>674</v>
@@ -10346,10 +10352,10 @@
         <v>84</v>
       </c>
       <c r="H279" t="s">
-        <v>967</v>
+        <v>944</v>
       </c>
       <c r="I279" t="s">
-        <v>929</v>
+        <v>906</v>
       </c>
       <c r="J279" t="s">
         <v>761</v>
@@ -10375,10 +10381,10 @@
         <v>86</v>
       </c>
       <c r="H280" t="s">
-        <v>845</v>
+        <v>822</v>
       </c>
       <c r="I280" t="s">
-        <v>916</v>
+        <v>893</v>
       </c>
       <c r="J280" t="s">
         <v>673</v>
@@ -10407,7 +10413,7 @@
         <v>39</v>
       </c>
       <c r="I281" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
       <c r="J281" t="s">
         <v>768</v>
@@ -10439,7 +10445,7 @@
         <v>39</v>
       </c>
       <c r="I282" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
       <c r="J282" t="s">
         <v>769</v>
@@ -10468,7 +10474,7 @@
         <v>39</v>
       </c>
       <c r="I283" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
       <c r="J283" t="s">
         <v>770</v>
@@ -10497,7 +10503,7 @@
         <v>39</v>
       </c>
       <c r="I284" t="s">
-        <v>930</v>
+        <v>907</v>
       </c>
       <c r="J284" t="s">
         <v>760</v>
@@ -10529,7 +10535,7 @@
         <v>39</v>
       </c>
       <c r="I285" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
       <c r="J285" t="s">
         <v>759</v>
@@ -10558,7 +10564,7 @@
         <v>39</v>
       </c>
       <c r="I286" t="s">
-        <v>938</v>
+        <v>915</v>
       </c>
       <c r="J286" t="s">
         <v>750</v>
@@ -10590,7 +10596,7 @@
         <v>39</v>
       </c>
       <c r="I287" t="s">
-        <v>938</v>
+        <v>915</v>
       </c>
       <c r="J287" t="s">
         <v>752</v>
@@ -10622,7 +10628,7 @@
         <v>39</v>
       </c>
       <c r="I288" t="s">
-        <v>930</v>
+        <v>907</v>
       </c>
       <c r="J288" t="s">
         <v>667</v>
@@ -10654,7 +10660,7 @@
         <v>39</v>
       </c>
       <c r="I289" t="s">
-        <v>898</v>
+        <v>875</v>
       </c>
       <c r="J289" t="s">
         <v>758</v>
@@ -10686,7 +10692,7 @@
         <v>39</v>
       </c>
       <c r="I290" t="s">
-        <v>930</v>
+        <v>907</v>
       </c>
       <c r="J290" t="s">
         <v>675</v>
@@ -10713,7 +10719,7 @@
         <v>虹</v>
       </c>
       <c r="I291" t="s">
-        <v>930</v>
+        <v>907</v>
       </c>
     </row>
     <row r="292" spans="1:20" x14ac:dyDescent="0.35">
@@ -10734,7 +10740,7 @@
         <v>神</v>
       </c>
       <c r="I292" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
     </row>
     <row r="293" spans="1:20" x14ac:dyDescent="0.35">
@@ -10755,7 +10761,7 @@
         <v>魔</v>
       </c>
       <c r="I293" t="s">
-        <v>946</v>
+        <v>923</v>
       </c>
     </row>
     <row r="294" spans="1:20" x14ac:dyDescent="0.35">
@@ -10776,7 +10782,7 @@
         <v>赤</v>
       </c>
       <c r="I294" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
     </row>
     <row r="295" spans="1:20" x14ac:dyDescent="0.35">
@@ -10800,7 +10806,7 @@
         <v>启</v>
       </c>
       <c r="I295" t="s">
-        <v>946</v>
+        <v>923</v>
       </c>
     </row>
     <row r="296" spans="1:20" x14ac:dyDescent="0.35">
@@ -10824,7 +10830,7 @@
         <v>怒</v>
       </c>
       <c r="I296" t="s">
-        <v>916</v>
+        <v>893</v>
       </c>
     </row>
     <row r="297" spans="1:20" x14ac:dyDescent="0.35">
@@ -10872,7 +10878,7 @@
         <v>逍</v>
       </c>
       <c r="I298" t="s">
-        <v>946</v>
+        <v>923</v>
       </c>
     </row>
     <row r="299" spans="1:20" x14ac:dyDescent="0.35">
@@ -10893,15 +10899,15 @@
         <v>卧</v>
       </c>
       <c r="I299" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
     </row>
     <row r="300" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>984</v>
+        <v>961</v>
       </c>
       <c r="B300" t="s">
-        <v>985</v>
+        <v>962</v>
       </c>
       <c r="C300">
         <v>11</v>
@@ -10910,10 +10916,10 @@
         <v>2</v>
       </c>
       <c r="H300" t="s">
-        <v>987</v>
+        <v>964</v>
       </c>
       <c r="I300" t="s">
-        <v>899</v>
+        <v>876</v>
       </c>
       <c r="J300" s="3" t="s">
         <v>748</v>
@@ -10925,7 +10931,7 @@
         <v>3</v>
       </c>
       <c r="R300" s="3" t="s">
-        <v>981</v>
+        <v>958</v>
       </c>
     </row>
     <row r="301" spans="1:20" x14ac:dyDescent="0.35">
@@ -10952,7 +10958,7 @@
         <v>682</v>
       </c>
       <c r="T301" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="302" spans="1:20" x14ac:dyDescent="0.35">
@@ -10979,7 +10985,7 @@
         <v>682</v>
       </c>
       <c r="T302" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="303" spans="1:20" x14ac:dyDescent="0.35">
@@ -11006,7 +11012,7 @@
         <v>682</v>
       </c>
       <c r="T303" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="304" spans="1:20" x14ac:dyDescent="0.35">
@@ -11033,7 +11039,7 @@
         <v>682</v>
       </c>
       <c r="T304" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="305" spans="1:20" x14ac:dyDescent="0.35">
@@ -11060,7 +11066,7 @@
         <v>682</v>
       </c>
       <c r="T305" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="306" spans="1:20" x14ac:dyDescent="0.35">
@@ -11087,7 +11093,7 @@
         <v>682</v>
       </c>
       <c r="T306" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="307" spans="1:20" x14ac:dyDescent="0.35">
@@ -11114,7 +11120,7 @@
         <v>682</v>
       </c>
       <c r="T307" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
     </row>
     <row r="308" spans="1:20" x14ac:dyDescent="0.35">
@@ -11131,7 +11137,7 @@
         <v>2</v>
       </c>
       <c r="H308" t="s">
-        <v>988</v>
+        <v>965</v>
       </c>
       <c r="I308" t="s">
         <v>682</v>
@@ -11144,7 +11150,7 @@
         <v>4</v>
       </c>
       <c r="R308" s="3" t="s">
-        <v>981</v>
+        <v>958</v>
       </c>
     </row>
     <row r="309" spans="1:20" x14ac:dyDescent="0.35">
@@ -11530,7 +11536,7 @@
         <v>683</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>880</v>
+        <v>857</v>
       </c>
       <c r="C327">
         <v>7</v>
@@ -11539,13 +11545,13 @@
         <v>0</v>
       </c>
       <c r="H327" t="s">
-        <v>801</v>
+        <v>778</v>
       </c>
       <c r="I327" t="s">
         <v>708</v>
       </c>
       <c r="J327" t="s">
-        <v>748</v>
+        <v>968</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.35">
@@ -11553,7 +11559,7 @@
         <v>684</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>884</v>
+        <v>861</v>
       </c>
       <c r="C328">
         <v>7</v>
@@ -11562,13 +11568,13 @@
         <v>0</v>
       </c>
       <c r="H328" t="s">
-        <v>802</v>
+        <v>779</v>
       </c>
       <c r="I328" t="s">
         <v>708</v>
       </c>
       <c r="J328" t="s">
-        <v>783</v>
+        <v>969</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.35">
@@ -11576,7 +11582,7 @@
         <v>685</v>
       </c>
       <c r="B329" t="s">
-        <v>889</v>
+        <v>866</v>
       </c>
       <c r="C329">
         <v>7</v>
@@ -11585,13 +11591,13 @@
         <v>0</v>
       </c>
       <c r="H329" t="s">
-        <v>803</v>
+        <v>780</v>
       </c>
       <c r="I329" t="s">
         <v>708</v>
       </c>
       <c r="J329" t="s">
-        <v>784</v>
+        <v>970</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.35">
@@ -11599,7 +11605,7 @@
         <v>686</v>
       </c>
       <c r="B330" t="s">
-        <v>873</v>
+        <v>850</v>
       </c>
       <c r="C330">
         <v>7</v>
@@ -11608,13 +11614,13 @@
         <v>0</v>
       </c>
       <c r="H330" t="s">
-        <v>804</v>
+        <v>781</v>
       </c>
       <c r="I330" t="s">
         <v>708</v>
       </c>
       <c r="J330" t="s">
-        <v>785</v>
+        <v>971</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.35">
@@ -11622,7 +11628,7 @@
         <v>687</v>
       </c>
       <c r="B331" t="s">
-        <v>874</v>
+        <v>851</v>
       </c>
       <c r="C331">
         <v>7</v>
@@ -11631,13 +11637,13 @@
         <v>0</v>
       </c>
       <c r="H331" t="s">
-        <v>805</v>
+        <v>782</v>
       </c>
       <c r="I331" t="s">
         <v>708</v>
       </c>
       <c r="J331" t="s">
-        <v>786</v>
+        <v>972</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.35">
@@ -11645,7 +11651,7 @@
         <v>688</v>
       </c>
       <c r="B332" t="s">
-        <v>875</v>
+        <v>852</v>
       </c>
       <c r="C332">
         <v>14</v>
@@ -11654,13 +11660,13 @@
         <v>1</v>
       </c>
       <c r="H332" t="s">
-        <v>806</v>
+        <v>783</v>
       </c>
       <c r="I332" t="s">
         <v>708</v>
       </c>
       <c r="J332" t="s">
-        <v>721</v>
+        <v>973</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.35">
@@ -11668,7 +11674,7 @@
         <v>689</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>885</v>
+        <v>862</v>
       </c>
       <c r="C333">
         <v>14</v>
@@ -11677,13 +11683,13 @@
         <v>1</v>
       </c>
       <c r="H333" t="s">
-        <v>807</v>
+        <v>784</v>
       </c>
       <c r="I333" t="s">
         <v>708</v>
       </c>
       <c r="J333" t="s">
-        <v>787</v>
+        <v>974</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.35">
@@ -11691,7 +11697,7 @@
         <v>690</v>
       </c>
       <c r="B334" t="s">
-        <v>876</v>
+        <v>853</v>
       </c>
       <c r="C334">
         <v>14</v>
@@ -11700,13 +11706,13 @@
         <v>1</v>
       </c>
       <c r="H334" t="s">
-        <v>808</v>
+        <v>785</v>
       </c>
       <c r="I334" t="s">
         <v>708</v>
       </c>
       <c r="J334" t="s">
-        <v>788</v>
+        <v>975</v>
       </c>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.35">
@@ -11714,7 +11720,7 @@
         <v>691</v>
       </c>
       <c r="B335" t="s">
-        <v>877</v>
+        <v>854</v>
       </c>
       <c r="C335">
         <v>14</v>
@@ -11723,13 +11729,13 @@
         <v>1</v>
       </c>
       <c r="H335" t="s">
-        <v>809</v>
+        <v>786</v>
       </c>
       <c r="I335" t="s">
         <v>708</v>
       </c>
       <c r="J335" t="s">
-        <v>789</v>
+        <v>976</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.35">
@@ -11737,7 +11743,7 @@
         <v>692</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>894</v>
+        <v>871</v>
       </c>
       <c r="C336">
         <v>14</v>
@@ -11746,13 +11752,13 @@
         <v>1</v>
       </c>
       <c r="H336" t="s">
-        <v>810</v>
+        <v>787</v>
       </c>
       <c r="I336" t="s">
         <v>708</v>
       </c>
       <c r="J336" t="s">
-        <v>790</v>
+        <v>977</v>
       </c>
     </row>
     <row r="337" spans="1:17" x14ac:dyDescent="0.35">
@@ -11760,7 +11766,7 @@
         <v>693</v>
       </c>
       <c r="B337" t="s">
-        <v>881</v>
+        <v>858</v>
       </c>
       <c r="C337">
         <v>21</v>
@@ -11769,13 +11775,13 @@
         <v>2</v>
       </c>
       <c r="H337" t="s">
-        <v>811</v>
+        <v>788</v>
       </c>
       <c r="I337" t="s">
         <v>708</v>
       </c>
       <c r="J337" t="s">
-        <v>791</v>
+        <v>978</v>
       </c>
     </row>
     <row r="338" spans="1:17" x14ac:dyDescent="0.35">
@@ -11783,7 +11789,7 @@
         <v>694</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>886</v>
+        <v>863</v>
       </c>
       <c r="C338">
         <v>21</v>
@@ -11792,13 +11798,13 @@
         <v>2</v>
       </c>
       <c r="H338" t="s">
-        <v>812</v>
+        <v>789</v>
       </c>
       <c r="I338" t="s">
         <v>708</v>
       </c>
       <c r="J338" t="s">
-        <v>792</v>
+        <v>979</v>
       </c>
     </row>
     <row r="339" spans="1:17" x14ac:dyDescent="0.35">
@@ -11806,7 +11812,7 @@
         <v>695</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>890</v>
+        <v>867</v>
       </c>
       <c r="C339">
         <v>21</v>
@@ -11815,13 +11821,13 @@
         <v>2</v>
       </c>
       <c r="H339" t="s">
-        <v>813</v>
+        <v>790</v>
       </c>
       <c r="I339" t="s">
         <v>708</v>
       </c>
       <c r="J339" t="s">
-        <v>793</v>
+        <v>980</v>
       </c>
     </row>
     <row r="340" spans="1:17" x14ac:dyDescent="0.35">
@@ -11829,7 +11835,7 @@
         <v>696</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>892</v>
+        <v>869</v>
       </c>
       <c r="C340">
         <v>21</v>
@@ -11838,13 +11844,13 @@
         <v>2</v>
       </c>
       <c r="H340" t="s">
-        <v>814</v>
+        <v>791</v>
       </c>
       <c r="I340" t="s">
         <v>708</v>
       </c>
       <c r="J340" t="s">
-        <v>794</v>
+        <v>981</v>
       </c>
     </row>
     <row r="341" spans="1:17" x14ac:dyDescent="0.35">
@@ -11852,7 +11858,7 @@
         <v>697</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>895</v>
+        <v>872</v>
       </c>
       <c r="C341">
         <v>21</v>
@@ -11861,13 +11867,13 @@
         <v>2</v>
       </c>
       <c r="H341" t="s">
-        <v>815</v>
+        <v>792</v>
       </c>
       <c r="I341" t="s">
         <v>708</v>
       </c>
       <c r="J341" t="s">
-        <v>795</v>
+        <v>982</v>
       </c>
     </row>
     <row r="342" spans="1:17" x14ac:dyDescent="0.35">
@@ -11875,7 +11881,7 @@
         <v>698</v>
       </c>
       <c r="B342" t="s">
-        <v>882</v>
+        <v>859</v>
       </c>
       <c r="C342">
         <v>28</v>
@@ -11884,13 +11890,13 @@
         <v>3</v>
       </c>
       <c r="H342" t="s">
-        <v>816</v>
+        <v>793</v>
       </c>
       <c r="I342" t="s">
         <v>708</v>
       </c>
       <c r="J342" t="s">
-        <v>796</v>
+        <v>983</v>
       </c>
     </row>
     <row r="343" spans="1:17" x14ac:dyDescent="0.35">
@@ -11898,7 +11904,7 @@
         <v>699</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>887</v>
+        <v>864</v>
       </c>
       <c r="C343">
         <v>28</v>
@@ -11907,13 +11913,13 @@
         <v>3</v>
       </c>
       <c r="H343" t="s">
-        <v>817</v>
+        <v>794</v>
       </c>
       <c r="I343" t="s">
         <v>708</v>
       </c>
       <c r="J343" t="s">
-        <v>797</v>
+        <v>984</v>
       </c>
     </row>
     <row r="344" spans="1:17" x14ac:dyDescent="0.35">
@@ -11921,7 +11927,7 @@
         <v>700</v>
       </c>
       <c r="B344" t="s">
-        <v>878</v>
+        <v>855</v>
       </c>
       <c r="C344">
         <v>28</v>
@@ -11930,13 +11936,13 @@
         <v>3</v>
       </c>
       <c r="H344" t="s">
-        <v>818</v>
+        <v>795</v>
       </c>
       <c r="I344" t="s">
         <v>708</v>
       </c>
       <c r="J344" t="s">
-        <v>798</v>
+        <v>985</v>
       </c>
     </row>
     <row r="345" spans="1:17" x14ac:dyDescent="0.35">
@@ -11944,7 +11950,7 @@
         <v>701</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>893</v>
+        <v>870</v>
       </c>
       <c r="C345">
         <v>28</v>
@@ -11953,13 +11959,13 @@
         <v>3</v>
       </c>
       <c r="H345" t="s">
-        <v>819</v>
+        <v>796</v>
       </c>
       <c r="I345" t="s">
         <v>708</v>
       </c>
       <c r="J345" t="s">
-        <v>799</v>
+        <v>986</v>
       </c>
     </row>
     <row r="346" spans="1:17" x14ac:dyDescent="0.35">
@@ -11967,7 +11973,7 @@
         <v>702</v>
       </c>
       <c r="B346" t="s">
-        <v>896</v>
+        <v>873</v>
       </c>
       <c r="C346">
         <v>28</v>
@@ -11976,13 +11982,13 @@
         <v>3</v>
       </c>
       <c r="H346" t="s">
-        <v>820</v>
+        <v>797</v>
       </c>
       <c r="I346" t="s">
         <v>708</v>
       </c>
       <c r="J346" t="s">
-        <v>800</v>
+        <v>987</v>
       </c>
     </row>
     <row r="347" spans="1:17" x14ac:dyDescent="0.35">
@@ -11990,7 +11996,7 @@
         <v>703</v>
       </c>
       <c r="B347" t="s">
-        <v>883</v>
+        <v>860</v>
       </c>
       <c r="C347">
         <v>35</v>
@@ -11999,13 +12005,13 @@
         <v>4</v>
       </c>
       <c r="H347" t="s">
-        <v>821</v>
+        <v>798</v>
       </c>
       <c r="I347" t="s">
         <v>708</v>
       </c>
       <c r="J347" t="s">
-        <v>778</v>
+        <v>988</v>
       </c>
     </row>
     <row r="348" spans="1:17" x14ac:dyDescent="0.35">
@@ -12013,7 +12019,7 @@
         <v>704</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>888</v>
+        <v>865</v>
       </c>
       <c r="C348">
         <v>35</v>
@@ -12022,13 +12028,13 @@
         <v>4</v>
       </c>
       <c r="H348" t="s">
-        <v>822</v>
+        <v>799</v>
       </c>
       <c r="I348" t="s">
         <v>708</v>
       </c>
       <c r="J348" t="s">
-        <v>779</v>
+        <v>989</v>
       </c>
     </row>
     <row r="349" spans="1:17" x14ac:dyDescent="0.35">
@@ -12036,7 +12042,7 @@
         <v>705</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>891</v>
+        <v>868</v>
       </c>
       <c r="C349">
         <v>35</v>
@@ -12045,13 +12051,13 @@
         <v>4</v>
       </c>
       <c r="H349" t="s">
-        <v>823</v>
+        <v>800</v>
       </c>
       <c r="I349" t="s">
         <v>708</v>
       </c>
       <c r="J349" t="s">
-        <v>780</v>
+        <v>990</v>
       </c>
     </row>
     <row r="350" spans="1:17" x14ac:dyDescent="0.35">
@@ -12059,7 +12065,7 @@
         <v>706</v>
       </c>
       <c r="B350" t="s">
-        <v>879</v>
+        <v>856</v>
       </c>
       <c r="C350">
         <v>35</v>
@@ -12068,13 +12074,13 @@
         <v>4</v>
       </c>
       <c r="H350" t="s">
-        <v>824</v>
+        <v>801</v>
       </c>
       <c r="I350" t="s">
         <v>708</v>
       </c>
       <c r="J350" t="s">
-        <v>781</v>
+        <v>991</v>
       </c>
     </row>
     <row r="351" spans="1:17" x14ac:dyDescent="0.35">
@@ -12082,7 +12088,7 @@
         <v>707</v>
       </c>
       <c r="B351" t="s">
-        <v>897</v>
+        <v>874</v>
       </c>
       <c r="C351">
         <v>35</v>
@@ -12091,21 +12097,21 @@
         <v>4</v>
       </c>
       <c r="H351" t="s">
-        <v>825</v>
+        <v>802</v>
       </c>
       <c r="I351" t="s">
         <v>708</v>
       </c>
       <c r="J351" t="s">
-        <v>782</v>
+        <v>992</v>
       </c>
     </row>
     <row r="352" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>970</v>
+        <v>947</v>
       </c>
       <c r="B352" t="s">
-        <v>971</v>
+        <v>948</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -12121,16 +12127,16 @@
         <v>711</v>
       </c>
       <c r="J352" t="s">
-        <v>974</v>
+        <v>951</v>
       </c>
       <c r="O352" t="s">
-        <v>872</v>
+        <v>849</v>
       </c>
       <c r="P352" t="s">
-        <v>972</v>
+        <v>949</v>
       </c>
       <c r="Q352" t="s">
-        <v>973</v>
+        <v>950</v>
       </c>
     </row>
     <row r="353" spans="1:19" x14ac:dyDescent="0.35">
@@ -12154,10 +12160,10 @@
         <v>711</v>
       </c>
       <c r="J353" t="s">
-        <v>854</v>
+        <v>831</v>
       </c>
       <c r="K353" t="s">
-        <v>853</v>
+        <v>830</v>
       </c>
       <c r="M353">
         <v>0</v>
@@ -12166,13 +12172,13 @@
         <v>1</v>
       </c>
       <c r="O353" t="s">
-        <v>872</v>
+        <v>849</v>
       </c>
       <c r="P353" t="s">
-        <v>968</v>
+        <v>945</v>
       </c>
       <c r="Q353" t="s">
-        <v>852</v>
+        <v>829</v>
       </c>
     </row>
     <row r="354" spans="1:19" x14ac:dyDescent="0.35">
@@ -12196,10 +12202,10 @@
         <v>717</v>
       </c>
       <c r="J354" t="s">
-        <v>976</v>
+        <v>953</v>
       </c>
       <c r="R354" s="3" t="s">
-        <v>981</v>
+        <v>958</v>
       </c>
       <c r="S354">
         <v>2</v>
@@ -12207,7 +12213,7 @@
     </row>
     <row r="355" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>975</v>
+        <v>952</v>
       </c>
       <c r="B355" t="s">
         <v>716</v>
@@ -12226,10 +12232,10 @@
         <v>717</v>
       </c>
       <c r="J355" t="s">
-        <v>977</v>
+        <v>954</v>
       </c>
       <c r="R355" s="3" t="s">
-        <v>981</v>
+        <v>958</v>
       </c>
       <c r="S355">
         <v>3</v>

--- a/configs/Item.xlsx
+++ b/configs/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DB7AA1-79C4-4C3B-9697-8F67B1F16D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68E130A-2688-43E3-98FD-EC77E0D51CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="13710" windowHeight="20970" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="1000">
   <si>
     <t>id</t>
   </si>
@@ -3045,6 +3045,27 @@
   </si>
   <si>
     <t>plrs,0</t>
+  </si>
+  <si>
+    <t>INV_Gauntlets_16</t>
+  </si>
+  <si>
+    <t>INV_Gauntlets_18</t>
+  </si>
+  <si>
+    <t>INV_Gauntlets_17</t>
+  </si>
+  <si>
+    <t>INV_Gauntlets_11</t>
+  </si>
+  <si>
+    <t>INV_Gauntlets_10</t>
+  </si>
+  <si>
+    <t>INV_Gauntlets_12</t>
+  </si>
+  <si>
+    <t>INV_Gauntlets_05</t>
   </si>
 </sst>
 </file>
@@ -3496,7 +3517,7 @@
     <col min="5" max="5" width="6.453125" customWidth="1"/>
     <col min="6" max="6" width="7.1796875" customWidth="1"/>
     <col min="7" max="7" width="11.26953125" customWidth="1"/>
-    <col min="8" max="8" width="9.81640625" customWidth="1"/>
+    <col min="8" max="8" width="22.08984375" customWidth="1"/>
     <col min="9" max="9" width="12.453125" customWidth="1"/>
     <col min="10" max="10" width="15.7265625" customWidth="1"/>
     <col min="11" max="11" width="15.1796875" customWidth="1"/>
@@ -5731,9 +5752,8 @@
       <c r="E87">
         <v>2</v>
       </c>
-      <c r="H87" t="str">
-        <f t="shared" ref="H87:H117" si="2">LEFT(B87,1)</f>
-        <v>布</v>
+      <c r="H87" t="s">
+        <v>993</v>
       </c>
       <c r="I87" t="s">
         <v>234</v>
@@ -5758,9 +5778,8 @@
       <c r="E88">
         <v>2</v>
       </c>
-      <c r="H88" t="str">
-        <f t="shared" si="2"/>
-        <v>皮</v>
+      <c r="H88" t="s">
+        <v>994</v>
       </c>
       <c r="I88" t="s">
         <v>234</v>
@@ -5785,9 +5804,8 @@
       <c r="E89">
         <v>2</v>
       </c>
-      <c r="H89" t="str">
-        <f t="shared" si="2"/>
-        <v>轻</v>
+      <c r="H89" t="s">
+        <v>995</v>
       </c>
       <c r="I89" t="s">
         <v>234</v>
@@ -5812,9 +5830,8 @@
       <c r="E90">
         <v>2</v>
       </c>
-      <c r="H90" t="str">
-        <f t="shared" si="2"/>
-        <v>青</v>
+      <c r="H90" t="s">
+        <v>996</v>
       </c>
       <c r="I90" t="s">
         <v>234</v>
@@ -5839,9 +5856,8 @@
       <c r="E91">
         <v>2</v>
       </c>
-      <c r="H91" t="str">
-        <f t="shared" si="2"/>
-        <v>中</v>
+      <c r="H91" t="s">
+        <v>999</v>
       </c>
       <c r="I91" t="s">
         <v>234</v>
@@ -5866,9 +5882,8 @@
       <c r="E92">
         <v>2</v>
       </c>
-      <c r="H92" t="str">
-        <f t="shared" si="2"/>
-        <v>铁</v>
+      <c r="H92" t="s">
+        <v>997</v>
       </c>
       <c r="I92" t="s">
         <v>234</v>
@@ -5893,9 +5908,8 @@
       <c r="E93">
         <v>2</v>
       </c>
-      <c r="H93" t="str">
-        <f t="shared" si="2"/>
-        <v>钢</v>
+      <c r="H93" t="s">
+        <v>998</v>
       </c>
       <c r="I93" t="s">
         <v>234</v>
@@ -5918,7 +5932,7 @@
         <v>3</v>
       </c>
       <c r="H94" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H87:H117" si="2">LEFT(B94,1)</f>
         <v>坚</v>
       </c>
       <c r="I94" t="s">

--- a/configs/Item.xlsx
+++ b/configs/Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7DC823-DD84-44A7-BE21-C2FD4E4EF727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6994EDC0-F448-47BA-9769-C8A6084C2876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="1031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="1040">
   <si>
     <t>id</t>
   </si>
@@ -2032,18 +2032,12 @@
     <t>xdr1,1</t>
   </si>
   <si>
-    <t>xdr1,1.5</t>
-  </si>
-  <si>
     <t>xdr1,1.7</t>
   </si>
   <si>
     <t>xdr1,2</t>
   </si>
   <si>
-    <t>xdr1,2.5</t>
-  </si>
-  <si>
     <t>xdmg1,1.2</t>
   </si>
   <si>
@@ -2203,9 +2197,6 @@
     <t>套装件数</t>
   </si>
   <si>
-    <t>xdr1,1.2:spi1,1</t>
-  </si>
-  <si>
     <t>xdr1,0</t>
   </si>
   <si>
@@ -2216,36 +2207,6 @@
   </si>
   <si>
     <t>xdr1,0.7</t>
-  </si>
-  <si>
-    <t>xdr1,0.2:spi1,1</t>
-  </si>
-  <si>
-    <t>xdr1,0.7:spi1,1</t>
-  </si>
-  <si>
-    <t>xdr1,0.2:int1,1</t>
-  </si>
-  <si>
-    <t>xdr1,0.5:int1,1</t>
-  </si>
-  <si>
-    <t>xdr1,0.7:int1,1</t>
-  </si>
-  <si>
-    <t>xdr1,1.1</t>
-  </si>
-  <si>
-    <t>xdr1,3:str1,1</t>
-  </si>
-  <si>
-    <t>xdr1,4</t>
-  </si>
-  <si>
-    <t>xdr1,1.8:spi1,1.5</t>
-  </si>
-  <si>
-    <t>xdr1,1:int1,1.5</t>
   </si>
   <si>
     <t>$res1,0/fthp/:</t>
@@ -2903,9 +2864,6 @@
     <t>INV_Mace_118</t>
   </si>
   <si>
-    <t>polearm,staff,dao2h</t>
-  </si>
-  <si>
     <t>$,0/int1,spi1/:</t>
   </si>
   <si>
@@ -2915,9 +2873,6 @@
     <t>钢铁</t>
   </si>
   <si>
-    <t>sword,sword2h,dao,dao2h,dagger,axe,axe2h,mace,mace2h,polearm</t>
-  </si>
-  <si>
     <t>rune2,rune1</t>
   </si>
   <si>
@@ -3159,6 +3114,78 @@
   </si>
   <si>
     <t>法器剑</t>
+  </si>
+  <si>
+    <t>sword,woodsword,sword2h,dao,katana,dao2h,dagger,axe,axe2h,mace,mace2h,polearm</t>
+  </si>
+  <si>
+    <t>polearm,staff,magestaff,dao2h</t>
+  </si>
+  <si>
+    <t>xdr1,-0.2</t>
+  </si>
+  <si>
+    <t>$dr1,-0.8/fthp/:</t>
+  </si>
+  <si>
+    <t>xdr1,-0.2:spi1,-0.8</t>
+  </si>
+  <si>
+    <t>xdr1,-0.4:spi1,-0.6</t>
+  </si>
+  <si>
+    <t>$dr1,-0.6/fthp/:</t>
+  </si>
+  <si>
+    <t>xdr1,0.4</t>
+  </si>
+  <si>
+    <t>xdr1,0.6</t>
+  </si>
+  <si>
+    <t>$dr1,-0.9/fthp/:</t>
+  </si>
+  <si>
+    <t>xdr1,0.6:str1,-0.6</t>
+  </si>
+  <si>
+    <t>xdr1,0.2:spi1,-0.6</t>
+  </si>
+  <si>
+    <t>xdr1,0.1:spi1,-0.5</t>
+  </si>
+  <si>
+    <t>xdr1,0:spi1,0</t>
+  </si>
+  <si>
+    <t>xdr1,0.2:spi1,-0.2</t>
+  </si>
+  <si>
+    <t>xdr1,0.2:int1,-0.6</t>
+  </si>
+  <si>
+    <t>xdr1,0.1:int1,-.05</t>
+  </si>
+  <si>
+    <t>xdr1,0:int1,0</t>
+  </si>
+  <si>
+    <t>xdr1,-0.2:int1,0.2</t>
+  </si>
+  <si>
+    <t>xdr1,0.8</t>
+  </si>
+  <si>
+    <t>$dr1,0.8/fthp/:</t>
+  </si>
+  <si>
+    <t>$dr1,0.4/fthp/:</t>
+  </si>
+  <si>
+    <t>$dr1,0.4/fth/:</t>
+  </si>
+  <si>
+    <t>xdr1,-0.5:pdr1,1.1</t>
   </si>
 </sst>
 </file>
@@ -3229,7 +3256,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3600,7 +3637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
-  <dimension ref="A1:T367"/>
+  <dimension ref="A1:U367"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
@@ -3612,7 +3649,7 @@
     <col min="7" max="7" width="11.28515625" customWidth="1"/>
     <col min="8" max="8" width="22.140625" customWidth="1"/>
     <col min="9" max="9" width="12.42578125" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" customWidth="1"/>
     <col min="11" max="11" width="15.140625" customWidth="1"/>
     <col min="12" max="12" width="8.42578125" customWidth="1"/>
     <col min="13" max="13" width="9.42578125" customWidth="1"/>
@@ -3624,7 +3661,7 @@
     <col min="19" max="19" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3638,7 +3675,7 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="F1" t="s">
         <v>36</v>
@@ -3656,39 +3693,39 @@
         <v>658</v>
       </c>
       <c r="K1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="L1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="M1" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="N1" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
       <c r="O1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="P1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="Q1" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="R1" t="s">
-        <v>955</v>
+        <v>940</v>
       </c>
       <c r="S1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="T1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -3733,30 +3770,30 @@
         <v>659</v>
       </c>
       <c r="P2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="Q2" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="R2" t="s">
-        <v>956</v>
+        <v>941</v>
       </c>
       <c r="S2" t="s">
         <v>5</v>
       </c>
       <c r="T2" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>44</v>
       </c>
       <c r="I3" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>489</v>
       </c>
@@ -3770,7 +3807,7 @@
         <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>53</v>
@@ -3788,37 +3825,37 @@
         <v>661</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>957</v>
+        <v>942</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>48</v>
       </c>
@@ -3838,22 +3875,25 @@
         <v>108</v>
       </c>
       <c r="H5" t="s">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="I5" t="s">
         <v>40</v>
       </c>
       <c r="J5" t="s">
-        <v>721</v>
+        <v>1018</v>
       </c>
       <c r="K5" t="s">
-        <v>735</v>
+        <v>1019</v>
       </c>
       <c r="T5" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -3870,24 +3910,27 @@
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="I6" t="s">
         <v>40</v>
       </c>
       <c r="J6" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="T6" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1001</v>
+        <v>986</v>
       </c>
       <c r="B7" t="s">
-        <v>1029</v>
+        <v>1014</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -3902,24 +3945,27 @@
         <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="I7" t="s">
-        <v>1000</v>
+        <v>985</v>
       </c>
       <c r="J7" t="s">
-        <v>722</v>
+        <v>1020</v>
       </c>
       <c r="T7" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1003</v>
+        <v>988</v>
       </c>
       <c r="B8" t="s">
-        <v>1004</v>
+        <v>989</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -3934,19 +3980,22 @@
         <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="I8" t="s">
-        <v>1000</v>
+        <v>985</v>
       </c>
       <c r="J8" t="s">
-        <v>722</v>
+        <v>1021</v>
       </c>
       <c r="T8" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>109</v>
       </c>
@@ -3963,22 +4012,25 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="I9" t="s">
         <v>40</v>
       </c>
       <c r="J9" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="K9" t="s">
-        <v>735</v>
+        <v>1019</v>
       </c>
       <c r="T9" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+      <c r="U9">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>110</v>
       </c>
@@ -3995,19 +4047,22 @@
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>806</v>
+        <v>793</v>
       </c>
       <c r="I10" t="s">
         <v>40</v>
       </c>
       <c r="J10" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="T10" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+      <c r="U10">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>111</v>
       </c>
@@ -4024,22 +4079,25 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
       <c r="I11" t="s">
         <v>40</v>
       </c>
       <c r="J11" t="s">
-        <v>662</v>
+        <v>718</v>
       </c>
       <c r="K11" t="s">
-        <v>735</v>
+        <v>1022</v>
       </c>
       <c r="T11" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+      <c r="U11">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>112</v>
       </c>
@@ -4056,19 +4114,22 @@
         <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
       <c r="I12" t="s">
         <v>40</v>
       </c>
       <c r="J12" t="s">
-        <v>730</v>
+        <v>1023</v>
       </c>
       <c r="T12" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+      <c r="U12">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>113</v>
       </c>
@@ -4085,19 +4146,22 @@
         <v>2</v>
       </c>
       <c r="H13" t="s">
-        <v>809</v>
+        <v>796</v>
       </c>
       <c r="I13" t="s">
         <v>40</v>
       </c>
       <c r="J13" t="s">
-        <v>663</v>
+        <v>1024</v>
       </c>
       <c r="T13" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+      <c r="U13">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>157</v>
       </c>
@@ -4114,19 +4178,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="I14" t="s">
         <v>40</v>
       </c>
       <c r="J14" t="s">
-        <v>665</v>
+        <v>720</v>
+      </c>
+      <c r="K14" t="s">
+        <v>1025</v>
       </c>
       <c r="T14" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+        <v>822</v>
+      </c>
+      <c r="U14">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>119</v>
       </c>
@@ -4150,13 +4220,22 @@
         <v>40</v>
       </c>
       <c r="J15" t="s">
-        <v>663</v>
+        <v>1024</v>
       </c>
       <c r="K15" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+      <c r="M15">
+        <v>3</v>
+      </c>
+      <c r="N15">
+        <v>6</v>
+      </c>
+      <c r="U15">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>120</v>
       </c>
@@ -4180,13 +4259,22 @@
         <v>40</v>
       </c>
       <c r="J16" t="s">
-        <v>666</v>
+        <v>1024</v>
       </c>
       <c r="K16" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+      <c r="M16">
+        <v>3</v>
+      </c>
+      <c r="N16">
+        <v>6</v>
+      </c>
+      <c r="U16">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -4210,13 +4298,22 @@
         <v>40</v>
       </c>
       <c r="J17" t="s">
-        <v>731</v>
+        <v>1026</v>
       </c>
       <c r="K17" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+      <c r="M17">
+        <v>3</v>
+      </c>
+      <c r="N17">
+        <v>6</v>
+      </c>
+      <c r="U17">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>122</v>
       </c>
@@ -4240,13 +4337,22 @@
         <v>40</v>
       </c>
       <c r="J18" t="s">
-        <v>732</v>
+        <v>662</v>
       </c>
       <c r="K18" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+      <c r="M18">
+        <v>3</v>
+      </c>
+      <c r="N18">
+        <v>8</v>
+      </c>
+      <c r="U18">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>127</v>
       </c>
@@ -4267,16 +4373,25 @@
         <v>灵</v>
       </c>
       <c r="I19" t="s">
-        <v>1000</v>
+        <v>985</v>
       </c>
       <c r="J19" t="s">
-        <v>725</v>
+        <v>1027</v>
       </c>
       <c r="K19" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+      <c r="M19">
+        <v>3</v>
+      </c>
+      <c r="N19">
+        <v>6</v>
+      </c>
+      <c r="U19">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>128</v>
       </c>
@@ -4297,16 +4412,25 @@
         <v>幽</v>
       </c>
       <c r="I20" t="s">
-        <v>1000</v>
+        <v>985</v>
       </c>
       <c r="J20" t="s">
-        <v>726</v>
+        <v>1028</v>
       </c>
       <c r="K20" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+      <c r="M20">
+        <v>3</v>
+      </c>
+      <c r="N20">
+        <v>6</v>
+      </c>
+      <c r="U20">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>129</v>
       </c>
@@ -4327,16 +4451,25 @@
         <v>天</v>
       </c>
       <c r="I21" t="s">
-        <v>1000</v>
+        <v>985</v>
       </c>
       <c r="J21" t="s">
-        <v>720</v>
+        <v>1029</v>
       </c>
       <c r="K21" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+      <c r="M21">
+        <v>3</v>
+      </c>
+      <c r="N21">
+        <v>6</v>
+      </c>
+      <c r="U21">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>130</v>
       </c>
@@ -4357,16 +4490,25 @@
         <v>天</v>
       </c>
       <c r="I22" t="s">
-        <v>1000</v>
+        <v>985</v>
       </c>
       <c r="J22" t="s">
-        <v>733</v>
+        <v>1030</v>
       </c>
       <c r="K22" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+      <c r="M22">
+        <v>3</v>
+      </c>
+      <c r="N22">
+        <v>8</v>
+      </c>
+      <c r="U22">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>139</v>
       </c>
@@ -4390,13 +4532,22 @@
         <v>40</v>
       </c>
       <c r="J23" t="s">
-        <v>727</v>
+        <v>1031</v>
       </c>
       <c r="K23" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+      <c r="M23">
+        <v>3</v>
+      </c>
+      <c r="N23">
+        <v>6</v>
+      </c>
+      <c r="U23">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>140</v>
       </c>
@@ -4420,13 +4571,22 @@
         <v>40</v>
       </c>
       <c r="J24" t="s">
-        <v>728</v>
+        <v>1032</v>
       </c>
       <c r="K24" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+      <c r="M24">
+        <v>3</v>
+      </c>
+      <c r="N24">
+        <v>6</v>
+      </c>
+      <c r="U24">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>141</v>
       </c>
@@ -4450,13 +4610,22 @@
         <v>40</v>
       </c>
       <c r="J25" t="s">
-        <v>729</v>
+        <v>1033</v>
       </c>
       <c r="K25" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+      <c r="M25">
+        <v>3</v>
+      </c>
+      <c r="N25">
+        <v>6</v>
+      </c>
+      <c r="U25">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>142</v>
       </c>
@@ -4480,32 +4649,43 @@
         <v>40</v>
       </c>
       <c r="J26" t="s">
-        <v>734</v>
+        <v>1034</v>
       </c>
       <c r="K26" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+      <c r="M26">
+        <v>3</v>
+      </c>
+      <c r="N26">
+        <v>8</v>
+      </c>
+      <c r="U26">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>959</v>
+        <v>944</v>
       </c>
       <c r="B27" t="s">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="C27">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D27">
         <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>963</v>
+        <v>948</v>
       </c>
       <c r="I27" t="s">
         <v>40</v>
       </c>
-      <c r="J27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>719</v>
+      </c>
       <c r="M27">
         <v>3</v>
       </c>
@@ -4513,10 +4693,10 @@
         <v>4</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>337</v>
       </c>
@@ -4524,7 +4704,7 @@
         <v>174</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -4536,8 +4716,20 @@
       <c r="I28" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J28" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="K28" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M28">
+        <v>3</v>
+      </c>
+      <c r="N28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>525</v>
       </c>
@@ -4545,7 +4737,7 @@
         <v>520</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -4557,8 +4749,17 @@
       <c r="I29" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J29" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M29">
+        <v>3</v>
+      </c>
+      <c r="N29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>526</v>
       </c>
@@ -4566,7 +4767,7 @@
         <v>521</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -4578,8 +4779,20 @@
       <c r="I30" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J30" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="K30" t="s">
+        <v>1037</v>
+      </c>
+      <c r="M30">
+        <v>3</v>
+      </c>
+      <c r="N30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>527</v>
       </c>
@@ -4587,7 +4800,7 @@
         <v>522</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -4599,8 +4812,17 @@
       <c r="I31" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J31" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="M31">
+        <v>3</v>
+      </c>
+      <c r="N31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>528</v>
       </c>
@@ -4608,7 +4830,7 @@
         <v>523</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D32">
         <v>3</v>
@@ -4620,6 +4842,15 @@
       <c r="I32" t="s">
         <v>40</v>
       </c>
+      <c r="J32" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M32">
+        <v>3</v>
+      </c>
+      <c r="N32">
+        <v>6</v>
+      </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
@@ -4629,7 +4860,7 @@
         <v>524</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D33">
         <v>3</v>
@@ -4641,6 +4872,16 @@
       <c r="I33" t="s">
         <v>40</v>
       </c>
+      <c r="J33" s="3"/>
+      <c r="K33" t="s">
+        <v>1036</v>
+      </c>
+      <c r="M33">
+        <v>3</v>
+      </c>
+      <c r="N33">
+        <v>6</v>
+      </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -4666,7 +4907,7 @@
         <v>235</v>
       </c>
       <c r="T34" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4693,7 +4934,7 @@
         <v>235</v>
       </c>
       <c r="T35" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4720,7 +4961,7 @@
         <v>235</v>
       </c>
       <c r="T36" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4747,7 +4988,7 @@
         <v>235</v>
       </c>
       <c r="T37" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4774,7 +5015,7 @@
         <v>235</v>
       </c>
       <c r="T38" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4801,7 +5042,7 @@
         <v>235</v>
       </c>
       <c r="T39" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4828,7 +5069,7 @@
         <v>235</v>
       </c>
       <c r="T40" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -5257,7 +5498,7 @@
         <v>261</v>
       </c>
       <c r="T60" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5284,7 +5525,7 @@
         <v>261</v>
       </c>
       <c r="T61" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5311,7 +5552,7 @@
         <v>261</v>
       </c>
       <c r="T62" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5338,7 +5579,7 @@
         <v>261</v>
       </c>
       <c r="T63" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -5365,7 +5606,7 @@
         <v>261</v>
       </c>
       <c r="T64" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -5392,7 +5633,7 @@
         <v>261</v>
       </c>
       <c r="T65" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -5419,7 +5660,7 @@
         <v>261</v>
       </c>
       <c r="T66" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -5841,10 +6082,10 @@
         <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>813</v>
+        <v>800</v>
       </c>
       <c r="I86" t="s">
-        <v>916</v>
+        <v>903</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
@@ -5864,10 +6105,10 @@
         <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="I87" t="s">
-        <v>917</v>
+        <v>904</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.25">
@@ -5887,10 +6128,10 @@
         <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
       <c r="I88" t="s">
-        <v>918</v>
+        <v>905</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
@@ -5910,21 +6151,21 @@
         <v>2</v>
       </c>
       <c r="H89" t="s">
-        <v>993</v>
+        <v>978</v>
       </c>
       <c r="I89" t="s">
         <v>234</v>
       </c>
       <c r="T89" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1005</v>
+        <v>990</v>
       </c>
       <c r="B90" t="s">
-        <v>1008</v>
+        <v>993</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -5939,21 +6180,21 @@
         <v>43</v>
       </c>
       <c r="H90" t="s">
-        <v>1009</v>
+        <v>994</v>
       </c>
       <c r="I90" t="s">
-        <v>1010</v>
+        <v>995</v>
       </c>
       <c r="T90" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1006</v>
+        <v>991</v>
       </c>
       <c r="B91" t="s">
-        <v>1007</v>
+        <v>992</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -5968,13 +6209,13 @@
         <v>43</v>
       </c>
       <c r="H91" t="s">
-        <v>1009</v>
+        <v>994</v>
       </c>
       <c r="I91" t="s">
-        <v>1010</v>
+        <v>995</v>
       </c>
       <c r="T91" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
@@ -5994,13 +6235,13 @@
         <v>2</v>
       </c>
       <c r="H92" t="s">
-        <v>994</v>
+        <v>979</v>
       </c>
       <c r="I92" t="s">
         <v>234</v>
       </c>
       <c r="T92" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
@@ -6020,13 +6261,13 @@
         <v>2</v>
       </c>
       <c r="H93" t="s">
-        <v>995</v>
+        <v>980</v>
       </c>
       <c r="I93" t="s">
         <v>234</v>
       </c>
       <c r="T93" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
@@ -6046,13 +6287,13 @@
         <v>2</v>
       </c>
       <c r="H94" t="s">
-        <v>996</v>
+        <v>981</v>
       </c>
       <c r="I94" t="s">
         <v>234</v>
       </c>
       <c r="T94" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
@@ -6072,13 +6313,13 @@
         <v>2</v>
       </c>
       <c r="H95" t="s">
-        <v>999</v>
+        <v>984</v>
       </c>
       <c r="I95" t="s">
         <v>234</v>
       </c>
       <c r="T95" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.25">
@@ -6098,13 +6339,13 @@
         <v>2</v>
       </c>
       <c r="H96" t="s">
-        <v>997</v>
+        <v>982</v>
       </c>
       <c r="I96" t="s">
         <v>234</v>
       </c>
       <c r="T96" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.25">
@@ -6124,13 +6365,13 @@
         <v>2</v>
       </c>
       <c r="H97" t="s">
-        <v>998</v>
+        <v>983</v>
       </c>
       <c r="I97" t="s">
         <v>234</v>
       </c>
       <c r="T97" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.25">
@@ -6556,7 +6797,7 @@
         <v>160</v>
       </c>
       <c r="T117" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="118" spans="1:20" x14ac:dyDescent="0.25">
@@ -6583,7 +6824,7 @@
         <v>160</v>
       </c>
       <c r="T118" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.25">
@@ -6610,7 +6851,7 @@
         <v>160</v>
       </c>
       <c r="T119" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="120" spans="1:20" x14ac:dyDescent="0.25">
@@ -6637,10 +6878,10 @@
         <v>160</v>
       </c>
       <c r="J120" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="T120" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="121" spans="1:20" x14ac:dyDescent="0.25">
@@ -6667,7 +6908,7 @@
         <v>160</v>
       </c>
       <c r="T121" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="122" spans="1:20" x14ac:dyDescent="0.25">
@@ -6694,7 +6935,7 @@
         <v>160</v>
       </c>
       <c r="T122" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="123" spans="1:20" x14ac:dyDescent="0.25">
@@ -6721,7 +6962,7 @@
         <v>160</v>
       </c>
       <c r="T123" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="124" spans="1:20" x14ac:dyDescent="0.25">
@@ -6745,10 +6986,10 @@
         <v>160</v>
       </c>
       <c r="J124" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="K124" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
     </row>
     <row r="125" spans="1:20" x14ac:dyDescent="0.25">
@@ -6772,10 +7013,10 @@
         <v>160</v>
       </c>
       <c r="J125" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="K125" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
     </row>
     <row r="126" spans="1:20" x14ac:dyDescent="0.25">
@@ -6799,7 +7040,7 @@
         <v>160</v>
       </c>
       <c r="J126" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="127" spans="1:20" x14ac:dyDescent="0.25">
@@ -6823,7 +7064,7 @@
         <v>160</v>
       </c>
       <c r="J127" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="128" spans="1:20" x14ac:dyDescent="0.25">
@@ -6847,10 +7088,10 @@
         <v>160</v>
       </c>
       <c r="J128" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="K128" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
     </row>
     <row r="129" spans="1:20" x14ac:dyDescent="0.25">
@@ -6874,10 +7115,10 @@
         <v>160</v>
       </c>
       <c r="J129" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K129" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
     </row>
     <row r="130" spans="1:20" x14ac:dyDescent="0.25">
@@ -6901,10 +7142,10 @@
         <v>160</v>
       </c>
       <c r="J130" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K130" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
     </row>
     <row r="131" spans="1:20" x14ac:dyDescent="0.25">
@@ -7170,10 +7411,10 @@
     </row>
     <row r="143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="B143" t="s">
-        <v>773</v>
+        <v>760</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -7185,13 +7426,13 @@
         <v>2</v>
       </c>
       <c r="H143" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="I143" t="s">
         <v>258</v>
       </c>
       <c r="T143" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
     </row>
     <row r="144" spans="1:20" x14ac:dyDescent="0.25">
@@ -7215,7 +7456,7 @@
         <v>258</v>
       </c>
       <c r="J144" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -7239,7 +7480,7 @@
         <v>258</v>
       </c>
       <c r="J145" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -7263,7 +7504,7 @@
         <v>258</v>
       </c>
       <c r="J146" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -7287,7 +7528,7 @@
         <v>258</v>
       </c>
       <c r="J147" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -7311,7 +7552,7 @@
         <v>258</v>
       </c>
       <c r="J148" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -7335,10 +7576,10 @@
         <v>258</v>
       </c>
       <c r="J149" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="K149" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7362,7 +7603,7 @@
         <v>258</v>
       </c>
       <c r="J150" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7386,7 +7627,7 @@
         <v>258</v>
       </c>
       <c r="J151" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7410,7 +7651,7 @@
         <v>258</v>
       </c>
       <c r="J152" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7434,7 +7675,7 @@
         <v>258</v>
       </c>
       <c r="J153" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -7458,7 +7699,7 @@
         <v>258</v>
       </c>
       <c r="J154" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -7482,7 +7723,7 @@
         <v>258</v>
       </c>
       <c r="J155" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -7506,7 +7747,7 @@
         <v>258</v>
       </c>
       <c r="J156" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -7530,7 +7771,7 @@
         <v>258</v>
       </c>
       <c r="J157" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -7554,7 +7795,7 @@
         <v>258</v>
       </c>
       <c r="J158" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -7578,7 +7819,7 @@
         <v>258</v>
       </c>
       <c r="J159" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -7602,7 +7843,7 @@
         <v>258</v>
       </c>
       <c r="J160" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
     </row>
     <row r="161" spans="1:20" x14ac:dyDescent="0.25">
@@ -7626,7 +7867,7 @@
         <v>258</v>
       </c>
       <c r="J161" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
     </row>
     <row r="162" spans="1:20" x14ac:dyDescent="0.25">
@@ -7650,7 +7891,7 @@
         <v>258</v>
       </c>
       <c r="J162" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
     </row>
     <row r="163" spans="1:20" x14ac:dyDescent="0.25">
@@ -7674,7 +7915,7 @@
         <v>258</v>
       </c>
       <c r="J163" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
     </row>
     <row r="164" spans="1:20" x14ac:dyDescent="0.25">
@@ -7698,7 +7939,7 @@
         <v>258</v>
       </c>
       <c r="J164" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
     </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.25">
@@ -7722,7 +7963,7 @@
         <v>258</v>
       </c>
       <c r="J165" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.25">
@@ -7833,7 +8074,7 @@
         <v>260</v>
       </c>
       <c r="T170" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="171" spans="1:20" x14ac:dyDescent="0.25">
@@ -7860,7 +8101,7 @@
         <v>260</v>
       </c>
       <c r="T171" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="172" spans="1:20" x14ac:dyDescent="0.25">
@@ -7887,7 +8128,7 @@
         <v>260</v>
       </c>
       <c r="T172" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="173" spans="1:20" x14ac:dyDescent="0.25">
@@ -7914,7 +8155,7 @@
         <v>260</v>
       </c>
       <c r="T173" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="174" spans="1:20" x14ac:dyDescent="0.25">
@@ -7941,7 +8182,7 @@
         <v>260</v>
       </c>
       <c r="T174" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="175" spans="1:20" x14ac:dyDescent="0.25">
@@ -7968,7 +8209,7 @@
         <v>260</v>
       </c>
       <c r="T175" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="176" spans="1:20" x14ac:dyDescent="0.25">
@@ -7995,7 +8236,7 @@
         <v>260</v>
       </c>
       <c r="T176" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
@@ -8421,7 +8662,7 @@
         <v>259</v>
       </c>
       <c r="T196" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.25">
@@ -8448,7 +8689,7 @@
         <v>259</v>
       </c>
       <c r="T197" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="198" spans="1:20" x14ac:dyDescent="0.25">
@@ -8475,7 +8716,7 @@
         <v>259</v>
       </c>
       <c r="T198" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="199" spans="1:20" x14ac:dyDescent="0.25">
@@ -8502,7 +8743,7 @@
         <v>259</v>
       </c>
       <c r="T199" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="200" spans="1:20" x14ac:dyDescent="0.25">
@@ -8529,7 +8770,7 @@
         <v>259</v>
       </c>
       <c r="T200" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="201" spans="1:20" x14ac:dyDescent="0.25">
@@ -8556,7 +8797,7 @@
         <v>259</v>
       </c>
       <c r="T201" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="202" spans="1:20" x14ac:dyDescent="0.25">
@@ -8583,7 +8824,7 @@
         <v>259</v>
       </c>
       <c r="T202" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="203" spans="1:20" x14ac:dyDescent="0.25">
@@ -8987,10 +9228,10 @@
     </row>
     <row r="222" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="B222" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -9002,13 +9243,13 @@
         <v>2</v>
       </c>
       <c r="H222" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="I222" t="s">
         <v>209</v>
       </c>
       <c r="T222" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
     </row>
     <row r="223" spans="1:20" x14ac:dyDescent="0.25">
@@ -9577,16 +9818,16 @@
         <v>58</v>
       </c>
       <c r="H249" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="I249" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="J249" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="T249" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="250" spans="1:20" x14ac:dyDescent="0.25">
@@ -9609,24 +9850,24 @@
         <v>64</v>
       </c>
       <c r="H250" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="I250" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="J250" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
       <c r="T250" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
     </row>
     <row r="251" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1022</v>
+        <v>1007</v>
       </c>
       <c r="B251" t="s">
-        <v>1021</v>
+        <v>1006</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9644,24 +9885,24 @@
         <v>58</v>
       </c>
       <c r="H251" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="I251" t="s">
         <v>6</v>
       </c>
       <c r="J251" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="T251" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="252" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>1023</v>
+        <v>1008</v>
       </c>
       <c r="B252" t="s">
-        <v>1030</v>
+        <v>1015</v>
       </c>
       <c r="C252">
         <v>5</v>
@@ -9679,16 +9920,16 @@
         <v>64</v>
       </c>
       <c r="H252" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="I252" t="s">
         <v>6</v>
       </c>
       <c r="J252" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
       <c r="T252" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
     </row>
     <row r="253" spans="1:20" x14ac:dyDescent="0.25">
@@ -9711,27 +9952,27 @@
         <v>62</v>
       </c>
       <c r="H253" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
       <c r="I253" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="J253" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
       <c r="K253" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="T253" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="254" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="B254" t="s">
-        <v>886</v>
+        <v>873</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9743,24 +9984,24 @@
         <v>2</v>
       </c>
       <c r="H254" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="I254" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="J254" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="T254" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="255" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1015</v>
+        <v>1000</v>
       </c>
       <c r="B255" t="s">
-        <v>1012</v>
+        <v>997</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9775,24 +10016,24 @@
         <v>41</v>
       </c>
       <c r="H255" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="I255" t="s">
-        <v>1011</v>
+        <v>996</v>
       </c>
       <c r="J255" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="T255" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="256" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="B256" t="s">
-        <v>1013</v>
+        <v>998</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9807,16 +10048,16 @@
         <v>41</v>
       </c>
       <c r="H256" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="I256" t="s">
-        <v>1011</v>
+        <v>996</v>
       </c>
       <c r="J256" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="T256" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="257" spans="1:20" x14ac:dyDescent="0.25">
@@ -9824,7 +10065,7 @@
         <v>10</v>
       </c>
       <c r="B257" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
       <c r="C257">
         <v>10</v>
@@ -9839,16 +10080,16 @@
         <v>65</v>
       </c>
       <c r="H257" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
       <c r="I257" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="J257" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="T257" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="258" spans="1:20" x14ac:dyDescent="0.25">
@@ -9856,7 +10097,7 @@
         <v>11</v>
       </c>
       <c r="B258" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="C258">
         <v>10</v>
@@ -9871,24 +10112,24 @@
         <v>66</v>
       </c>
       <c r="H258" t="s">
-        <v>924</v>
+        <v>911</v>
       </c>
       <c r="I258" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="J258" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="T258" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
     </row>
     <row r="259" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>889</v>
+        <v>876</v>
       </c>
       <c r="B259" t="s">
-        <v>890</v>
+        <v>877</v>
       </c>
       <c r="C259">
         <v>10</v>
@@ -9900,24 +10141,24 @@
         <v>2</v>
       </c>
       <c r="H259" t="s">
-        <v>925</v>
+        <v>912</v>
       </c>
       <c r="I259" t="s">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="J259" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="T259" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="260" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>891</v>
+        <v>878</v>
       </c>
       <c r="B260" t="s">
-        <v>892</v>
+        <v>879</v>
       </c>
       <c r="C260">
         <v>10</v>
@@ -9929,24 +10170,24 @@
         <v>2</v>
       </c>
       <c r="H260" t="s">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="I260" t="s">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="J260" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="T260" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="261" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>1020</v>
+        <v>1005</v>
       </c>
       <c r="B261" t="s">
-        <v>1019</v>
+        <v>1004</v>
       </c>
       <c r="C261">
         <v>10</v>
@@ -9961,24 +10202,24 @@
         <v>41</v>
       </c>
       <c r="H261" t="s">
-        <v>925</v>
+        <v>912</v>
       </c>
       <c r="I261" t="s">
-        <v>1016</v>
+        <v>1001</v>
       </c>
       <c r="J261" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="T261" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="262" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>1018</v>
+        <v>1003</v>
       </c>
       <c r="B262" t="s">
-        <v>1017</v>
+        <v>1002</v>
       </c>
       <c r="C262">
         <v>10</v>
@@ -9993,16 +10234,16 @@
         <v>41</v>
       </c>
       <c r="H262" t="s">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="I262" t="s">
-        <v>1016</v>
+        <v>1001</v>
       </c>
       <c r="J262" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="T262" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="263" spans="1:20" x14ac:dyDescent="0.25">
@@ -10025,24 +10266,24 @@
         <v>60</v>
       </c>
       <c r="H263" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="I263" t="s">
         <v>7</v>
       </c>
       <c r="J263" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="T263" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="264" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>882</v>
+        <v>869</v>
       </c>
       <c r="B264" t="s">
-        <v>883</v>
+        <v>870</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -10054,24 +10295,24 @@
         <v>2</v>
       </c>
       <c r="H264" t="s">
-        <v>927</v>
+        <v>914</v>
       </c>
       <c r="I264" t="s">
         <v>7</v>
       </c>
       <c r="J264" t="s">
-        <v>884</v>
+        <v>871</v>
       </c>
       <c r="T264" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="265" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>887</v>
+        <v>874</v>
       </c>
       <c r="B265" t="s">
-        <v>888</v>
+        <v>875</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -10083,16 +10324,16 @@
         <v>2</v>
       </c>
       <c r="H265" t="s">
-        <v>928</v>
+        <v>915</v>
       </c>
       <c r="I265" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
       <c r="J265" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="T265" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="266" spans="1:20" x14ac:dyDescent="0.25">
@@ -10115,24 +10356,24 @@
         <v>70</v>
       </c>
       <c r="H266" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
       <c r="I266" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
       <c r="J266" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="T266" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
     </row>
     <row r="267" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>894</v>
+        <v>881</v>
       </c>
       <c r="B267" t="s">
-        <v>896</v>
+        <v>883</v>
       </c>
       <c r="C267">
         <v>11</v>
@@ -10144,24 +10385,24 @@
         <v>2</v>
       </c>
       <c r="H267" t="s">
-        <v>929</v>
+        <v>916</v>
       </c>
       <c r="I267" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="J267" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="T267" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="268" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>895</v>
+        <v>882</v>
       </c>
       <c r="B268" t="s">
-        <v>897</v>
+        <v>884</v>
       </c>
       <c r="C268">
         <v>11</v>
@@ -10173,24 +10414,24 @@
         <v>2</v>
       </c>
       <c r="H268" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="I268" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="J268" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="T268" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="269" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>898</v>
+        <v>885</v>
       </c>
       <c r="B269" t="s">
-        <v>902</v>
+        <v>889</v>
       </c>
       <c r="C269">
         <v>11</v>
@@ -10202,24 +10443,24 @@
         <v>2</v>
       </c>
       <c r="H269" t="s">
-        <v>931</v>
+        <v>918</v>
       </c>
       <c r="I269" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="J269" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="T269" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="270" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="B270" t="s">
-        <v>903</v>
+        <v>890</v>
       </c>
       <c r="C270">
         <v>11</v>
@@ -10231,24 +10472,24 @@
         <v>2</v>
       </c>
       <c r="H270" t="s">
-        <v>933</v>
+        <v>920</v>
       </c>
       <c r="I270" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="J270" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="T270" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
     </row>
     <row r="271" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>900</v>
+        <v>887</v>
       </c>
       <c r="B271" t="s">
-        <v>904</v>
+        <v>891</v>
       </c>
       <c r="C271">
         <v>11</v>
@@ -10260,24 +10501,24 @@
         <v>2</v>
       </c>
       <c r="H271" t="s">
-        <v>932</v>
+        <v>919</v>
       </c>
       <c r="I271" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
       <c r="J271" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="T271" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="272" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>901</v>
+        <v>888</v>
       </c>
       <c r="B272" t="s">
-        <v>905</v>
+        <v>892</v>
       </c>
       <c r="C272">
         <v>11</v>
@@ -10289,24 +10530,24 @@
         <v>2</v>
       </c>
       <c r="H272" t="s">
-        <v>934</v>
+        <v>921</v>
       </c>
       <c r="I272" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
       <c r="J272" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="T272" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="273" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>907</v>
+        <v>894</v>
       </c>
       <c r="B273" t="s">
-        <v>911</v>
+        <v>898</v>
       </c>
       <c r="C273">
         <v>11</v>
@@ -10318,24 +10559,24 @@
         <v>2</v>
       </c>
       <c r="H273" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="I273" t="s">
-        <v>907</v>
+        <v>894</v>
       </c>
       <c r="J273" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="T273" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="274" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>908</v>
+        <v>895</v>
       </c>
       <c r="B274" t="s">
-        <v>912</v>
+        <v>899</v>
       </c>
       <c r="C274">
         <v>11</v>
@@ -10347,24 +10588,24 @@
         <v>2</v>
       </c>
       <c r="H274" t="s">
-        <v>936</v>
+        <v>923</v>
       </c>
       <c r="I274" t="s">
-        <v>907</v>
+        <v>894</v>
       </c>
       <c r="J274" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="T274" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="275" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>1025</v>
+        <v>1010</v>
       </c>
       <c r="B275" t="s">
-        <v>1026</v>
+        <v>1011</v>
       </c>
       <c r="C275">
         <v>11</v>
@@ -10379,24 +10620,24 @@
         <v>43</v>
       </c>
       <c r="H275" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="I275" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="J275" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="T275" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="276" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>1028</v>
+        <v>1013</v>
       </c>
       <c r="B276" t="s">
-        <v>1027</v>
+        <v>1012</v>
       </c>
       <c r="C276">
         <v>11</v>
@@ -10411,24 +10652,24 @@
         <v>43</v>
       </c>
       <c r="H276" t="s">
-        <v>936</v>
+        <v>923</v>
       </c>
       <c r="I276" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="J276" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="T276" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="277" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>909</v>
+        <v>896</v>
       </c>
       <c r="B277" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
       <c r="C277">
         <v>11</v>
@@ -10440,24 +10681,24 @@
         <v>2</v>
       </c>
       <c r="H277" t="s">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="I277" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="J277" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="T277" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
     </row>
     <row r="278" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="B278" t="s">
-        <v>914</v>
+        <v>901</v>
       </c>
       <c r="C278">
         <v>11</v>
@@ -10469,24 +10710,24 @@
         <v>2</v>
       </c>
       <c r="H278" t="s">
-        <v>938</v>
+        <v>925</v>
       </c>
       <c r="I278" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="J278" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="T278" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
     </row>
     <row r="279" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>919</v>
+        <v>906</v>
       </c>
       <c r="B279" t="s">
-        <v>921</v>
+        <v>908</v>
       </c>
       <c r="C279">
         <v>11</v>
@@ -10498,24 +10739,24 @@
         <v>2</v>
       </c>
       <c r="H279" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
       <c r="I279" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
       <c r="K279" t="s">
-        <v>946</v>
+        <v>932</v>
       </c>
       <c r="T279" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="280" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>920</v>
+        <v>907</v>
       </c>
       <c r="B280" t="s">
-        <v>922</v>
+        <v>909</v>
       </c>
       <c r="C280">
         <v>11</v>
@@ -10527,16 +10768,16 @@
         <v>2</v>
       </c>
       <c r="H280" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="I280" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
       <c r="K280" t="s">
-        <v>946</v>
+        <v>932</v>
       </c>
       <c r="T280" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
     </row>
     <row r="281" spans="1:20" x14ac:dyDescent="0.25">
@@ -10556,13 +10797,13 @@
         <v>68</v>
       </c>
       <c r="H281" t="s">
-        <v>941</v>
+        <v>928</v>
       </c>
       <c r="I281" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
       <c r="J281" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
     </row>
     <row r="282" spans="1:20" x14ac:dyDescent="0.25">
@@ -10582,13 +10823,13 @@
         <v>72</v>
       </c>
       <c r="H282" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
       <c r="I282" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="J282" t="s">
-        <v>967</v>
+        <v>952</v>
       </c>
     </row>
     <row r="283" spans="1:20" x14ac:dyDescent="0.25">
@@ -10611,13 +10852,13 @@
         <v>74</v>
       </c>
       <c r="H283" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
       <c r="I283" t="s">
-        <v>1016</v>
+        <v>1001</v>
       </c>
       <c r="J283" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
     </row>
     <row r="284" spans="1:20" x14ac:dyDescent="0.25">
@@ -10640,13 +10881,13 @@
         <v>76</v>
       </c>
       <c r="H284" t="s">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="I284" t="s">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="J284" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
     </row>
     <row r="285" spans="1:20" x14ac:dyDescent="0.25">
@@ -10669,13 +10910,13 @@
         <v>77</v>
       </c>
       <c r="H285" t="s">
-        <v>942</v>
+        <v>929</v>
       </c>
       <c r="I285" t="s">
-        <v>1016</v>
+        <v>1001</v>
       </c>
       <c r="J285" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
     </row>
     <row r="286" spans="1:20" x14ac:dyDescent="0.25">
@@ -10698,13 +10939,13 @@
         <v>78</v>
       </c>
       <c r="H286" t="s">
-        <v>821</v>
+        <v>808</v>
       </c>
       <c r="I286" t="s">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="J286" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="287" spans="1:20" x14ac:dyDescent="0.25">
@@ -10727,13 +10968,13 @@
         <v>79</v>
       </c>
       <c r="H287" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="I287" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
       <c r="J287" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
     </row>
     <row r="288" spans="1:20" x14ac:dyDescent="0.25">
@@ -10756,13 +10997,13 @@
         <v>80</v>
       </c>
       <c r="H288" t="s">
-        <v>823</v>
+        <v>810</v>
       </c>
       <c r="I288" t="s">
-        <v>1011</v>
+        <v>996</v>
       </c>
       <c r="J288" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -10785,13 +11026,13 @@
         <v>81</v>
       </c>
       <c r="H289" t="s">
-        <v>943</v>
+        <v>930</v>
       </c>
       <c r="I289" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="J289" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -10814,13 +11055,13 @@
         <v>82</v>
       </c>
       <c r="H290" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="I290" t="s">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="J290" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -10843,13 +11084,13 @@
         <v>84</v>
       </c>
       <c r="H291" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
       <c r="I291" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
       <c r="J291" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -10872,13 +11113,13 @@
         <v>86</v>
       </c>
       <c r="H292" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="I292" t="s">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="J292" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -10904,13 +11145,13 @@
         <v>39</v>
       </c>
       <c r="I293" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="J293" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="K293" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -10939,7 +11180,7 @@
         <v>6</v>
       </c>
       <c r="J294" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -10965,10 +11206,10 @@
         <v>39</v>
       </c>
       <c r="I295" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="J295" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -10994,13 +11235,13 @@
         <v>39</v>
       </c>
       <c r="I296" t="s">
-        <v>907</v>
+        <v>894</v>
       </c>
       <c r="J296" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="K296" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -11029,7 +11270,7 @@
         <v>6</v>
       </c>
       <c r="J297" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -11055,13 +11296,13 @@
         <v>39</v>
       </c>
       <c r="I298" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="J298" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="K298" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -11087,13 +11328,13 @@
         <v>39</v>
       </c>
       <c r="I299" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="J299" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="K299" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -11119,13 +11360,13 @@
         <v>39</v>
       </c>
       <c r="I300" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="J300" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="K300" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -11151,13 +11392,13 @@
         <v>39</v>
       </c>
       <c r="I301" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="J301" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="K301" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -11183,13 +11424,13 @@
         <v>39</v>
       </c>
       <c r="I302" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="J302" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="K302" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
@@ -11210,7 +11451,7 @@
         <v>虹</v>
       </c>
       <c r="I303" t="s">
-        <v>907</v>
+        <v>894</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -11231,7 +11472,7 @@
         <v>神</v>
       </c>
       <c r="I304" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
     </row>
     <row r="305" spans="1:20" x14ac:dyDescent="0.25">
@@ -11252,7 +11493,7 @@
         <v>魔</v>
       </c>
       <c r="I305" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
     </row>
     <row r="306" spans="1:20" x14ac:dyDescent="0.25">
@@ -11273,7 +11514,7 @@
         <v>赤</v>
       </c>
       <c r="I306" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
     </row>
     <row r="307" spans="1:20" x14ac:dyDescent="0.25">
@@ -11297,7 +11538,7 @@
         <v>启</v>
       </c>
       <c r="I307" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
     </row>
     <row r="308" spans="1:20" x14ac:dyDescent="0.25">
@@ -11321,7 +11562,7 @@
         <v>怒</v>
       </c>
       <c r="I308" t="s">
-        <v>893</v>
+        <v>880</v>
       </c>
     </row>
     <row r="309" spans="1:20" x14ac:dyDescent="0.25">
@@ -11369,7 +11610,7 @@
         <v>逍</v>
       </c>
       <c r="I310" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
     </row>
     <row r="311" spans="1:20" x14ac:dyDescent="0.25">
@@ -11390,15 +11631,15 @@
         <v>卧</v>
       </c>
       <c r="I311" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
     </row>
     <row r="312" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>961</v>
+        <v>946</v>
       </c>
       <c r="B312" t="s">
-        <v>962</v>
+        <v>947</v>
       </c>
       <c r="C312">
         <v>11</v>
@@ -11407,13 +11648,13 @@
         <v>2</v>
       </c>
       <c r="H312" t="s">
-        <v>964</v>
+        <v>949</v>
       </c>
       <c r="I312" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
       <c r="J312" s="3" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="M312">
         <v>2</v>
@@ -11422,7 +11663,7 @@
         <v>3</v>
       </c>
       <c r="R312" s="3" t="s">
-        <v>958</v>
+        <v>943</v>
       </c>
     </row>
     <row r="313" spans="1:20" x14ac:dyDescent="0.25">
@@ -11446,10 +11687,10 @@
         <v>白</v>
       </c>
       <c r="I313" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="T313" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="314" spans="1:20" x14ac:dyDescent="0.25">
@@ -11473,10 +11714,10 @@
         <v>软</v>
       </c>
       <c r="I314" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="T314" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="315" spans="1:20" x14ac:dyDescent="0.25">
@@ -11500,10 +11741,10 @@
         <v>轻</v>
       </c>
       <c r="I315" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="T315" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="316" spans="1:20" x14ac:dyDescent="0.25">
@@ -11527,10 +11768,10 @@
         <v>青</v>
       </c>
       <c r="I316" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="T316" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="317" spans="1:20" x14ac:dyDescent="0.25">
@@ -11554,10 +11795,10 @@
         <v>中</v>
       </c>
       <c r="I317" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="T317" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="318" spans="1:20" x14ac:dyDescent="0.25">
@@ -11581,10 +11822,10 @@
         <v>铁</v>
       </c>
       <c r="I318" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="T318" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="319" spans="1:20" x14ac:dyDescent="0.25">
@@ -11608,10 +11849,10 @@
         <v>钢</v>
       </c>
       <c r="I319" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="T319" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="320" spans="1:20" x14ac:dyDescent="0.25">
@@ -11628,10 +11869,10 @@
         <v>2</v>
       </c>
       <c r="H320" t="s">
-        <v>965</v>
+        <v>950</v>
       </c>
       <c r="I320" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="J320" s="3"/>
       <c r="M320">
@@ -11641,7 +11882,7 @@
         <v>4</v>
       </c>
       <c r="R320" s="3" t="s">
-        <v>958</v>
+        <v>943</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
@@ -11662,7 +11903,7 @@
         <v>铁</v>
       </c>
       <c r="I321" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.25">
@@ -11683,7 +11924,7 @@
         <v>小</v>
       </c>
       <c r="I322" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.25">
@@ -11704,7 +11945,7 @@
         <v>银</v>
       </c>
       <c r="I323" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
@@ -11725,7 +11966,7 @@
         <v>大</v>
       </c>
       <c r="I324" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
@@ -11746,7 +11987,7 @@
         <v>钢</v>
       </c>
       <c r="I325" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
@@ -11767,7 +12008,7 @@
         <v>魔</v>
       </c>
       <c r="I326" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
@@ -11788,7 +12029,7 @@
         <v>夏</v>
       </c>
       <c r="I327" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
@@ -11809,7 +12050,7 @@
         <v>辟</v>
       </c>
       <c r="I328" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
@@ -11830,7 +12071,7 @@
         <v>道</v>
       </c>
       <c r="I329" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
@@ -11851,7 +12092,7 @@
         <v>黑</v>
       </c>
       <c r="I330" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
@@ -11872,7 +12113,7 @@
         <v>魔</v>
       </c>
       <c r="I331" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
@@ -11893,7 +12134,7 @@
         <v>金</v>
       </c>
       <c r="I332" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
@@ -11914,7 +12155,7 @@
         <v>心</v>
       </c>
       <c r="I333" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
@@ -11935,7 +12176,7 @@
         <v>三</v>
       </c>
       <c r="I334" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
@@ -11956,7 +12197,7 @@
         <v>思</v>
       </c>
       <c r="I335" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.25">
@@ -11977,7 +12218,7 @@
         <v>龙</v>
       </c>
       <c r="I336" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.25">
@@ -11998,7 +12239,7 @@
         <v>骑</v>
       </c>
       <c r="I337" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.25">
@@ -12019,15 +12260,15 @@
         <v>魔</v>
       </c>
       <c r="I338" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>857</v>
+        <v>844</v>
       </c>
       <c r="C339">
         <v>7</v>
@@ -12036,21 +12277,21 @@
         <v>0</v>
       </c>
       <c r="H339" t="s">
-        <v>778</v>
+        <v>765</v>
       </c>
       <c r="I339" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J339" t="s">
-        <v>968</v>
+        <v>953</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>861</v>
+        <v>848</v>
       </c>
       <c r="C340">
         <v>7</v>
@@ -12059,21 +12300,21 @@
         <v>0</v>
       </c>
       <c r="H340" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
       <c r="I340" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J340" t="s">
-        <v>969</v>
+        <v>954</v>
       </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B341" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="C341">
         <v>7</v>
@@ -12082,21 +12323,21 @@
         <v>0</v>
       </c>
       <c r="H341" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="I341" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J341" t="s">
-        <v>970</v>
+        <v>955</v>
       </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B342" t="s">
-        <v>850</v>
+        <v>837</v>
       </c>
       <c r="C342">
         <v>7</v>
@@ -12105,21 +12346,21 @@
         <v>0</v>
       </c>
       <c r="H342" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="I342" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J342" t="s">
-        <v>971</v>
+        <v>956</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B343" t="s">
-        <v>851</v>
+        <v>838</v>
       </c>
       <c r="C343">
         <v>7</v>
@@ -12128,21 +12369,21 @@
         <v>0</v>
       </c>
       <c r="H343" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="I343" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J343" t="s">
-        <v>972</v>
+        <v>957</v>
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B344" t="s">
-        <v>852</v>
+        <v>839</v>
       </c>
       <c r="C344">
         <v>14</v>
@@ -12151,21 +12392,21 @@
         <v>1</v>
       </c>
       <c r="H344" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="I344" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J344" t="s">
-        <v>973</v>
+        <v>958</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="C345">
         <v>14</v>
@@ -12174,21 +12415,21 @@
         <v>1</v>
       </c>
       <c r="H345" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
       <c r="I345" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J345" t="s">
-        <v>974</v>
+        <v>959</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B346" t="s">
-        <v>853</v>
+        <v>840</v>
       </c>
       <c r="C346">
         <v>14</v>
@@ -12197,21 +12438,21 @@
         <v>1</v>
       </c>
       <c r="H346" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
       <c r="I346" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J346" t="s">
-        <v>975</v>
+        <v>960</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B347" t="s">
-        <v>854</v>
+        <v>841</v>
       </c>
       <c r="C347">
         <v>14</v>
@@ -12220,21 +12461,21 @@
         <v>1</v>
       </c>
       <c r="H347" t="s">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="I347" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J347" t="s">
-        <v>976</v>
+        <v>961</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>871</v>
+        <v>858</v>
       </c>
       <c r="C348">
         <v>14</v>
@@ -12243,21 +12484,21 @@
         <v>1</v>
       </c>
       <c r="H348" t="s">
-        <v>787</v>
+        <v>774</v>
       </c>
       <c r="I348" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J348" t="s">
-        <v>977</v>
+        <v>962</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B349" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="C349">
         <v>21</v>
@@ -12266,21 +12507,21 @@
         <v>2</v>
       </c>
       <c r="H349" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="I349" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J349" t="s">
-        <v>978</v>
+        <v>963</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="C350">
         <v>21</v>
@@ -12289,21 +12530,21 @@
         <v>2</v>
       </c>
       <c r="H350" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="I350" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J350" t="s">
-        <v>979</v>
+        <v>964</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="C351">
         <v>21</v>
@@ -12312,21 +12553,21 @@
         <v>2</v>
       </c>
       <c r="H351" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="I351" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J351" t="s">
-        <v>980</v>
+        <v>965</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>869</v>
+        <v>856</v>
       </c>
       <c r="C352">
         <v>21</v>
@@ -12335,21 +12576,21 @@
         <v>2</v>
       </c>
       <c r="H352" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="I352" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J352" t="s">
-        <v>981</v>
+        <v>966</v>
       </c>
     </row>
     <row r="353" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
       <c r="C353">
         <v>21</v>
@@ -12358,21 +12599,21 @@
         <v>2</v>
       </c>
       <c r="H353" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="I353" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J353" t="s">
-        <v>982</v>
+        <v>967</v>
       </c>
     </row>
     <row r="354" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B354" t="s">
-        <v>859</v>
+        <v>846</v>
       </c>
       <c r="C354">
         <v>28</v>
@@ -12381,21 +12622,21 @@
         <v>3</v>
       </c>
       <c r="H354" t="s">
-        <v>793</v>
+        <v>780</v>
       </c>
       <c r="I354" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J354" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
     </row>
     <row r="355" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="C355">
         <v>28</v>
@@ -12404,21 +12645,21 @@
         <v>3</v>
       </c>
       <c r="H355" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
       <c r="I355" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J355" t="s">
-        <v>984</v>
+        <v>969</v>
       </c>
     </row>
     <row r="356" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B356" t="s">
-        <v>855</v>
+        <v>842</v>
       </c>
       <c r="C356">
         <v>28</v>
@@ -12427,21 +12668,21 @@
         <v>3</v>
       </c>
       <c r="H356" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
       <c r="I356" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J356" t="s">
-        <v>985</v>
+        <v>970</v>
       </c>
     </row>
     <row r="357" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>870</v>
+        <v>857</v>
       </c>
       <c r="C357">
         <v>28</v>
@@ -12450,21 +12691,21 @@
         <v>3</v>
       </c>
       <c r="H357" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="I357" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J357" t="s">
-        <v>986</v>
+        <v>971</v>
       </c>
     </row>
     <row r="358" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B358" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="C358">
         <v>28</v>
@@ -12473,21 +12714,21 @@
         <v>3</v>
       </c>
       <c r="H358" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
       <c r="I358" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J358" t="s">
-        <v>987</v>
+        <v>972</v>
       </c>
     </row>
     <row r="359" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B359" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
       <c r="C359">
         <v>35</v>
@@ -12496,21 +12737,21 @@
         <v>4</v>
       </c>
       <c r="H359" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="I359" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J359" t="s">
-        <v>988</v>
+        <v>973</v>
       </c>
     </row>
     <row r="360" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="C360">
         <v>35</v>
@@ -12519,21 +12760,21 @@
         <v>4</v>
       </c>
       <c r="H360" t="s">
-        <v>799</v>
+        <v>786</v>
       </c>
       <c r="I360" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J360" t="s">
-        <v>989</v>
+        <v>974</v>
       </c>
     </row>
     <row r="361" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>868</v>
+        <v>855</v>
       </c>
       <c r="C361">
         <v>35</v>
@@ -12542,21 +12783,21 @@
         <v>4</v>
       </c>
       <c r="H361" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="I361" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J361" t="s">
-        <v>990</v>
+        <v>975</v>
       </c>
     </row>
     <row r="362" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B362" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
       <c r="C362">
         <v>35</v>
@@ -12565,21 +12806,21 @@
         <v>4</v>
       </c>
       <c r="H362" t="s">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="I362" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J362" t="s">
-        <v>991</v>
+        <v>976</v>
       </c>
     </row>
     <row r="363" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B363" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="C363">
         <v>35</v>
@@ -12588,21 +12829,21 @@
         <v>4</v>
       </c>
       <c r="H363" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="I363" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J363" t="s">
-        <v>992</v>
+        <v>977</v>
       </c>
     </row>
     <row r="364" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>947</v>
+        <v>933</v>
       </c>
       <c r="B364" t="s">
-        <v>948</v>
+        <v>934</v>
       </c>
       <c r="C364">
         <v>1</v>
@@ -12615,27 +12856,27 @@
         <v>钢</v>
       </c>
       <c r="I364" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="J364" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="O364" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
       <c r="P364" t="s">
-        <v>949</v>
+        <v>1016</v>
       </c>
       <c r="Q364" t="s">
-        <v>950</v>
+        <v>935</v>
       </c>
     </row>
     <row r="365" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B365" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C365">
         <v>1</v>
@@ -12648,13 +12889,13 @@
         <v>无</v>
       </c>
       <c r="I365" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="J365" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="K365" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="M365">
         <v>0</v>
@@ -12663,21 +12904,21 @@
         <v>1</v>
       </c>
       <c r="O365" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
       <c r="P365" t="s">
-        <v>945</v>
+        <v>1017</v>
       </c>
       <c r="Q365" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
     </row>
     <row r="366" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B366" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C366">
         <v>1</v>
@@ -12690,13 +12931,13 @@
         <v>沃</v>
       </c>
       <c r="I366" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="J366" t="s">
-        <v>953</v>
+        <v>938</v>
       </c>
       <c r="R366" s="3" t="s">
-        <v>958</v>
+        <v>943</v>
       </c>
       <c r="S366">
         <v>2</v>
@@ -12704,10 +12945,10 @@
     </row>
     <row r="367" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
       <c r="B367" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C367">
         <v>1</v>
@@ -12720,13 +12961,13 @@
         <v>沃</v>
       </c>
       <c r="I367" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="J367" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
       <c r="R367" s="3" t="s">
-        <v>958</v>
+        <v>943</v>
       </c>
       <c r="S367">
         <v>3</v>
@@ -12736,16 +12977,7 @@
   <autoFilter ref="A4:T367" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J27">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J312">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J320">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/configs/Item.xlsx
+++ b/configs/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6994EDC0-F448-47BA-9769-C8A6084C2876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDADD336-1375-4C04-80BA-CE2AB07E9016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{32817E20-F0A4-463C-B290-2589502B59A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="1040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="1041">
   <si>
     <t>id</t>
   </si>
@@ -3186,6 +3186,9 @@
   </si>
   <si>
     <t>xdr1,-0.5:pdr1,1.1</t>
+  </si>
+  <si>
+    <t>Map&lt;AffixId,number&gt;[]</t>
   </si>
 </sst>
 </file>
@@ -3650,7 +3653,7 @@
     <col min="8" max="8" width="22.140625" customWidth="1"/>
     <col min="9" max="9" width="12.42578125" customWidth="1"/>
     <col min="10" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" customWidth="1"/>
     <col min="12" max="12" width="8.42578125" customWidth="1"/>
     <col min="13" max="13" width="9.42578125" customWidth="1"/>
     <col min="14" max="14" width="7" customWidth="1"/>
@@ -3755,7 +3758,7 @@
         <v>660</v>
       </c>
       <c r="K2" t="s">
-        <v>660</v>
+        <v>1040</v>
       </c>
       <c r="L2" t="s">
         <v>5</v>
@@ -4303,11 +4306,14 @@
       <c r="K17" t="s">
         <v>1019</v>
       </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
       <c r="M17">
         <v>3</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>1.2</v>

--- a/configs/Item.xlsx
+++ b/configs/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA83D0C-73E4-420E-BBA5-DDE2DA24EEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DA88A3-AB13-4284-A94A-3498A05C03D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{03E97168-5F7A-4CBC-B68A-30D1DC85464C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{03E97168-5F7A-4CBC-B68A-30D1DC85464C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7417,13 +7417,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -7480,7 +7480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -7488,10 +7488,9 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -7558,7 +7557,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -7875,31 +7874,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
   <dimension ref="A1:U434"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="21.875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.375" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.08984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.90625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.6328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.36328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.08984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.08984375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.36328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.6328125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="21.90625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.36328125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9.36328125" style="1" customWidth="1"/>
     <col min="14" max="14" width="7" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.25" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.6328125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.08984375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.90625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.26953125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.26953125" style="1" customWidth="1"/>
     <col min="20" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7961,7 +7960,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>417</v>
       </c>
@@ -8023,7 +8022,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>44</v>
       </c>
@@ -8031,7 +8030,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>619</v>
       </c>
@@ -8093,7 +8092,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>66</v>
       </c>
@@ -8122,7 +8121,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>231</v>
       </c>
@@ -8151,7 +8150,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>232</v>
       </c>
@@ -8180,7 +8179,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>233</v>
       </c>
@@ -8209,7 +8208,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>234</v>
       </c>
@@ -8238,7 +8237,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>235</v>
       </c>
@@ -8267,7 +8266,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>236</v>
       </c>
@@ -8296,7 +8295,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>237</v>
       </c>
@@ -8331,7 +8330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>238</v>
       </c>
@@ -8366,7 +8365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>239</v>
       </c>
@@ -8395,7 +8394,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>240</v>
       </c>
@@ -8424,7 +8423,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>241</v>
       </c>
@@ -8459,7 +8458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>242</v>
       </c>
@@ -8494,7 +8493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>243</v>
       </c>
@@ -8529,7 +8528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>159</v>
       </c>
@@ -8558,7 +8557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>163</v>
       </c>
@@ -8596,7 +8595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>164</v>
       </c>
@@ -8634,7 +8633,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>165</v>
       </c>
@@ -8672,7 +8671,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>297</v>
       </c>
@@ -8701,7 +8700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>298</v>
       </c>
@@ -8730,7 +8729,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>299</v>
       </c>
@@ -8759,7 +8758,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>300</v>
       </c>
@@ -8794,7 +8793,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>301</v>
       </c>
@@ -8823,7 +8822,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>244</v>
       </c>
@@ -8852,7 +8851,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>245</v>
       </c>
@@ -8881,7 +8880,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>246</v>
       </c>
@@ -8910,7 +8909,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>247</v>
       </c>
@@ -8939,7 +8938,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>248</v>
       </c>
@@ -8968,7 +8967,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>249</v>
       </c>
@@ -8997,7 +8996,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>250</v>
       </c>
@@ -9026,7 +9025,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>251</v>
       </c>
@@ -9055,7 +9054,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>252</v>
       </c>
@@ -9084,7 +9083,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>253</v>
       </c>
@@ -9113,7 +9112,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>254</v>
       </c>
@@ -9142,7 +9141,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>255</v>
       </c>
@@ -9171,7 +9170,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>256</v>
       </c>
@@ -9200,7 +9199,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>257</v>
       </c>
@@ -9229,7 +9228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>158</v>
       </c>
@@ -9258,7 +9257,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>170</v>
       </c>
@@ -9287,7 +9286,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>317</v>
       </c>
@@ -9316,7 +9315,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>318</v>
       </c>
@@ -9345,7 +9344,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>319</v>
       </c>
@@ -9374,7 +9373,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>320</v>
       </c>
@@ -9403,7 +9402,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>321</v>
       </c>
@@ -9432,7 +9431,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>322</v>
       </c>
@@ -9461,7 +9460,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>323</v>
       </c>
@@ -9490,7 +9489,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>324</v>
       </c>
@@ -9519,7 +9518,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>325</v>
       </c>
@@ -9548,7 +9547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>326</v>
       </c>
@@ -9577,7 +9576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>47</v>
       </c>
@@ -9618,7 +9617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>48</v>
       </c>
@@ -9650,7 +9649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>590</v>
       </c>
@@ -9691,7 +9690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>592</v>
       </c>
@@ -9732,7 +9731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>49</v>
       </c>
@@ -9770,7 +9769,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>50</v>
       </c>
@@ -9802,7 +9801,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>51</v>
       </c>
@@ -9840,7 +9839,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>52</v>
       </c>
@@ -9872,7 +9871,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>53</v>
       </c>
@@ -9904,7 +9903,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>67</v>
       </c>
@@ -9942,7 +9941,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>76</v>
       </c>
@@ -9977,7 +9976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>258</v>
       </c>
@@ -10006,7 +10005,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" ht="15" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>1308</v>
       </c>
@@ -10026,7 +10025,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>259</v>
       </c>
@@ -10061,7 +10060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>260</v>
       </c>
@@ -10096,7 +10095,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>261</v>
       </c>
@@ -10125,7 +10124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>262</v>
       </c>
@@ -10157,7 +10156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>77</v>
       </c>
@@ -10184,7 +10183,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>78</v>
       </c>
@@ -10211,7 +10210,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>79</v>
       </c>
@@ -10238,7 +10237,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>80</v>
       </c>
@@ -10265,7 +10264,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>81</v>
       </c>
@@ -10292,7 +10291,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>82</v>
       </c>
@@ -10319,7 +10318,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>83</v>
       </c>
@@ -10346,7 +10345,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>85</v>
       </c>
@@ -10367,7 +10366,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>86</v>
       </c>
@@ -10388,7 +10387,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>87</v>
       </c>
@@ -10409,7 +10408,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>88</v>
       </c>
@@ -10430,7 +10429,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>89</v>
       </c>
@@ -10451,7 +10450,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>90</v>
       </c>
@@ -10472,7 +10471,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>91</v>
       </c>
@@ -10493,7 +10492,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>92</v>
       </c>
@@ -10514,7 +10513,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>93</v>
       </c>
@@ -10535,7 +10534,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>94</v>
       </c>
@@ -10556,7 +10555,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>95</v>
       </c>
@@ -10577,7 +10576,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>96</v>
       </c>
@@ -10598,7 +10597,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>97</v>
       </c>
@@ -10619,7 +10618,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>98</v>
       </c>
@@ -10640,7 +10639,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>99</v>
       </c>
@@ -10661,7 +10660,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>100</v>
       </c>
@@ -10682,7 +10681,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>101</v>
       </c>
@@ -10703,7 +10702,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>102</v>
       </c>
@@ -10724,7 +10723,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>103</v>
       </c>
@@ -10753,7 +10752,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>1187</v>
       </c>
@@ -10788,7 +10787,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>594</v>
       </c>
@@ -10823,7 +10822,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>104</v>
       </c>
@@ -10852,7 +10851,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>105</v>
       </c>
@@ -10881,7 +10880,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>106</v>
       </c>
@@ -10910,7 +10909,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>107</v>
       </c>
@@ -10939,7 +10938,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>108</v>
       </c>
@@ -10968,7 +10967,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>109</v>
       </c>
@@ -10997,7 +10996,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>110</v>
       </c>
@@ -11026,7 +11025,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>111</v>
       </c>
@@ -11055,7 +11054,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>1188</v>
       </c>
@@ -11084,7 +11083,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>113</v>
       </c>
@@ -11113,7 +11112,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>142</v>
       </c>
@@ -11142,7 +11141,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="15" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>1311</v>
       </c>
@@ -11162,7 +11161,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>151</v>
       </c>
@@ -11191,7 +11190,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>157</v>
       </c>
@@ -11220,7 +11219,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>161</v>
       </c>
@@ -11249,7 +11248,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>171</v>
       </c>
@@ -11278,7 +11277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>284</v>
       </c>
@@ -11307,7 +11306,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>285</v>
       </c>
@@ -11336,7 +11335,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>286</v>
       </c>
@@ -11365,7 +11364,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>287</v>
       </c>
@@ -11394,7 +11393,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>288</v>
       </c>
@@ -11423,7 +11422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>289</v>
       </c>
@@ -11452,7 +11451,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>290</v>
       </c>
@@ -11481,7 +11480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>291</v>
       </c>
@@ -11510,7 +11509,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>292</v>
       </c>
@@ -11539,7 +11538,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>293</v>
       </c>
@@ -11568,7 +11567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>114</v>
       </c>
@@ -11595,7 +11594,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>115</v>
       </c>
@@ -11622,7 +11621,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>116</v>
       </c>
@@ -11649,7 +11648,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>117</v>
       </c>
@@ -11676,7 +11675,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>118</v>
       </c>
@@ -11703,7 +11702,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>119</v>
       </c>
@@ -11730,7 +11729,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>120</v>
       </c>
@@ -11757,7 +11756,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>121</v>
       </c>
@@ -11778,7 +11777,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>141</v>
       </c>
@@ -11799,7 +11798,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>144</v>
       </c>
@@ -11820,7 +11819,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>148</v>
       </c>
@@ -11841,7 +11840,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>149</v>
       </c>
@@ -11862,7 +11861,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>152</v>
       </c>
@@ -11886,7 +11885,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>166</v>
       </c>
@@ -11907,7 +11906,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>167</v>
       </c>
@@ -11928,7 +11927,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>263</v>
       </c>
@@ -11949,7 +11948,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>264</v>
       </c>
@@ -11970,7 +11969,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>265</v>
       </c>
@@ -11991,7 +11990,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>266</v>
       </c>
@@ -12012,7 +12011,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>267</v>
       </c>
@@ -12033,7 +12032,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>268</v>
       </c>
@@ -12054,7 +12053,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>269</v>
       </c>
@@ -12075,7 +12074,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>270</v>
       </c>
@@ -12096,7 +12095,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>271</v>
       </c>
@@ -12117,7 +12116,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>272</v>
       </c>
@@ -12138,7 +12137,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>273</v>
       </c>
@@ -12159,7 +12158,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>122</v>
       </c>
@@ -12188,7 +12187,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>123</v>
       </c>
@@ -12217,7 +12216,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>124</v>
       </c>
@@ -12246,7 +12245,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>125</v>
       </c>
@@ -12275,7 +12274,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>126</v>
       </c>
@@ -12304,7 +12303,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>127</v>
       </c>
@@ -12333,7 +12332,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>128</v>
       </c>
@@ -12362,7 +12361,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>129</v>
       </c>
@@ -12391,7 +12390,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>1229</v>
       </c>
@@ -12420,7 +12419,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>145</v>
       </c>
@@ -12449,7 +12448,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>146</v>
       </c>
@@ -12478,7 +12477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>150</v>
       </c>
@@ -12507,7 +12506,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>154</v>
       </c>
@@ -12536,7 +12535,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>156</v>
       </c>
@@ -12565,7 +12564,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>162</v>
       </c>
@@ -12594,7 +12593,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>172</v>
       </c>
@@ -12623,7 +12622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>306</v>
       </c>
@@ -12652,7 +12651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>307</v>
       </c>
@@ -12681,7 +12680,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>308</v>
       </c>
@@ -12710,7 +12709,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>309</v>
       </c>
@@ -12739,7 +12738,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>310</v>
       </c>
@@ -12768,7 +12767,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>311</v>
       </c>
@@ -12797,7 +12796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>312</v>
       </c>
@@ -12826,7 +12825,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>313</v>
       </c>
@@ -12855,7 +12854,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>314</v>
       </c>
@@ -12884,7 +12883,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>315</v>
       </c>
@@ -12913,7 +12912,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>130</v>
       </c>
@@ -12940,7 +12939,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>131</v>
       </c>
@@ -12967,7 +12966,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>132</v>
       </c>
@@ -12994,7 +12993,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>133</v>
       </c>
@@ -13021,7 +13020,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>134</v>
       </c>
@@ -13048,7 +13047,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>135</v>
       </c>
@@ -13075,7 +13074,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>136</v>
       </c>
@@ -13102,7 +13101,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>137</v>
       </c>
@@ -13123,7 +13122,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>138</v>
       </c>
@@ -13144,7 +13143,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>139</v>
       </c>
@@ -13165,7 +13164,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>140</v>
       </c>
@@ -13186,7 +13185,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>147</v>
       </c>
@@ -13207,7 +13206,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>153</v>
       </c>
@@ -13228,7 +13227,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>155</v>
       </c>
@@ -13249,7 +13248,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>160</v>
       </c>
@@ -13270,7 +13269,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>168</v>
       </c>
@@ -13294,7 +13293,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>274</v>
       </c>
@@ -13315,7 +13314,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>275</v>
       </c>
@@ -13336,7 +13335,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>276</v>
       </c>
@@ -13357,7 +13356,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>277</v>
       </c>
@@ -13378,7 +13377,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>278</v>
       </c>
@@ -13399,7 +13398,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>279</v>
       </c>
@@ -13420,7 +13419,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>280</v>
       </c>
@@ -13441,7 +13440,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>281</v>
       </c>
@@ -13462,7 +13461,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>282</v>
       </c>
@@ -13483,7 +13482,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>283</v>
       </c>
@@ -13504,7 +13503,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>224</v>
       </c>
@@ -13527,7 +13526,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>225</v>
       </c>
@@ -13550,7 +13549,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>226</v>
       </c>
@@ -13573,7 +13572,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>418</v>
       </c>
@@ -13599,7 +13598,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>202</v>
       </c>
@@ -13623,7 +13622,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>203</v>
       </c>
@@ -13647,7 +13646,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>204</v>
       </c>
@@ -13671,7 +13670,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>205</v>
       </c>
@@ -13695,7 +13694,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>206</v>
       </c>
@@ -13719,7 +13718,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>207</v>
       </c>
@@ -13749,7 +13748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>208</v>
       </c>
@@ -13773,7 +13772,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>209</v>
       </c>
@@ -13797,7 +13796,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>210</v>
       </c>
@@ -13821,7 +13820,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>211</v>
       </c>
@@ -13845,7 +13844,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>212</v>
       </c>
@@ -13869,7 +13868,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>213</v>
       </c>
@@ -13893,7 +13892,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>214</v>
       </c>
@@ -13917,7 +13916,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>215</v>
       </c>
@@ -13941,7 +13940,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>216</v>
       </c>
@@ -13965,7 +13964,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>217</v>
       </c>
@@ -13989,7 +13988,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>218</v>
       </c>
@@ -14013,7 +14012,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>219</v>
       </c>
@@ -14037,7 +14036,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>220</v>
       </c>
@@ -14061,7 +14060,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>221</v>
       </c>
@@ -14085,7 +14084,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>222</v>
       </c>
@@ -14109,7 +14108,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>223</v>
       </c>
@@ -14133,7 +14132,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>302</v>
       </c>
@@ -14154,7 +14153,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>303</v>
       </c>
@@ -14175,7 +14174,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>304</v>
       </c>
@@ -14196,7 +14195,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>305</v>
       </c>
@@ -14217,7 +14216,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>419</v>
       </c>
@@ -14243,7 +14242,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>177</v>
       </c>
@@ -14264,7 +14263,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>178</v>
       </c>
@@ -14285,7 +14284,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>179</v>
       </c>
@@ -14306,7 +14305,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>180</v>
       </c>
@@ -14327,7 +14326,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>181</v>
       </c>
@@ -14348,7 +14347,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>182</v>
       </c>
@@ -14369,7 +14368,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>183</v>
       </c>
@@ -14390,7 +14389,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>184</v>
       </c>
@@ -14411,7 +14410,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>185</v>
       </c>
@@ -14432,7 +14431,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>186</v>
       </c>
@@ -14453,7 +14452,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>187</v>
       </c>
@@ -14474,7 +14473,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>188</v>
       </c>
@@ -14495,7 +14494,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>189</v>
       </c>
@@ -14516,7 +14515,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>190</v>
       </c>
@@ -14537,7 +14536,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>191</v>
       </c>
@@ -14558,7 +14557,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>192</v>
       </c>
@@ -14579,7 +14578,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>193</v>
       </c>
@@ -14600,7 +14599,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>194</v>
       </c>
@@ -14621,7 +14620,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>195</v>
       </c>
@@ -14642,7 +14641,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>196</v>
       </c>
@@ -14663,7 +14662,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>197</v>
       </c>
@@ -14684,7 +14683,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>198</v>
       </c>
@@ -14705,7 +14704,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>199</v>
       </c>
@@ -14726,7 +14725,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>200</v>
       </c>
@@ -14747,7 +14746,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>201</v>
       </c>
@@ -14768,7 +14767,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>316</v>
       </c>
@@ -14789,7 +14788,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>6</v>
       </c>
@@ -14821,7 +14820,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>9</v>
       </c>
@@ -14853,7 +14852,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>602</v>
       </c>
@@ -14888,7 +14887,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>603</v>
       </c>
@@ -14923,7 +14922,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>8</v>
       </c>
@@ -14961,7 +14960,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>496</v>
       </c>
@@ -14990,7 +14989,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>598</v>
       </c>
@@ -15022,7 +15021,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>597</v>
       </c>
@@ -15054,7 +15053,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>10</v>
       </c>
@@ -15086,7 +15085,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>11</v>
       </c>
@@ -15118,7 +15117,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>498</v>
       </c>
@@ -15147,7 +15146,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>499</v>
       </c>
@@ -15176,7 +15175,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>601</v>
       </c>
@@ -15208,7 +15207,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>600</v>
       </c>
@@ -15240,7 +15239,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>7</v>
       </c>
@@ -15272,7 +15271,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>494</v>
       </c>
@@ -15301,7 +15300,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>497</v>
       </c>
@@ -15330,7 +15329,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>13</v>
       </c>
@@ -15362,7 +15361,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>501</v>
       </c>
@@ -15391,7 +15390,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A279" s="1" t="s">
         <v>502</v>
       </c>
@@ -15420,7 +15419,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A280" s="1" t="s">
         <v>503</v>
       </c>
@@ -15449,7 +15448,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>504</v>
       </c>
@@ -15478,7 +15477,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>505</v>
       </c>
@@ -15507,7 +15506,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>506</v>
       </c>
@@ -15536,7 +15535,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>508</v>
       </c>
@@ -15565,7 +15564,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>509</v>
       </c>
@@ -15594,7 +15593,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>605</v>
       </c>
@@ -15626,7 +15625,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
         <v>606</v>
       </c>
@@ -15658,7 +15657,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
         <v>510</v>
       </c>
@@ -15687,7 +15686,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A289" s="1" t="s">
         <v>511</v>
       </c>
@@ -15716,7 +15715,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
         <v>516</v>
       </c>
@@ -15748,7 +15747,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>517</v>
       </c>
@@ -15780,7 +15779,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A292" s="1" t="s">
         <v>12</v>
       </c>
@@ -15806,7 +15805,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A293" s="1" t="s">
         <v>14</v>
       </c>
@@ -15832,7 +15831,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:20" ht="15" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
         <v>1299</v>
       </c>
@@ -15861,7 +15860,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
         <v>15</v>
       </c>
@@ -15890,7 +15889,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A296" s="1" t="s">
         <v>16</v>
       </c>
@@ -15919,7 +15918,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A297" s="1" t="s">
         <v>17</v>
       </c>
@@ -15948,7 +15947,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>18</v>
       </c>
@@ -15977,7 +15976,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
         <v>19</v>
       </c>
@@ -16006,7 +16005,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>20</v>
       </c>
@@ -16035,7 +16034,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A301" s="1" t="s">
         <v>21</v>
       </c>
@@ -16064,7 +16063,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>22</v>
       </c>
@@ -16093,7 +16092,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>23</v>
       </c>
@@ -16122,7 +16121,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>24</v>
       </c>
@@ -16151,7 +16150,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
         <v>25</v>
       </c>
@@ -16186,7 +16185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
         <v>26</v>
       </c>
@@ -16215,7 +16214,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A307" s="1" t="s">
         <v>27</v>
       </c>
@@ -16244,7 +16243,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>28</v>
       </c>
@@ -16279,7 +16278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A309" s="1" t="s">
         <v>29</v>
       </c>
@@ -16308,7 +16307,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
         <v>30</v>
       </c>
@@ -16343,7 +16342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
         <v>31</v>
       </c>
@@ -16378,7 +16377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
         <v>32</v>
       </c>
@@ -16413,7 +16412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A313" s="1" t="s">
         <v>33</v>
       </c>
@@ -16448,7 +16447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A314" s="1" t="s">
         <v>34</v>
       </c>
@@ -16483,7 +16482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
         <v>227</v>
       </c>
@@ -16504,7 +16503,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A316" s="1" t="s">
         <v>228</v>
       </c>
@@ -16525,7 +16524,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
         <v>229</v>
       </c>
@@ -16546,7 +16545,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A318" s="1" t="s">
         <v>230</v>
       </c>
@@ -16567,7 +16566,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
         <v>1304</v>
       </c>
@@ -16591,7 +16590,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
         <v>169</v>
       </c>
@@ -16615,7 +16614,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
         <v>173</v>
       </c>
@@ -16639,7 +16638,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
         <v>174</v>
       </c>
@@ -16663,7 +16662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
         <v>175</v>
       </c>
@@ -16687,7 +16686,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
         <v>176</v>
       </c>
@@ -16711,7 +16710,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
         <v>344</v>
       </c>
@@ -16734,7 +16733,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>345</v>
       </c>
@@ -16757,7 +16756,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
         <v>346</v>
       </c>
@@ -16780,7 +16779,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A328" s="1" t="s">
         <v>347</v>
       </c>
@@ -16803,7 +16802,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
         <v>348</v>
       </c>
@@ -16826,7 +16825,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
         <v>349</v>
       </c>
@@ -16849,7 +16848,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
         <v>350</v>
       </c>
@@ -16872,7 +16871,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
         <v>351</v>
       </c>
@@ -16895,7 +16894,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
         <v>352</v>
       </c>
@@ -16918,7 +16917,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
         <v>353</v>
       </c>
@@ -16941,7 +16940,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
         <v>354</v>
       </c>
@@ -16964,7 +16963,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
         <v>355</v>
       </c>
@@ -16987,7 +16986,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
         <v>356</v>
       </c>
@@ -17010,7 +17009,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
         <v>357</v>
       </c>
@@ -17033,7 +17032,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
         <v>358</v>
       </c>
@@ -17056,7 +17055,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
         <v>359</v>
       </c>
@@ -17079,7 +17078,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
         <v>360</v>
       </c>
@@ -17102,7 +17101,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
         <v>361</v>
       </c>
@@ -17125,7 +17124,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
         <v>362</v>
       </c>
@@ -17148,7 +17147,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
         <v>363</v>
       </c>
@@ -17171,7 +17170,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
         <v>364</v>
       </c>
@@ -17194,7 +17193,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
         <v>365</v>
       </c>
@@ -17217,7 +17216,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>366</v>
       </c>
@@ -17240,7 +17239,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
         <v>367</v>
       </c>
@@ -17263,7 +17262,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
         <v>368</v>
       </c>
@@ -17286,7 +17285,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
         <v>541</v>
       </c>
@@ -17319,7 +17318,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="351" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
         <v>370</v>
       </c>
@@ -17364,7 +17363,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
         <v>294</v>
       </c>
@@ -17384,7 +17383,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="353" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
         <v>295</v>
       </c>
@@ -17404,7 +17403,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="354" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
         <v>296</v>
       </c>
@@ -17424,7 +17423,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="355" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>550</v>
       </c>
@@ -17456,7 +17455,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="356" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>84</v>
       </c>
@@ -17485,7 +17484,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="357" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>551</v>
       </c>
@@ -17517,7 +17516,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="358" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
         <v>374</v>
       </c>
@@ -17547,7 +17546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>544</v>
       </c>
@@ -17577,7 +17576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="360" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>1075</v>
       </c>
@@ -17618,7 +17617,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="361" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
         <v>1134</v>
       </c>
@@ -17653,7 +17652,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="362" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
         <v>54</v>
       </c>
@@ -17697,7 +17696,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="363" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
         <v>1177</v>
       </c>
@@ -17732,7 +17731,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="364" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>1218</v>
       </c>
@@ -17767,7 +17766,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="365" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>1275</v>
       </c>
@@ -17799,7 +17798,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="366" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>1276</v>
       </c>
@@ -17831,7 +17830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>1077</v>
       </c>
@@ -17872,7 +17871,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="368" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
         <v>1135</v>
       </c>
@@ -17907,7 +17906,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="369" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
         <v>55</v>
       </c>
@@ -17951,7 +17950,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="370" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>1178</v>
       </c>
@@ -17986,7 +17985,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="371" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
         <v>1219</v>
       </c>
@@ -18021,7 +18020,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="372" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
         <v>1263</v>
       </c>
@@ -18050,7 +18049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="373" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
         <v>1264</v>
       </c>
@@ -18079,7 +18078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
         <v>1078</v>
       </c>
@@ -18120,7 +18119,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="375" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
         <v>1136</v>
       </c>
@@ -18155,7 +18154,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="376" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
         <v>56</v>
       </c>
@@ -18199,7 +18198,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="377" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>1179</v>
       </c>
@@ -18234,7 +18233,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="378" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">
         <v>1220</v>
       </c>
@@ -18269,7 +18268,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="379" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A379" s="1" t="s">
         <v>1266</v>
       </c>
@@ -18295,7 +18294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="380" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A380" s="1" t="s">
         <v>1268</v>
       </c>
@@ -18321,7 +18320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A381" s="1" t="s">
         <v>1079</v>
       </c>
@@ -18362,7 +18361,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="382" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A382" s="1" t="s">
         <v>1137</v>
       </c>
@@ -18397,7 +18396,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="383" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A383" s="1" t="s">
         <v>57</v>
       </c>
@@ -18441,7 +18440,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="384" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:21" ht="15" x14ac:dyDescent="0.35">
       <c r="A384" s="1" t="s">
         <v>1284</v>
       </c>
@@ -18476,7 +18475,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="385" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A385" s="1" t="s">
         <v>1180</v>
       </c>
@@ -18511,7 +18510,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="386" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A386" s="1" t="s">
         <v>1286</v>
       </c>
@@ -18546,7 +18545,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="387" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A387" s="1" t="s">
         <v>1221</v>
       </c>
@@ -18581,7 +18580,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="388" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A388" s="1" t="s">
         <v>1288</v>
       </c>
@@ -18616,7 +18615,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="389" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A389" s="1" t="s">
         <v>1290</v>
       </c>
@@ -18651,7 +18650,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="390" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A390" s="1" t="s">
         <v>1269</v>
       </c>
@@ -18677,7 +18676,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A391" s="1" t="s">
         <v>1271</v>
       </c>
@@ -18703,7 +18702,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="392" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A392" s="1" t="s">
         <v>1272</v>
       </c>
@@ -18729,7 +18728,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="393" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A393" s="1" t="s">
         <v>1091</v>
       </c>
@@ -18742,7 +18741,7 @@
       <c r="D393" s="1">
         <v>3</v>
       </c>
-      <c r="F393" s="7" t="s">
+      <c r="F393" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H393" s="1" t="s">
@@ -18770,7 +18769,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="394" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A394" s="1" t="s">
         <v>1138</v>
       </c>
@@ -18783,7 +18782,7 @@
       <c r="D394" s="1">
         <v>3</v>
       </c>
-      <c r="F394" s="7" t="s">
+      <c r="F394" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H394" s="1" t="s">
@@ -18805,7 +18804,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="395" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A395" s="1" t="s">
         <v>58</v>
       </c>
@@ -18818,7 +18817,7 @@
       <c r="D395" s="1">
         <v>3</v>
       </c>
-      <c r="F395" s="7" t="s">
+      <c r="F395" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H395" s="1" t="s">
@@ -18849,7 +18848,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="396" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A396" s="1" t="s">
         <v>1181</v>
       </c>
@@ -18862,7 +18861,7 @@
       <c r="D396" s="1">
         <v>3</v>
       </c>
-      <c r="F396" s="7" t="s">
+      <c r="F396" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H396" s="1" t="s">
@@ -18884,7 +18883,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="397" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A397" s="1" t="s">
         <v>1222</v>
       </c>
@@ -18897,7 +18896,7 @@
       <c r="D397" s="1">
         <v>3</v>
       </c>
-      <c r="F397" s="7" t="s">
+      <c r="F397" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H397" s="1" t="s">
@@ -18919,7 +18918,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="398" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A398" s="1" t="s">
         <v>1295</v>
       </c>
@@ -18932,7 +18931,7 @@
       <c r="D398" s="1">
         <v>3</v>
       </c>
-      <c r="F398" s="7" t="s">
+      <c r="F398" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H398" s="1" t="s">
@@ -18948,7 +18947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="399" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A399" s="1" t="s">
         <v>1296</v>
       </c>
@@ -18961,7 +18960,7 @@
       <c r="D399" s="1">
         <v>3</v>
       </c>
-      <c r="F399" s="7" t="s">
+      <c r="F399" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H399" s="1" t="s">
@@ -18977,7 +18976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A400" s="1" t="s">
         <v>1092</v>
       </c>
@@ -18990,7 +18989,7 @@
       <c r="D400" s="1">
         <v>3</v>
       </c>
-      <c r="F400" s="7" t="s">
+      <c r="F400" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H400" s="1" t="s">
@@ -19015,7 +19014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A401" s="1" t="s">
         <v>1139</v>
       </c>
@@ -19028,7 +19027,7 @@
       <c r="D401" s="1">
         <v>3</v>
       </c>
-      <c r="F401" s="7" t="s">
+      <c r="F401" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H401" s="1" t="s">
@@ -19047,7 +19046,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="402" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A402" s="1" t="s">
         <v>59</v>
       </c>
@@ -19060,7 +19059,7 @@
       <c r="D402" s="1">
         <v>3</v>
       </c>
-      <c r="F402" s="7" t="s">
+      <c r="F402" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H402" s="1" t="s">
@@ -19088,7 +19087,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="403" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A403" s="1" t="s">
         <v>112</v>
       </c>
@@ -19101,7 +19100,7 @@
       <c r="D403" s="1">
         <v>3</v>
       </c>
-      <c r="F403" s="7" t="s">
+      <c r="F403" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H403" s="1" t="s">
@@ -19120,7 +19119,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="404" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A404" s="1" t="s">
         <v>1223</v>
       </c>
@@ -19133,7 +19132,7 @@
       <c r="D404" s="1">
         <v>3</v>
       </c>
-      <c r="F404" s="7" t="s">
+      <c r="F404" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H404" s="1" t="s">
@@ -19152,7 +19151,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="405" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A405" s="1" t="s">
         <v>1093</v>
       </c>
@@ -19165,7 +19164,7 @@
       <c r="D405" s="1">
         <v>3</v>
       </c>
-      <c r="F405" s="7" t="s">
+      <c r="F405" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H405" s="1" t="s">
@@ -19190,7 +19189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="406" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A406" s="1" t="s">
         <v>1140</v>
       </c>
@@ -19203,7 +19202,7 @@
       <c r="D406" s="1">
         <v>3</v>
       </c>
-      <c r="F406" s="7" t="s">
+      <c r="F406" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H406" s="1" t="s">
@@ -19222,7 +19221,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="407" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A407" s="1" t="s">
         <v>60</v>
       </c>
@@ -19235,7 +19234,7 @@
       <c r="D407" s="1">
         <v>3</v>
       </c>
-      <c r="F407" s="7" t="s">
+      <c r="F407" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H407" s="1" t="s">
@@ -19263,7 +19262,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="408" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A408" s="1" t="s">
         <v>1182</v>
       </c>
@@ -19276,7 +19275,7 @@
       <c r="D408" s="1">
         <v>3</v>
       </c>
-      <c r="F408" s="7" t="s">
+      <c r="F408" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H408" s="1" t="s">
@@ -19295,7 +19294,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="409" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A409" s="1" t="s">
         <v>1224</v>
       </c>
@@ -19308,7 +19307,7 @@
       <c r="D409" s="1">
         <v>3</v>
       </c>
-      <c r="F409" s="7" t="s">
+      <c r="F409" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H409" s="1" t="s">
@@ -19327,7 +19326,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="410" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A410" s="1" t="s">
         <v>1094</v>
       </c>
@@ -19340,7 +19339,7 @@
       <c r="D410" s="1">
         <v>4</v>
       </c>
-      <c r="F410" s="7" t="s">
+      <c r="F410" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H410" s="1" t="s">
@@ -19365,7 +19364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="411" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A411" s="1" t="s">
         <v>1141</v>
       </c>
@@ -19378,7 +19377,7 @@
       <c r="D411" s="1">
         <v>4</v>
       </c>
-      <c r="F411" s="7" t="s">
+      <c r="F411" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H411" s="1" t="s">
@@ -19397,7 +19396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="412" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A412" s="1" t="s">
         <v>61</v>
       </c>
@@ -19410,7 +19409,7 @@
       <c r="D412" s="1">
         <v>4</v>
       </c>
-      <c r="F412" s="7" t="s">
+      <c r="F412" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H412" s="1" t="s">
@@ -19438,7 +19437,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="413" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A413" s="1" t="s">
         <v>1183</v>
       </c>
@@ -19451,7 +19450,7 @@
       <c r="D413" s="1">
         <v>4</v>
       </c>
-      <c r="F413" s="7" t="s">
+      <c r="F413" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H413" s="1" t="s">
@@ -19470,7 +19469,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="414" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A414" s="1" t="s">
         <v>1225</v>
       </c>
@@ -19483,7 +19482,7 @@
       <c r="D414" s="1">
         <v>4</v>
       </c>
-      <c r="F414" s="7" t="s">
+      <c r="F414" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H414" s="1" t="s">
@@ -19502,7 +19501,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="415" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A415" s="1" t="s">
         <v>1095</v>
       </c>
@@ -19515,7 +19514,7 @@
       <c r="D415" s="1">
         <v>3</v>
       </c>
-      <c r="F415" s="7" t="s">
+      <c r="F415" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H415" s="1" t="s">
@@ -19540,7 +19539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A416" s="1" t="s">
         <v>1142</v>
       </c>
@@ -19553,7 +19552,7 @@
       <c r="D416" s="1">
         <v>3</v>
       </c>
-      <c r="F416" s="7" t="s">
+      <c r="F416" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H416" s="1" t="s">
@@ -19572,7 +19571,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="417" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A417" s="1" t="s">
         <v>62</v>
       </c>
@@ -19585,7 +19584,7 @@
       <c r="D417" s="1">
         <v>3</v>
       </c>
-      <c r="F417" s="7" t="s">
+      <c r="F417" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H417" s="1" t="s">
@@ -19613,7 +19612,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="418" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A418" s="1" t="s">
         <v>593</v>
       </c>
@@ -19626,7 +19625,7 @@
       <c r="D418" s="1">
         <v>3</v>
       </c>
-      <c r="F418" s="7" t="s">
+      <c r="F418" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H418" s="1" t="s">
@@ -19648,7 +19647,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="419" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A419" s="1" t="s">
         <v>1226</v>
       </c>
@@ -19661,7 +19660,7 @@
       <c r="D419" s="1">
         <v>3</v>
       </c>
-      <c r="F419" s="7" t="s">
+      <c r="F419" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H419" s="1" t="s">
@@ -19680,7 +19679,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="420" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A420" s="1" t="s">
         <v>1096</v>
       </c>
@@ -19693,7 +19692,7 @@
       <c r="D420" s="1">
         <v>3</v>
       </c>
-      <c r="F420" s="7" t="s">
+      <c r="F420" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H420" s="1" t="s">
@@ -19718,7 +19717,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="421" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A421" s="1" t="s">
         <v>1143</v>
       </c>
@@ -19731,7 +19730,7 @@
       <c r="D421" s="1">
         <v>3</v>
       </c>
-      <c r="F421" s="7" t="s">
+      <c r="F421" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H421" s="1" t="s">
@@ -19750,7 +19749,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="422" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A422" s="1" t="s">
         <v>63</v>
       </c>
@@ -19763,7 +19762,7 @@
       <c r="D422" s="1">
         <v>3</v>
       </c>
-      <c r="F422" s="7" t="s">
+      <c r="F422" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H422" s="1" t="s">
@@ -19791,7 +19790,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="423" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A423" s="1" t="s">
         <v>1184</v>
       </c>
@@ -19804,7 +19803,7 @@
       <c r="D423" s="1">
         <v>3</v>
       </c>
-      <c r="F423" s="7" t="s">
+      <c r="F423" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H423" s="1" t="s">
@@ -19826,7 +19825,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="424" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A424" s="1" t="s">
         <v>143</v>
       </c>
@@ -19839,7 +19838,7 @@
       <c r="D424" s="1">
         <v>3</v>
       </c>
-      <c r="F424" s="7" t="s">
+      <c r="F424" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H424" s="1" t="s">
@@ -19858,7 +19857,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="425" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A425" s="1" t="s">
         <v>1097</v>
       </c>
@@ -19871,7 +19870,7 @@
       <c r="D425" s="1">
         <v>3</v>
       </c>
-      <c r="F425" s="7" t="s">
+      <c r="F425" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H425" s="1" t="s">
@@ -19896,7 +19895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="426" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A426" s="1" t="s">
         <v>1144</v>
       </c>
@@ -19909,7 +19908,7 @@
       <c r="D426" s="1">
         <v>3</v>
       </c>
-      <c r="F426" s="7" t="s">
+      <c r="F426" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H426" s="1" t="s">
@@ -19928,7 +19927,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="427" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A427" s="1" t="s">
         <v>64</v>
       </c>
@@ -19941,7 +19940,7 @@
       <c r="D427" s="1">
         <v>3</v>
       </c>
-      <c r="F427" s="7" t="s">
+      <c r="F427" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H427" s="1" t="s">
@@ -19969,7 +19968,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="428" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A428" s="1" t="s">
         <v>1185</v>
       </c>
@@ -19982,7 +19981,7 @@
       <c r="D428" s="1">
         <v>3</v>
       </c>
-      <c r="F428" s="7" t="s">
+      <c r="F428" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H428" s="1" t="s">
@@ -20004,7 +20003,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="429" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A429" s="1" t="s">
         <v>1227</v>
       </c>
@@ -20017,7 +20016,7 @@
       <c r="D429" s="1">
         <v>3</v>
       </c>
-      <c r="F429" s="7" t="s">
+      <c r="F429" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H429" s="1" t="s">
@@ -20036,7 +20035,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="430" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A430" s="1" t="s">
         <v>1098</v>
       </c>
@@ -20049,7 +20048,7 @@
       <c r="D430" s="1">
         <v>4</v>
       </c>
-      <c r="F430" s="7" t="s">
+      <c r="F430" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H430" s="1" t="s">
@@ -20074,7 +20073,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="431" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A431" s="1" t="s">
         <v>1145</v>
       </c>
@@ -20087,7 +20086,7 @@
       <c r="D431" s="1">
         <v>4</v>
       </c>
-      <c r="F431" s="7" t="s">
+      <c r="F431" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H431" s="1" t="s">
@@ -20106,7 +20105,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="432" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A432" s="1" t="s">
         <v>65</v>
       </c>
@@ -20119,7 +20118,7 @@
       <c r="D432" s="1">
         <v>4</v>
       </c>
-      <c r="F432" s="7" t="s">
+      <c r="F432" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H432" s="1" t="s">
@@ -20147,7 +20146,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A433" s="1" t="s">
         <v>1186</v>
       </c>
@@ -20160,7 +20159,7 @@
       <c r="D433" s="1">
         <v>4</v>
       </c>
-      <c r="F433" s="7" t="s">
+      <c r="F433" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H433" s="1" t="s">
@@ -20182,7 +20181,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A434" s="1" t="s">
         <v>1228</v>
       </c>
@@ -20195,7 +20194,7 @@
       <c r="D434" s="1">
         <v>4</v>
       </c>
-      <c r="F434" s="7" t="s">
+      <c r="F434" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H434" s="1" t="s">
@@ -20217,17 +20216,17 @@
   </sheetData>
   <autoFilter ref="A4:T434" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A393:A397 A381:A389 A1:A371 A374:A378 A400:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="23"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A372:A373">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A379:A380">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A390:A392">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A393:A397 A381:A389 A1:A371 A374:A378 A400:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A398:A399">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/configs/Item.xlsx
+++ b/configs/Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F05FC9-0FFF-4860-BB39-17090C7B7BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAF50AD-D5D9-4FC7-8C69-4957151A6D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{03E97168-5F7A-4CBC-B68A-30D1DC85464C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="1352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="1353">
   <si>
     <t>id</t>
   </si>
@@ -7521,6 +7521,9 @@
   </si>
   <si>
     <t>xlrs,2:flrs,2:hlrs,2:warrlvls,2</t>
+  </si>
+  <si>
+    <t>sokinf</t>
   </si>
 </sst>
 </file>
@@ -16934,6 +16937,9 @@
       <c r="N326" s="1">
         <v>4</v>
       </c>
+      <c r="T326" s="1" t="s">
+        <v>1352</v>
+      </c>
       <c r="U326" s="1" t="b">
         <v>1</v>
       </c>

--- a/configs/Item.xlsx
+++ b/configs/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAF50AD-D5D9-4FC7-8C69-4957151A6D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BC316E-6E3E-49B2-8DBD-3408541EE787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{03E97168-5F7A-4CBC-B68A-30D1DC85464C}"/>
+    <workbookView xWindow="4680" yWindow="1170" windowWidth="32160" windowHeight="20430" xr2:uid="{03E97168-5F7A-4CBC-B68A-30D1DC85464C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7534,13 +7534,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -7614,7 +7614,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -7681,7 +7681,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -7997,32 +7997,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U436"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.90625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.36328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.08984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.08984375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.6328125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.7265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.36328125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.36328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9.375" style="1" customWidth="1"/>
     <col min="14" max="14" width="7" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.6328125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.08984375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.90625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.26953125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.26953125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.25" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.25" style="1" customWidth="1"/>
     <col min="20" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8087,7 +8088,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>416</v>
       </c>
@@ -8152,7 +8153,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>44</v>
       </c>
@@ -8160,7 +8161,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>618</v>
       </c>
@@ -8225,7 +8226,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>66</v>
       </c>
@@ -8254,7 +8255,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>231</v>
       </c>
@@ -8283,7 +8284,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>232</v>
       </c>
@@ -8312,7 +8313,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>233</v>
       </c>
@@ -8341,7 +8342,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>234</v>
       </c>
@@ -8370,7 +8371,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>235</v>
       </c>
@@ -8399,7 +8400,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>236</v>
       </c>
@@ -8428,7 +8429,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>237</v>
       </c>
@@ -8463,7 +8464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>238</v>
       </c>
@@ -8498,7 +8499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>239</v>
       </c>
@@ -8527,7 +8528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>240</v>
       </c>
@@ -8556,7 +8557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>241</v>
       </c>
@@ -8591,7 +8592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>242</v>
       </c>
@@ -8626,7 +8627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>243</v>
       </c>
@@ -8661,7 +8662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>159</v>
       </c>
@@ -8690,7 +8691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>163</v>
       </c>
@@ -8728,7 +8729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>164</v>
       </c>
@@ -8766,7 +8767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>165</v>
       </c>
@@ -8804,7 +8805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>297</v>
       </c>
@@ -8833,7 +8834,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>298</v>
       </c>
@@ -8862,7 +8863,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>299</v>
       </c>
@@ -8891,7 +8892,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>300</v>
       </c>
@@ -8926,7 +8927,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>301</v>
       </c>
@@ -8955,7 +8956,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>244</v>
       </c>
@@ -8984,7 +8985,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>245</v>
       </c>
@@ -9013,7 +9014,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>246</v>
       </c>
@@ -9042,7 +9043,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>247</v>
       </c>
@@ -9071,7 +9072,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>248</v>
       </c>
@@ -9100,7 +9101,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>249</v>
       </c>
@@ -9129,7 +9130,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>250</v>
       </c>
@@ -9158,7 +9159,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>251</v>
       </c>
@@ -9187,7 +9188,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>252</v>
       </c>
@@ -9216,7 +9217,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>253</v>
       </c>
@@ -9245,7 +9246,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>254</v>
       </c>
@@ -9274,7 +9275,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>255</v>
       </c>
@@ -9303,7 +9304,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>256</v>
       </c>
@@ -9332,7 +9333,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>257</v>
       </c>
@@ -9361,7 +9362,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>158</v>
       </c>
@@ -9390,7 +9391,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>170</v>
       </c>
@@ -9419,7 +9420,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>317</v>
       </c>
@@ -9448,7 +9449,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>318</v>
       </c>
@@ -9477,7 +9478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>319</v>
       </c>
@@ -9506,7 +9507,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>320</v>
       </c>
@@ -9535,7 +9536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>321</v>
       </c>
@@ -9564,7 +9565,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>322</v>
       </c>
@@ -9593,7 +9594,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>323</v>
       </c>
@@ -9622,7 +9623,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>324</v>
       </c>
@@ -9651,7 +9652,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>325</v>
       </c>
@@ -9680,7 +9681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>326</v>
       </c>
@@ -9709,7 +9710,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>47</v>
       </c>
@@ -9747,7 +9748,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>48</v>
       </c>
@@ -9776,7 +9777,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>589</v>
       </c>
@@ -9814,7 +9815,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>591</v>
       </c>
@@ -9852,7 +9853,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>49</v>
       </c>
@@ -9887,7 +9888,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>50</v>
       </c>
@@ -9916,7 +9917,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>51</v>
       </c>
@@ -9951,7 +9952,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>52</v>
       </c>
@@ -9980,7 +9981,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>53</v>
       </c>
@@ -10009,7 +10010,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>67</v>
       </c>
@@ -10044,7 +10045,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>76</v>
       </c>
@@ -10079,7 +10080,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>258</v>
       </c>
@@ -10108,7 +10109,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="15" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>1302</v>
       </c>
@@ -10128,7 +10129,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>259</v>
       </c>
@@ -10163,7 +10164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>260</v>
       </c>
@@ -10198,7 +10199,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>261</v>
       </c>
@@ -10227,7 +10228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>262</v>
       </c>
@@ -10259,7 +10260,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>77</v>
       </c>
@@ -10286,7 +10287,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>78</v>
       </c>
@@ -10313,7 +10314,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>79</v>
       </c>
@@ -10340,7 +10341,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>80</v>
       </c>
@@ -10367,7 +10368,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>81</v>
       </c>
@@ -10394,7 +10395,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>82</v>
       </c>
@@ -10421,7 +10422,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>83</v>
       </c>
@@ -10448,7 +10449,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>85</v>
       </c>
@@ -10469,7 +10470,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>86</v>
       </c>
@@ -10490,7 +10491,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>87</v>
       </c>
@@ -10511,7 +10512,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>88</v>
       </c>
@@ -10532,7 +10533,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>89</v>
       </c>
@@ -10553,7 +10554,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>90</v>
       </c>
@@ -10574,7 +10575,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>91</v>
       </c>
@@ -10595,7 +10596,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>92</v>
       </c>
@@ -10616,7 +10617,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>93</v>
       </c>
@@ -10637,7 +10638,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>94</v>
       </c>
@@ -10658,7 +10659,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>95</v>
       </c>
@@ -10679,7 +10680,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>96</v>
       </c>
@@ -10700,7 +10701,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>97</v>
       </c>
@@ -10721,7 +10722,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>98</v>
       </c>
@@ -10742,7 +10743,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>99</v>
       </c>
@@ -10763,7 +10764,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>100</v>
       </c>
@@ -10784,7 +10785,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>101</v>
       </c>
@@ -10805,7 +10806,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>102</v>
       </c>
@@ -10826,7 +10827,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>103</v>
       </c>
@@ -10855,7 +10856,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>1184</v>
       </c>
@@ -10890,7 +10891,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>593</v>
       </c>
@@ -10925,7 +10926,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>104</v>
       </c>
@@ -10954,7 +10955,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>105</v>
       </c>
@@ -10983,7 +10984,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>106</v>
       </c>
@@ -11012,7 +11013,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>107</v>
       </c>
@@ -11041,7 +11042,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>108</v>
       </c>
@@ -11070,7 +11071,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>109</v>
       </c>
@@ -11099,7 +11100,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>110</v>
       </c>
@@ -11128,7 +11129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>111</v>
       </c>
@@ -11157,7 +11158,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>1185</v>
       </c>
@@ -11186,7 +11187,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>113</v>
       </c>
@@ -11215,7 +11216,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>142</v>
       </c>
@@ -11244,7 +11245,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="15" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>1305</v>
       </c>
@@ -11264,7 +11265,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>151</v>
       </c>
@@ -11293,7 +11294,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>157</v>
       </c>
@@ -11322,7 +11323,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>161</v>
       </c>
@@ -11351,7 +11352,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>171</v>
       </c>
@@ -11380,7 +11381,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>284</v>
       </c>
@@ -11409,7 +11410,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>285</v>
       </c>
@@ -11438,7 +11439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>286</v>
       </c>
@@ -11467,7 +11468,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>287</v>
       </c>
@@ -11496,7 +11497,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>288</v>
       </c>
@@ -11525,7 +11526,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>289</v>
       </c>
@@ -11554,7 +11555,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>290</v>
       </c>
@@ -11583,7 +11584,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>291</v>
       </c>
@@ -11612,7 +11613,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>292</v>
       </c>
@@ -11641,7 +11642,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>293</v>
       </c>
@@ -11670,7 +11671,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>114</v>
       </c>
@@ -11697,7 +11698,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>115</v>
       </c>
@@ -11724,7 +11725,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>116</v>
       </c>
@@ -11751,7 +11752,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>117</v>
       </c>
@@ -11778,7 +11779,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>118</v>
       </c>
@@ -11805,7 +11806,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>119</v>
       </c>
@@ -11832,7 +11833,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>120</v>
       </c>
@@ -11859,7 +11860,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>121</v>
       </c>
@@ -11880,7 +11881,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>141</v>
       </c>
@@ -11901,7 +11902,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>144</v>
       </c>
@@ -11922,7 +11923,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>148</v>
       </c>
@@ -11943,7 +11944,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>149</v>
       </c>
@@ -11964,7 +11965,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>152</v>
       </c>
@@ -11988,7 +11989,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>166</v>
       </c>
@@ -12009,7 +12010,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>167</v>
       </c>
@@ -12030,7 +12031,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>263</v>
       </c>
@@ -12051,7 +12052,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>264</v>
       </c>
@@ -12072,7 +12073,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>265</v>
       </c>
@@ -12093,7 +12094,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>266</v>
       </c>
@@ -12114,7 +12115,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>267</v>
       </c>
@@ -12135,7 +12136,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>268</v>
       </c>
@@ -12156,7 +12157,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>269</v>
       </c>
@@ -12177,7 +12178,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>270</v>
       </c>
@@ -12198,7 +12199,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>271</v>
       </c>
@@ -12219,7 +12220,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>272</v>
       </c>
@@ -12240,7 +12241,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>273</v>
       </c>
@@ -12261,7 +12262,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>122</v>
       </c>
@@ -12290,7 +12291,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>123</v>
       </c>
@@ -12319,7 +12320,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>124</v>
       </c>
@@ -12348,7 +12349,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>125</v>
       </c>
@@ -12377,7 +12378,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>126</v>
       </c>
@@ -12406,7 +12407,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>127</v>
       </c>
@@ -12435,7 +12436,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>128</v>
       </c>
@@ -12464,7 +12465,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>129</v>
       </c>
@@ -12493,7 +12494,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>1225</v>
       </c>
@@ -12522,7 +12523,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>145</v>
       </c>
@@ -12551,7 +12552,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>146</v>
       </c>
@@ -12580,7 +12581,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>150</v>
       </c>
@@ -12609,7 +12610,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>154</v>
       </c>
@@ -12638,7 +12639,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>156</v>
       </c>
@@ -12667,7 +12668,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>162</v>
       </c>
@@ -12696,7 +12697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>172</v>
       </c>
@@ -12725,7 +12726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>306</v>
       </c>
@@ -12754,7 +12755,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>307</v>
       </c>
@@ -12783,7 +12784,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>308</v>
       </c>
@@ -12812,7 +12813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>309</v>
       </c>
@@ -12841,7 +12842,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>310</v>
       </c>
@@ -12870,7 +12871,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>311</v>
       </c>
@@ -12899,7 +12900,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>312</v>
       </c>
@@ -12928,7 +12929,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>313</v>
       </c>
@@ -12957,7 +12958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>314</v>
       </c>
@@ -12986,7 +12987,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>315</v>
       </c>
@@ -13015,7 +13016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>130</v>
       </c>
@@ -13042,7 +13043,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>131</v>
       </c>
@@ -13069,7 +13070,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>132</v>
       </c>
@@ -13096,7 +13097,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>133</v>
       </c>
@@ -13123,7 +13124,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>134</v>
       </c>
@@ -13150,7 +13151,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>135</v>
       </c>
@@ -13177,7 +13178,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>136</v>
       </c>
@@ -13204,7 +13205,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>137</v>
       </c>
@@ -13225,7 +13226,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>138</v>
       </c>
@@ -13246,7 +13247,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>139</v>
       </c>
@@ -13267,7 +13268,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>140</v>
       </c>
@@ -13288,7 +13289,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>147</v>
       </c>
@@ -13309,7 +13310,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>153</v>
       </c>
@@ -13330,7 +13331,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>155</v>
       </c>
@@ -13351,7 +13352,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>160</v>
       </c>
@@ -13372,7 +13373,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>168</v>
       </c>
@@ -13396,7 +13397,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>274</v>
       </c>
@@ -13417,7 +13418,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>275</v>
       </c>
@@ -13438,7 +13439,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>276</v>
       </c>
@@ -13459,7 +13460,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>277</v>
       </c>
@@ -13480,7 +13481,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>278</v>
       </c>
@@ -13501,7 +13502,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>279</v>
       </c>
@@ -13522,7 +13523,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>280</v>
       </c>
@@ -13543,7 +13544,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>281</v>
       </c>
@@ -13564,7 +13565,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>282</v>
       </c>
@@ -13585,7 +13586,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>283</v>
       </c>
@@ -13606,7 +13607,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>224</v>
       </c>
@@ -13629,7 +13630,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>225</v>
       </c>
@@ -13652,7 +13653,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>226</v>
       </c>
@@ -13675,7 +13676,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>417</v>
       </c>
@@ -13701,7 +13702,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>202</v>
       </c>
@@ -13725,7 +13726,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>203</v>
       </c>
@@ -13749,7 +13750,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>204</v>
       </c>
@@ -13773,7 +13774,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>205</v>
       </c>
@@ -13797,7 +13798,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>206</v>
       </c>
@@ -13821,7 +13822,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>207</v>
       </c>
@@ -13851,7 +13852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>208</v>
       </c>
@@ -13875,7 +13876,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>209</v>
       </c>
@@ -13899,7 +13900,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>210</v>
       </c>
@@ -13923,7 +13924,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>211</v>
       </c>
@@ -13947,7 +13948,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>212</v>
       </c>
@@ -13971,7 +13972,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>213</v>
       </c>
@@ -13995,7 +13996,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>214</v>
       </c>
@@ -14019,7 +14020,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>215</v>
       </c>
@@ -14043,7 +14044,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>216</v>
       </c>
@@ -14067,7 +14068,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>217</v>
       </c>
@@ -14091,7 +14092,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>218</v>
       </c>
@@ -14115,7 +14116,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>219</v>
       </c>
@@ -14139,7 +14140,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="225" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>220</v>
       </c>
@@ -14163,7 +14164,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="226" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>221</v>
       </c>
@@ -14187,7 +14188,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="227" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>222</v>
       </c>
@@ -14211,7 +14212,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="228" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>223</v>
       </c>
@@ -14235,7 +14236,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="229" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>302</v>
       </c>
@@ -14256,7 +14257,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="230" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>303</v>
       </c>
@@ -14277,7 +14278,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="231" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>304</v>
       </c>
@@ -14298,7 +14299,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="232" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>305</v>
       </c>
@@ -14319,7 +14320,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="233" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>418</v>
       </c>
@@ -14345,7 +14346,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="234" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>177</v>
       </c>
@@ -14368,7 +14369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>178</v>
       </c>
@@ -14391,7 +14392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>179</v>
       </c>
@@ -14414,7 +14415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>180</v>
       </c>
@@ -14437,7 +14438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>181</v>
       </c>
@@ -14460,7 +14461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>182</v>
       </c>
@@ -14483,7 +14484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>183</v>
       </c>
@@ -14506,7 +14507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>184</v>
       </c>
@@ -14529,7 +14530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>185</v>
       </c>
@@ -14552,7 +14553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>186</v>
       </c>
@@ -14575,7 +14576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>187</v>
       </c>
@@ -14598,7 +14599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>188</v>
       </c>
@@ -14621,7 +14622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>189</v>
       </c>
@@ -14644,7 +14645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>190</v>
       </c>
@@ -14667,7 +14668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>191</v>
       </c>
@@ -14690,7 +14691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>192</v>
       </c>
@@ -14713,7 +14714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>193</v>
       </c>
@@ -14736,7 +14737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>194</v>
       </c>
@@ -14759,7 +14760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>195</v>
       </c>
@@ -14782,7 +14783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>196</v>
       </c>
@@ -14805,7 +14806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>197</v>
       </c>
@@ -14828,7 +14829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>198</v>
       </c>
@@ -14851,7 +14852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>199</v>
       </c>
@@ -14874,7 +14875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>200</v>
       </c>
@@ -14897,7 +14898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>201</v>
       </c>
@@ -14920,7 +14921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>316</v>
       </c>
@@ -14943,7 +14944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:21" ht="15" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>1309</v>
       </c>
@@ -14978,7 +14979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>6</v>
       </c>
@@ -15010,7 +15011,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="262" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>9</v>
       </c>
@@ -15042,7 +15043,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="263" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>601</v>
       </c>
@@ -15077,7 +15078,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="264" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>602</v>
       </c>
@@ -15112,7 +15113,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="265" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>8</v>
       </c>
@@ -15150,7 +15151,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="266" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>495</v>
       </c>
@@ -15179,7 +15180,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="267" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>597</v>
       </c>
@@ -15211,7 +15212,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="268" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>596</v>
       </c>
@@ -15243,7 +15244,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="269" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>10</v>
       </c>
@@ -15275,7 +15276,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="270" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>11</v>
       </c>
@@ -15307,7 +15308,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="271" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>497</v>
       </c>
@@ -15336,7 +15337,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="272" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>498</v>
       </c>
@@ -15365,7 +15366,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>600</v>
       </c>
@@ -15397,7 +15398,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>599</v>
       </c>
@@ -15429,7 +15430,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>7</v>
       </c>
@@ -15461,7 +15462,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>493</v>
       </c>
@@ -15490,7 +15491,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>496</v>
       </c>
@@ -15519,7 +15520,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>13</v>
       </c>
@@ -15551,7 +15552,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>500</v>
       </c>
@@ -15580,7 +15581,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>501</v>
       </c>
@@ -15609,7 +15610,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>502</v>
       </c>
@@ -15638,7 +15639,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>503</v>
       </c>
@@ -15667,7 +15668,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>504</v>
       </c>
@@ -15696,7 +15697,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>505</v>
       </c>
@@ -15725,7 +15726,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>507</v>
       </c>
@@ -15754,7 +15755,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>508</v>
       </c>
@@ -15783,7 +15784,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>604</v>
       </c>
@@ -15815,7 +15816,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>605</v>
       </c>
@@ -15847,7 +15848,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>509</v>
       </c>
@@ -15876,7 +15877,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>510</v>
       </c>
@@ -15905,7 +15906,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>515</v>
       </c>
@@ -15937,7 +15938,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>516</v>
       </c>
@@ -15969,7 +15970,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>12</v>
       </c>
@@ -15995,7 +15996,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>14</v>
       </c>
@@ -16021,7 +16022,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="295" spans="1:20" ht="15" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>1293</v>
       </c>
@@ -16050,7 +16051,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>15</v>
       </c>
@@ -16079,7 +16080,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>16</v>
       </c>
@@ -16108,7 +16109,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>17</v>
       </c>
@@ -16137,7 +16138,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>18</v>
       </c>
@@ -16166,7 +16167,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>19</v>
       </c>
@@ -16195,7 +16196,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>20</v>
       </c>
@@ -16224,7 +16225,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>21</v>
       </c>
@@ -16253,7 +16254,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>22</v>
       </c>
@@ -16282,7 +16283,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>23</v>
       </c>
@@ -16311,7 +16312,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>24</v>
       </c>
@@ -16340,7 +16341,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>25</v>
       </c>
@@ -16375,7 +16376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>26</v>
       </c>
@@ -16404,7 +16405,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>27</v>
       </c>
@@ -16433,7 +16434,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>28</v>
       </c>
@@ -16468,7 +16469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>29</v>
       </c>
@@ -16497,7 +16498,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>30</v>
       </c>
@@ -16538,7 +16539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>31</v>
       </c>
@@ -16573,7 +16574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>32</v>
       </c>
@@ -16608,7 +16609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>33</v>
       </c>
@@ -16643,7 +16644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>34</v>
       </c>
@@ -16678,7 +16679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>227</v>
       </c>
@@ -16699,7 +16700,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>228</v>
       </c>
@@ -16720,7 +16721,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>229</v>
       </c>
@@ -16741,7 +16742,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>230</v>
       </c>
@@ -16762,7 +16763,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="320" spans="1:14" ht="15" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>1298</v>
       </c>
@@ -16786,7 +16787,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="321" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>169</v>
       </c>
@@ -16810,7 +16811,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="322" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>173</v>
       </c>
@@ -16834,7 +16835,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="323" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>174</v>
       </c>
@@ -16858,7 +16859,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="324" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>175</v>
       </c>
@@ -16882,7 +16883,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="325" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>176</v>
       </c>
@@ -16906,7 +16907,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="326" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>1328</v>
       </c>
@@ -16944,7 +16945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>344</v>
       </c>
@@ -16967,7 +16968,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="328" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>345</v>
       </c>
@@ -16990,7 +16991,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="329" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>346</v>
       </c>
@@ -17013,7 +17014,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="330" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>347</v>
       </c>
@@ -17036,7 +17037,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="331" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>348</v>
       </c>
@@ -17059,7 +17060,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="332" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>349</v>
       </c>
@@ -17082,7 +17083,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="333" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>350</v>
       </c>
@@ -17105,7 +17106,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="334" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>351</v>
       </c>
@@ -17128,7 +17129,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="335" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>352</v>
       </c>
@@ -17151,7 +17152,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="336" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>353</v>
       </c>
@@ -17174,7 +17175,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>354</v>
       </c>
@@ -17197,7 +17198,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>355</v>
       </c>
@@ -17220,7 +17221,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>356</v>
       </c>
@@ -17243,7 +17244,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>357</v>
       </c>
@@ -17266,7 +17267,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>358</v>
       </c>
@@ -17289,7 +17290,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>359</v>
       </c>
@@ -17312,7 +17313,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>360</v>
       </c>
@@ -17335,7 +17336,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>361</v>
       </c>
@@ -17358,7 +17359,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>362</v>
       </c>
@@ -17381,7 +17382,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>363</v>
       </c>
@@ -17404,7 +17405,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>364</v>
       </c>
@@ -17427,7 +17428,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>365</v>
       </c>
@@ -17450,7 +17451,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>366</v>
       </c>
@@ -17473,7 +17474,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>367</v>
       </c>
@@ -17496,7 +17497,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="351" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>368</v>
       </c>
@@ -17519,7 +17520,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>540</v>
       </c>
@@ -17552,7 +17553,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="353" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>370</v>
       </c>
@@ -17597,7 +17598,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="354" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>294</v>
       </c>
@@ -17617,7 +17618,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="355" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>295</v>
       </c>
@@ -17637,7 +17638,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="356" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>296</v>
       </c>
@@ -17657,7 +17658,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="357" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>549</v>
       </c>
@@ -17689,7 +17690,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="358" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>84</v>
       </c>
@@ -17718,7 +17719,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="359" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>550</v>
       </c>
@@ -17750,7 +17751,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="360" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>374</v>
       </c>
@@ -17780,7 +17781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="361" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>543</v>
       </c>
@@ -17810,7 +17811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="362" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>1073</v>
       </c>
@@ -17851,7 +17852,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="363" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>1132</v>
       </c>
@@ -17886,7 +17887,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="364" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>54</v>
       </c>
@@ -17927,7 +17928,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="365" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>1174</v>
       </c>
@@ -17962,7 +17963,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="366" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>1214</v>
       </c>
@@ -17997,7 +17998,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="367" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>1270</v>
       </c>
@@ -18029,7 +18030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>1271</v>
       </c>
@@ -18061,7 +18062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>1075</v>
       </c>
@@ -18102,7 +18103,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="370" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>1133</v>
       </c>
@@ -18137,7 +18138,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="371" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>55</v>
       </c>
@@ -18178,7 +18179,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="372" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>1175</v>
       </c>
@@ -18213,7 +18214,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="373" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>1215</v>
       </c>
@@ -18248,7 +18249,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="374" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>1258</v>
       </c>
@@ -18277,7 +18278,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="375" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>1259</v>
       </c>
@@ -18306,7 +18307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>1076</v>
       </c>
@@ -18347,7 +18348,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="377" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>1134</v>
       </c>
@@ -18382,7 +18383,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="378" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>56</v>
       </c>
@@ -18423,7 +18424,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="379" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>1176</v>
       </c>
@@ -18458,7 +18459,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="380" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>1216</v>
       </c>
@@ -18493,7 +18494,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="381" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>1261</v>
       </c>
@@ -18519,7 +18520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="382" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>1263</v>
       </c>
@@ -18545,7 +18546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>1077</v>
       </c>
@@ -18586,7 +18587,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="384" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>1135</v>
       </c>
@@ -18627,7 +18628,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="385" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>57</v>
       </c>
@@ -18668,7 +18669,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="386" spans="1:19" ht="15" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>1279</v>
       </c>
@@ -18709,7 +18710,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="387" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>1177</v>
       </c>
@@ -18750,7 +18751,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="388" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>1281</v>
       </c>
@@ -18791,7 +18792,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="389" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>1217</v>
       </c>
@@ -18832,7 +18833,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="390" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>1283</v>
       </c>
@@ -18873,7 +18874,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="391" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>1285</v>
       </c>
@@ -18914,7 +18915,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="392" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>1264</v>
       </c>
@@ -18943,7 +18944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>1266</v>
       </c>
@@ -18972,7 +18973,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="394" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>1267</v>
       </c>
@@ -19001,7 +19002,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="395" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>1089</v>
       </c>
@@ -19042,7 +19043,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="396" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>1136</v>
       </c>
@@ -19077,7 +19078,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="397" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>58</v>
       </c>
@@ -19118,7 +19119,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="398" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>1178</v>
       </c>
@@ -19153,7 +19154,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="399" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>1218</v>
       </c>
@@ -19188,7 +19189,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="400" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>1289</v>
       </c>
@@ -19217,7 +19218,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>1290</v>
       </c>
@@ -19246,7 +19247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1090</v>
       </c>
@@ -19284,7 +19285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>1137</v>
       </c>
@@ -19316,7 +19317,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="404" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>59</v>
       </c>
@@ -19354,7 +19355,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="405" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>112</v>
       </c>
@@ -19386,7 +19387,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="406" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>1219</v>
       </c>
@@ -19418,7 +19419,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="407" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>1091</v>
       </c>
@@ -19456,7 +19457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="408" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>1138</v>
       </c>
@@ -19488,7 +19489,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="409" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>60</v>
       </c>
@@ -19526,7 +19527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="410" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>1179</v>
       </c>
@@ -19558,7 +19559,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="411" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>1220</v>
       </c>
@@ -19590,7 +19591,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="412" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>1092</v>
       </c>
@@ -19628,7 +19629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="413" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>1139</v>
       </c>
@@ -19660,7 +19661,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="414" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>61</v>
       </c>
@@ -19698,7 +19699,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="415" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>1180</v>
       </c>
@@ -19730,7 +19731,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="416" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>1221</v>
       </c>
@@ -19762,7 +19763,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>1093</v>
       </c>
@@ -19800,7 +19801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>1140</v>
       </c>
@@ -19832,7 +19833,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>62</v>
       </c>
@@ -19870,7 +19871,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>592</v>
       </c>
@@ -19905,7 +19906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>1222</v>
       </c>
@@ -19937,7 +19938,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>1094</v>
       </c>
@@ -19975,7 +19976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>1141</v>
       </c>
@@ -20007,7 +20008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>63</v>
       </c>
@@ -20045,7 +20046,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>1181</v>
       </c>
@@ -20080,7 +20081,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>143</v>
       </c>
@@ -20112,7 +20113,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>1095</v>
       </c>
@@ -20150,7 +20151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>1142</v>
       </c>
@@ -20182,7 +20183,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>64</v>
       </c>
@@ -20220,7 +20221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>1182</v>
       </c>
@@ -20255,7 +20256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>1223</v>
       </c>
@@ -20287,7 +20288,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>1096</v>
       </c>
@@ -20325,7 +20326,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>1143</v>
       </c>
@@ -20357,7 +20358,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>65</v>
       </c>
@@ -20395,7 +20396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>1183</v>
       </c>
@@ -20430,7 +20431,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>1224</v>
       </c>
@@ -20463,7 +20464,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T436" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}"/>
+  <autoFilter ref="A4:T436" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A374:A375">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
